--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="223">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -50,46 +50,52 @@
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>7. Otro</t>
+  </si>
+  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>7. Otro</t>
+    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
     <t>3. Falla De Rotación</t>
   </si>
   <si>
-    <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
+    <t>LANZA</t>
   </si>
   <si>
     <t>TAT MEDELLIN</t>
   </si>
   <si>
+    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+  </si>
+  <si>
     <t>FABIO GOMEZ</t>
   </si>
   <si>
     <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
   </si>
   <si>
-    <t>LANZA</t>
-  </si>
-  <si>
-    <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
+    <t>6. Transformación De Referencias</t>
+  </si>
+  <si>
+    <t>Pendiente Transformar Roto GT Por manipulación</t>
   </si>
   <si>
     <t>TAT CARTAGENA</t>
@@ -98,52 +104,61 @@
     <t>Dilan Barraza</t>
   </si>
   <si>
-    <t>6. Transformación De Referencias</t>
+    <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>Pendiente Transformar Roto GT Por manipulación</t>
-  </si>
-  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t>HUEVO B X30 CARTON GRIS</t>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>se equivocaron al cargar una estiba</t>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
+    <t>PALMAS</t>
   </si>
   <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
     <t>TAT CALI</t>
   </si>
   <si>
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
     <t>TAT CUCUTA</t>
@@ -152,31 +167,25 @@
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
-  </si>
-  <si>
     <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
-  </si>
-  <si>
-    <t>PALMAS</t>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>Clientes FS</t>
   </si>
   <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
     <t>Transformación de PET</t>
@@ -185,9 +194,6 @@
     <t>ANDRES MEJIA</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
   </si>
   <si>
@@ -197,52 +203,55 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
+    <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
-  </si>
-  <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+  </si>
+  <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -251,48 +260,63 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
+    <t>ALKA1</t>
+  </si>
+  <si>
     <t>TAT BARRANQUILLA</t>
   </si>
   <si>
     <t>Jhonatan Gomez</t>
   </si>
   <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+  </si>
+  <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
+  </si>
+  <si>
+    <t>Cargo en incubación</t>
   </si>
   <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
@@ -302,34 +326,25 @@
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
-    <t>ALKA1</t>
-  </si>
-  <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
     <t>Yovanis Arevalo</t>
   </si>
   <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
+    <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
+    <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
     <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
@@ -338,175 +353,181 @@
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
-  </si>
-  <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Se envía producto a Sincelejo con menor edad</t>
   </si>
   <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
     <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+    <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
     <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
-  </si>
-  <si>
     <t>TAT BUCARAMANGA</t>
   </si>
   <si>
     <t>SHIRLEY ARIZA</t>
   </si>
   <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
     <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
   </si>
   <si>
     <t>Producto queda en CEDI por calidad</t>
   </si>
   <si>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
     <t>Producto devuelto clientes TAT</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
+    <t>vehiculo pendiente pro llegar a planta</t>
   </si>
   <si>
     <t xml:space="preserve">ALEXANDER PEÑA </t>
   </si>
   <si>
+    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
+  </si>
+  <si>
     <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
   </si>
   <si>
     <t>ANDRES MEJA</t>
   </si>
   <si>
+    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
+  </si>
+  <si>
+    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
+  </si>
+  <si>
     <t>Se envía lotemás nuevo a Sincelejo</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
+    <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
+  </si>
+  <si>
+    <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
+  </si>
+  <si>
+    <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
   </si>
   <si>
     <t>Se envía huevo más fresco para clientes FS</t>
   </si>
   <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
+    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
   </si>
   <si>
     <t>Producto enviado a Rionegro y para FS más fresco</t>
-  </si>
-  <si>
-    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
-  </si>
-  <si>
-    <t>yOVANIS AREVALO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
-  </si>
-  <si>
-    <t>Se envía huevo fresco a Rionegro</t>
-  </si>
-  <si>
-    <t>Clientes Fs</t>
-  </si>
-  <si>
-    <t>Se envían para Rionegro con mejor fecha</t>
-  </si>
-  <si>
-    <t>Llega de planta bellavista</t>
-  </si>
-  <si>
-    <t>Jhonathan Gomez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
-  </si>
-  <si>
-    <t>LLegada de planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asignado canal TAT </t>
-  </si>
-  <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yovanis Arevalo </t>
-  </si>
-  <si>
-    <t>vehiculo pendiente pro llegar a planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salida de pedido especial </t>
-  </si>
-  <si>
-    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
-  </si>
-  <si>
-    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
-  </si>
-  <si>
-    <t>novedad en lotes por calidad</t>
-  </si>
-  <si>
-    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
-  </si>
-  <si>
-    <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
-  </si>
-  <si>
-    <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
-  </si>
-  <si>
-    <t>Productoenviado a Rionegro más fresco</t>
-  </si>
-  <si>
-    <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
-  </si>
-  <si>
-    <t>DIANA VITERIA</t>
-  </si>
-  <si>
-    <t>ERROR EN DIGITACION DE LAS EDAD</t>
-  </si>
-  <si>
-    <t>Pedidos para FD más fresco</t>
-  </si>
-  <si>
-    <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
-  </si>
-  <si>
-    <t>Padidos para FS con mayor frescura</t>
-  </si>
-  <si>
-    <t>Pendiente Transformacion a suelto</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
   </si>
   <si>
     <t xml:space="preserve"> estaba programado para despacho a tat cali, planeación quito el pedido y se nos notificó que se debía dar rotación inmediatamente.
 En simultáneo, se cargó la mula y se desencadenaron las 18.000 unidades de 112379 para despachar para Medellín. En esta acción nos percatamos solo cuando la mula ya estaba en un 70 % cargada que se nos estaban quedando 21.525 de la referencia L canastas (2110302) con fecha de producción 19/08/2026.</t>
   </si>
   <si>
+    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
+  </si>
+  <si>
+    <t>yOVANIS AREVALO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
+  </si>
+  <si>
+    <t>Se envía huevo fresco a Rionegro</t>
+  </si>
+  <si>
+    <t>REPOSICION SIN SOLTAR</t>
+  </si>
+  <si>
+    <t>Clientes Fs</t>
+  </si>
+  <si>
+    <t>Se envían para Rionegro con mejor fecha</t>
+  </si>
+  <si>
+    <t>Llega de planta bellavista</t>
+  </si>
+  <si>
+    <t>Jhonathan Gomez</t>
+  </si>
+  <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
+  </si>
+  <si>
+    <t>LLegada de planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asignado canal TAT </t>
+  </si>
+  <si>
+    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yovanis Arevalo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">salida de pedido especial </t>
+  </si>
+  <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>novedad en lotes por calidad</t>
+  </si>
+  <si>
+    <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
+  </si>
+  <si>
+    <t>Productoenviado a Rionegro más fresco</t>
+  </si>
+  <si>
+    <t>DIANA VITERIA</t>
+  </si>
+  <si>
+    <t>ERROR EN DIGITACION DE LAS EDAD</t>
+  </si>
+  <si>
+    <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Pedidos para FD más fresco</t>
+  </si>
+  <si>
+    <t>Padidos para FS con mayor frescura</t>
+  </si>
+  <si>
+    <t>Pendiente Transformacion a suelto</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
+  </si>
+  <si>
     <t>se registra mal el dia de ayer el lote de 2 dias</t>
   </si>
   <si>
@@ -519,9 +540,6 @@
     <t>DIANA  CAROLINA VITERI</t>
   </si>
   <si>
-    <t>REPOSICION SIN SOLTAR</t>
-  </si>
-  <si>
     <t>se realizo la entrega el día de hoy un asesor no habia pedido el producto</t>
   </si>
   <si>
@@ -558,9 +576,6 @@
     <t>Producto enviado para Sincelejo con menor edad</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cliente madamia </t>
   </si>
   <si>
@@ -579,9 +594,6 @@
     <t xml:space="preserve">JONATHAN MOSQUERA </t>
   </si>
   <si>
-    <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
-  </si>
-  <si>
     <t xml:space="preserve">FABIO GOMEZ </t>
   </si>
   <si>
@@ -594,9 +606,6 @@
     <t>SANTIAGO ARCHIBON</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
     <t xml:space="preserve">SE PASO A BAJA ROTACION </t>
   </si>
   <si>
@@ -630,9 +639,6 @@
     <t xml:space="preserve">CLIENTES FS  </t>
   </si>
   <si>
-    <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
-  </si>
-  <si>
     <t>Se carga en sugeridos</t>
   </si>
   <si>
@@ -640,12 +646,6 @@
   </si>
   <si>
     <t>LLEGO DESDE PLANTA PALMAS  REMISION 18250 PLACA NHP609</t>
-  </si>
-  <si>
-    <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
   </si>
   <si>
     <t>Devoluciones en las rutas de preventa que se bandejean para sacar hoy</t>
@@ -782,11 +782,11 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -809,11 +809,11 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -905,7 +905,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J179" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J179" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -923,7 +923,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J106" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J108" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1199,7 +1199,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="8">
         <v>359100.0</v>
@@ -1219,10 +1219,10 @@
         <v>46205.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="8">
         <v>2110402.0</v>
@@ -1239,8 +1239,8 @@
       <c r="H3" s="8">
         <v>260675.0</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>19</v>
+      <c r="I3" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J3" s="9"/>
     </row>
@@ -1249,16 +1249,16 @@
         <v>46205.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8">
         <v>21120.0</v>
@@ -1269,7 +1269,7 @@
       <c r="H4" s="8">
         <v>16920.0</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="9"/>
@@ -1279,16 +1279,16 @@
         <v>46205.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="8">
         <v>75680.0</v>
@@ -1299,11 +1299,11 @@
       <c r="H5" s="8">
         <v>3134.0</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="13" t="s">
+      <c r="I5" s="13" t="s">
         <v>32</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -1311,16 +1311,16 @@
         <v>46206.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="8">
         <v>189540.0</v>
@@ -1331,11 +1331,11 @@
       <c r="H6" s="8">
         <v>144720.0</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>34</v>
+      <c r="I6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -1343,16 +1343,16 @@
         <v>46206.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F7" s="8">
         <v>20640.0</v>
@@ -1363,11 +1363,11 @@
       <c r="H7" s="8">
         <v>13920.0</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>37</v>
+      <c r="I7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -1375,16 +1375,16 @@
         <v>46206.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="8">
         <v>152384.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F8" s="8">
         <v>14700.0</v>
@@ -1395,26 +1395,26 @@
       <c r="H8" s="8">
         <v>9600.0</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="13"/>
+      <c r="I8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
       <c r="A9" s="7">
         <v>46206.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D9" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="8">
         <v>228240.0</v>
@@ -1425,26 +1425,26 @@
       <c r="H9" s="8">
         <v>124260.0</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" s="13"/>
+      <c r="I9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
       <c r="A10" s="7">
         <v>46206.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D10" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F10" s="8">
         <v>7830.0</v>
@@ -1455,8 +1455,8 @@
       <c r="H10" s="8">
         <v>6030.0</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>28</v>
+      <c r="I10" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="J10" s="15"/>
     </row>
@@ -1465,10 +1465,10 @@
         <v>46206.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11" s="8">
         <v>2110402.0</v>
@@ -1485,11 +1485,11 @@
       <c r="H11" s="8">
         <v>23040.0</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>50</v>
+      <c r="I11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
@@ -1497,16 +1497,16 @@
         <v>46206.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12" s="8">
         <v>51387.0</v>
@@ -1517,11 +1517,11 @@
       <c r="H12" s="8">
         <v>12170.0</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>53</v>
+      <c r="I12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
@@ -1529,10 +1529,10 @@
         <v>46209.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="8">
         <v>2110402.0</v>
@@ -1549,11 +1549,11 @@
       <c r="H13" s="8">
         <v>133410.0</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>53</v>
+      <c r="I13" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -1561,10 +1561,10 @@
         <v>46209.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="8">
         <v>2110402.0</v>
@@ -1581,11 +1581,11 @@
       <c r="H14" s="8">
         <v>424588.0</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>55</v>
+      <c r="I14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -1593,16 +1593,16 @@
         <v>46209.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F15" s="8">
         <v>14160.0</v>
@@ -1613,11 +1613,11 @@
       <c r="H15" s="8">
         <v>12360.0</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>58</v>
+      <c r="I15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -1625,16 +1625,16 @@
         <v>46210.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16" s="8">
         <v>149040.0</v>
@@ -1645,26 +1645,26 @@
       <c r="H16" s="8">
         <v>289680.0</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="13"/>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="7">
         <v>46210.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F17" s="8">
         <v>22770.0</v>
@@ -1675,26 +1675,26 @@
       <c r="H17" s="8">
         <v>19770.0</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="7">
         <v>46210.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D18" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F18" s="8">
         <v>222021.0</v>
@@ -1705,20 +1705,20 @@
       <c r="H18" s="8">
         <v>162125.0</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="13"/>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
       <c r="A19" s="7">
         <v>46211.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" s="8">
         <v>2110402.0</v>
@@ -1735,11 +1735,11 @@
       <c r="H19" s="8">
         <v>401280.0</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>63</v>
+      <c r="I19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -1747,10 +1747,10 @@
         <v>46211.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="8">
         <v>2110402.0</v>
@@ -1767,26 +1767,26 @@
       <c r="H20" s="8">
         <v>74040.0</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="13"/>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
       <c r="A21" s="7">
         <v>46211.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D21" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F21" s="8">
         <v>162125.0</v>
@@ -1797,11 +1797,11 @@
       <c r="H21" s="8">
         <v>100687.0</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>64</v>
+      <c r="I21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -1818,7 +1818,7 @@
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F22" s="8">
         <v>32850.0</v>
@@ -1829,26 +1829,26 @@
       <c r="H22" s="8">
         <v>32700.0</v>
       </c>
-      <c r="I22" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="13"/>
+      <c r="I22" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="7">
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D23" s="8">
         <v>112271.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F23" s="8">
         <v>16500.0</v>
@@ -1859,26 +1859,26 @@
       <c r="H23" s="8">
         <v>18000.0</v>
       </c>
-      <c r="I23" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J23" s="13"/>
+      <c r="I23" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="7">
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D24" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" s="8">
         <v>190047.0</v>
@@ -1889,26 +1889,26 @@
       <c r="H24" s="8">
         <v>248481.0</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="13"/>
+      <c r="I24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="7">
         <v>46212.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D25" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F25" s="8">
         <v>178080.0</v>
@@ -1919,20 +1919,20 @@
       <c r="H25" s="8">
         <v>203520.0</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J25" s="13"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="7">
         <v>46212.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D26" s="8">
         <v>2110402.0</v>
@@ -1949,11 +1949,11 @@
       <c r="H26" s="8">
         <v>13200.0</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>70</v>
+      <c r="I26" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
@@ -1961,16 +1961,16 @@
         <v>46212.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D27" s="8">
         <v>112271.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F27" s="8">
         <v>18000.0</v>
@@ -1981,10 +1981,10 @@
       <c r="H27" s="8">
         <v>13500.0</v>
       </c>
-      <c r="I27" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="13"/>
+      <c r="I27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="7">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D28" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F28" s="8">
         <v>208440.0</v>
@@ -2011,11 +2011,11 @@
       <c r="H28" s="8">
         <v>150833.0</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>72</v>
+      <c r="I28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
@@ -2026,13 +2026,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D29" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" s="8">
         <v>962820.0</v>
@@ -2043,11 +2043,11 @@
       <c r="H29" s="8">
         <v>922140.0</v>
       </c>
-      <c r="I29" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>72</v>
+      <c r="I29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
@@ -2055,16 +2055,16 @@
         <v>46213.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D30" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="8">
         <v>335340.0</v>
@@ -2075,11 +2075,11 @@
       <c r="H30" s="8">
         <v>381600.0</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>73</v>
+      <c r="I30" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
@@ -2087,16 +2087,16 @@
         <v>46213.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D31" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F31" s="8">
         <v>316800.0</v>
@@ -2107,26 +2107,26 @@
       <c r="H31" s="8">
         <v>229680.0</v>
       </c>
-      <c r="I31" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="13"/>
+      <c r="I31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
       <c r="A32" s="7">
         <v>46213.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D32" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F32" s="8">
         <v>176850.0</v>
@@ -2137,20 +2137,20 @@
       <c r="H32" s="8">
         <v>128971.0</v>
       </c>
-      <c r="I32" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="13"/>
+      <c r="I32" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
       <c r="A33" s="7">
         <v>46213.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D33" s="8">
         <v>2110402.0</v>
@@ -2167,26 +2167,26 @@
       <c r="H33" s="8">
         <v>25440.0</v>
       </c>
-      <c r="I33" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="13"/>
+      <c r="I33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
       <c r="A34" s="7">
         <v>46217.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D34" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F34" s="8">
         <v>481440.0</v>
@@ -2197,26 +2197,26 @@
       <c r="H34" s="8">
         <v>151435.0</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="13"/>
+      <c r="I34" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="7">
         <v>46217.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D35" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" s="8">
         <v>355720.0</v>
@@ -2227,10 +2227,10 @@
       <c r="H35" s="8">
         <v>302760.0</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J35" s="13"/>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="7">
@@ -2240,13 +2240,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D36" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F36" s="8">
         <v>35280.0</v>
@@ -2257,11 +2257,11 @@
       <c r="H36" s="8">
         <v>37926.0</v>
       </c>
-      <c r="I36" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>80</v>
+      <c r="I36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -2272,13 +2272,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D37" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F37" s="8">
         <v>272073.0</v>
@@ -2289,11 +2289,11 @@
       <c r="H37" s="8">
         <v>275205.0</v>
       </c>
-      <c r="I37" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>82</v>
+      <c r="I37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
@@ -2304,13 +2304,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D38" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F38" s="8">
         <v>37926.0</v>
@@ -2321,11 +2321,11 @@
       <c r="H38" s="8">
         <v>25746.0</v>
       </c>
-      <c r="I38" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>80</v>
+      <c r="I38" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
@@ -2333,10 +2333,10 @@
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D39" s="8">
         <v>2110402.0</v>
@@ -2353,11 +2353,11 @@
       <c r="H39" s="8">
         <v>16320.0</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>84</v>
+      <c r="I39" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -2365,16 +2365,16 @@
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F40" s="8">
         <v>10980.0</v>
@@ -2385,26 +2385,26 @@
       <c r="H40" s="8">
         <v>13500.0</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="13"/>
+      <c r="I40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="7">
         <v>46219.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F41" s="8">
         <v>130320.0</v>
@@ -2415,11 +2415,11 @@
       <c r="H41" s="8">
         <v>90480.0</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>86</v>
+      <c r="I41" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
@@ -2427,16 +2427,16 @@
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D42" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F42" s="8">
         <v>36225.0</v>
@@ -2447,26 +2447,26 @@
       <c r="H42" s="8">
         <v>27570.0</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J42" s="13"/>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="7">
         <v>46219.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D43" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F43" s="8">
         <v>152833.0</v>
@@ -2477,11 +2477,11 @@
       <c r="H43" s="8">
         <v>96472.0</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J43" s="13" t="s">
-        <v>89</v>
+      <c r="J43" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
@@ -2489,16 +2489,16 @@
         <v>46219.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D44" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F44" s="8">
         <v>237828.0</v>
@@ -2509,10 +2509,10 @@
       <c r="H44" s="8">
         <v>71560.0</v>
       </c>
-      <c r="I44" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="13"/>
+      <c r="I44" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="7">
@@ -2522,13 +2522,13 @@
         <v>10</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D45" s="8">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F45" s="8">
         <v>31125.0</v>
@@ -2539,11 +2539,11 @@
       <c r="H45" s="8">
         <v>31845.0</v>
       </c>
-      <c r="I45" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>90</v>
+      <c r="I45" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -2554,13 +2554,13 @@
         <v>10</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D46" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F46" s="8">
         <v>25746.0</v>
@@ -2571,11 +2571,11 @@
       <c r="H46" s="8">
         <v>28683.0</v>
       </c>
-      <c r="I46" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>80</v>
+      <c r="I46" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
@@ -2586,13 +2586,13 @@
         <v>10</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D47" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F47" s="8">
         <v>261166.0</v>
@@ -2603,11 +2603,11 @@
       <c r="H47" s="8">
         <v>221549.0</v>
       </c>
-      <c r="I47" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>92</v>
+      <c r="I47" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
@@ -2618,13 +2618,13 @@
         <v>10</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D48" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F48" s="8">
         <v>115289.0</v>
@@ -2635,20 +2635,20 @@
       <c r="H48" s="8">
         <v>119584.0</v>
       </c>
-      <c r="I48" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" s="13"/>
+      <c r="I48" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="7">
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" s="8">
         <v>2110402.0</v>
@@ -2665,11 +2665,11 @@
       <c r="H49" s="8">
         <v>287235.0</v>
       </c>
-      <c r="I49" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>93</v>
+      <c r="I49" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" s="12" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
@@ -2677,10 +2677,10 @@
         <v>46224.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D50" s="8">
         <v>2110402.0</v>
@@ -2697,11 +2697,11 @@
       <c r="H50" s="8">
         <v>551645.0</v>
       </c>
-      <c r="I50" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>94</v>
+      <c r="I50" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
@@ -2709,16 +2709,16 @@
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D51" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F51" s="8">
         <v>130560.0</v>
@@ -2729,11 +2729,11 @@
       <c r="H51" s="8">
         <v>153840.0</v>
       </c>
-      <c r="I51" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>95</v>
+      <c r="I51" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
@@ -2741,16 +2741,16 @@
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D52" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F52" s="8">
         <v>87447.0</v>
@@ -2761,10 +2761,10 @@
       <c r="H52" s="8">
         <v>104365.0</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52" s="13"/>
+      <c r="I52" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="7">
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D53" s="8">
         <v>2110402.0</v>
@@ -2791,11 +2791,11 @@
       <c r="H53" s="8">
         <v>25920.0</v>
       </c>
-      <c r="I53" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>98</v>
+      <c r="I53" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
@@ -2803,10 +2803,10 @@
         <v>46226.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D54" s="8">
         <v>2110402.0</v>
@@ -2823,11 +2823,11 @@
       <c r="H54" s="8">
         <v>226069.0</v>
       </c>
-      <c r="I54" s="12" t="s">
+      <c r="I54" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J54" s="13" t="s">
-        <v>101</v>
+      <c r="J54" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
@@ -2835,16 +2835,16 @@
         <v>46226.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D55" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" s="8">
         <v>692280.0</v>
@@ -2855,26 +2855,26 @@
       <c r="H55" s="8">
         <v>700200.0</v>
       </c>
-      <c r="I55" s="12" t="s">
+      <c r="I55" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J55" s="13"/>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="7">
         <v>46227.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D56" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="8">
         <v>700200.0</v>
@@ -2885,20 +2885,20 @@
       <c r="H56" s="8">
         <v>668440.0</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J56" s="13"/>
+      <c r="I56" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="7">
         <v>46227.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D57" s="8">
         <v>2110402.0</v>
@@ -2915,11 +2915,11 @@
       <c r="H57" s="8">
         <v>326391.0</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>104</v>
+      <c r="I57" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
@@ -2927,16 +2927,16 @@
         <v>46227.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D58" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F58" s="8">
         <v>144637.0</v>
@@ -2947,20 +2947,20 @@
       <c r="H58" s="8">
         <v>128160.0</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J58" s="13"/>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="7">
         <v>46227.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D59" s="8">
         <v>2110402.0</v>
@@ -2977,11 +2977,11 @@
       <c r="H59" s="8">
         <v>166642.0</v>
       </c>
-      <c r="I59" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>106</v>
+      <c r="I59" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
@@ -2989,16 +2989,16 @@
         <v>46230.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D60" s="8">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F60" s="8">
         <v>9960.0</v>
@@ -3009,10 +3009,10 @@
       <c r="H60" s="8">
         <v>3660.0</v>
       </c>
-      <c r="I60" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60" s="13"/>
+      <c r="I60" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="7">
@@ -3022,13 +3022,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D61" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F61" s="8">
         <v>306720.0</v>
@@ -3039,26 +3039,26 @@
       <c r="H61" s="8">
         <v>247096.0</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J61" s="13"/>
+      <c r="I61" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="7">
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F62" s="8">
         <v>437080.0</v>
@@ -3069,11 +3069,11 @@
       <c r="H62" s="8">
         <v>353700.0</v>
       </c>
-      <c r="I62" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>109</v>
+      <c r="I62" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
@@ -3081,10 +3081,10 @@
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D63" s="8">
         <v>2110402.0</v>
@@ -3101,11 +3101,11 @@
       <c r="H63" s="8">
         <v>375549.0</v>
       </c>
-      <c r="I63" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J63" s="13" t="s">
-        <v>110</v>
+      <c r="I63" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" s="12" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
@@ -3113,16 +3113,16 @@
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D64" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F64" s="8">
         <v>238497.0</v>
@@ -3133,11 +3133,11 @@
       <c r="H64" s="8">
         <v>181858.0</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J64" s="13" t="s">
-        <v>111</v>
+      <c r="I64" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
@@ -3145,16 +3145,16 @@
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D65" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F65" s="8">
         <v>8190.0</v>
@@ -3165,11 +3165,11 @@
       <c r="H65" s="8">
         <v>7200.0</v>
       </c>
-      <c r="I65" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>111</v>
+      <c r="I65" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
@@ -3177,16 +3177,16 @@
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D66" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" s="8">
         <v>146224.0</v>
@@ -3197,11 +3197,11 @@
       <c r="H66" s="8">
         <v>98850.0</v>
       </c>
-      <c r="I66" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J66" s="13" t="s">
-        <v>111</v>
+      <c r="I66" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
@@ -3209,14 +3209,14 @@
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67" s="8">
         <v>14599.0</v>
@@ -3227,17 +3227,17 @@
       <c r="H67" s="8">
         <v>7263.0</v>
       </c>
-      <c r="I67" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="13"/>
+      <c r="I67" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
       <c r="A68" s="7">
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="8">
@@ -3255,17 +3255,17 @@
       <c r="H68" s="8">
         <v>36720.0</v>
       </c>
-      <c r="I68" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="13"/>
+      <c r="I68" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
       <c r="A69" s="7">
         <v>46232.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="8">
@@ -3283,24 +3283,24 @@
       <c r="H69" s="8">
         <v>117570.0</v>
       </c>
-      <c r="I69" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="13"/>
+      <c r="I69" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
       <c r="A70" s="7">
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F70" s="8">
         <v>5913.0</v>
@@ -3311,10 +3311,10 @@
       <c r="H70" s="8">
         <v>5893.0</v>
       </c>
-      <c r="I70" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="13"/>
+      <c r="I70" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
       <c r="A71" s="7">
@@ -3328,7 +3328,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F71" s="8">
         <v>256613.0</v>
@@ -3339,10 +3339,10 @@
       <c r="H71" s="8">
         <v>142320.0</v>
       </c>
-      <c r="I71" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="13"/>
+      <c r="I71" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
       <c r="A72" s="7">
@@ -3356,7 +3356,7 @@
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F72" s="8">
         <v>21300.0</v>
@@ -3367,17 +3367,17 @@
       <c r="H72" s="8">
         <v>18690.0</v>
       </c>
-      <c r="I72" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="13"/>
+      <c r="I72" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
       <c r="A73" s="7">
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="8">
@@ -3395,26 +3395,26 @@
       <c r="H73" s="8">
         <v>200114.0</v>
       </c>
-      <c r="I73" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="13"/>
+      <c r="I73" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="12"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
       <c r="A74" s="17">
         <v>46233.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D74" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F74" s="8">
         <v>158761.0</v>
@@ -3425,11 +3425,11 @@
       <c r="H74" s="8">
         <v>183014.0</v>
       </c>
-      <c r="I74" s="12" t="s">
+      <c r="I74" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J74" s="13" t="s">
-        <v>114</v>
+      <c r="J74" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
@@ -3437,16 +3437,16 @@
         <v>46233.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D75" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F75" s="8">
         <v>117430.0</v>
@@ -3457,10 +3457,10 @@
       <c r="H75" s="8">
         <v>86643.0</v>
       </c>
-      <c r="I75" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J75" s="13"/>
+      <c r="I75" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
       <c r="A76" s="7">
@@ -3470,13 +3470,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D76" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F76" s="8">
         <v>265693.0</v>
@@ -3487,26 +3487,26 @@
       <c r="H76" s="8">
         <v>116000.0</v>
       </c>
-      <c r="I76" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J76" s="13"/>
+      <c r="I76" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
       <c r="A77" s="7">
         <v>46234.0</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D77" s="8">
         <v>112357.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F77" s="8">
         <v>720.0</v>
@@ -3517,11 +3517,11 @@
       <c r="H77" s="8">
         <v>2040.0</v>
       </c>
-      <c r="I77" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J77" s="13" t="s">
-        <v>119</v>
+      <c r="I77" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
@@ -3529,16 +3529,16 @@
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D78" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F78" s="8">
         <v>5580.0</v>
@@ -3549,11 +3549,11 @@
       <c r="H78" s="8">
         <v>3984.0</v>
       </c>
-      <c r="I78" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J78" s="13" t="s">
-        <v>120</v>
+      <c r="I78" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
@@ -3561,16 +3561,16 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D79" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F79" s="8">
         <v>192903.0</v>
@@ -3581,11 +3581,11 @@
       <c r="H79" s="8">
         <v>77501.0</v>
       </c>
-      <c r="I79" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J79" s="13" t="s">
-        <v>121</v>
+      <c r="I79" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
@@ -3593,16 +3593,16 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D80" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F80" s="8">
         <v>152062.0</v>
@@ -3613,11 +3613,11 @@
       <c r="H80" s="8">
         <v>124423.0</v>
       </c>
-      <c r="I80" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J80" s="13" t="s">
-        <v>121</v>
+      <c r="I80" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
@@ -3625,16 +3625,16 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D81" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F81" s="8">
         <v>153692.0</v>
@@ -3645,11 +3645,11 @@
       <c r="H81" s="8">
         <v>63920.0</v>
       </c>
-      <c r="I81" s="12" t="s">
+      <c r="I81" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J81" s="13" t="s">
-        <v>124</v>
+      <c r="J81" s="12" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
@@ -3657,10 +3657,10 @@
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D82" s="8">
         <v>2110402.0</v>
@@ -3677,26 +3677,26 @@
       <c r="H82" s="8">
         <v>40560.0</v>
       </c>
-      <c r="I82" s="12" t="s">
+      <c r="I82" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J82" s="13"/>
+      <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="19">
         <v>46237.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D83" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F83" s="8">
         <v>93517.0</v>
@@ -3707,11 +3707,11 @@
       <c r="H83" s="8">
         <v>48804.0</v>
       </c>
-      <c r="I83" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J83" s="13" t="s">
-        <v>126</v>
+      <c r="I83" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
@@ -3722,13 +3722,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D84" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F84" s="8">
         <v>43200.0</v>
@@ -3739,10 +3739,10 @@
       <c r="H84" s="8">
         <v>40890.0</v>
       </c>
-      <c r="I84" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J84" s="13"/>
+      <c r="I84" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
       <c r="A85" s="7">
@@ -3752,13 +3752,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D85" s="8">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F85" s="8">
         <v>25350.0</v>
@@ -3769,10 +3769,10 @@
       <c r="H85" s="8">
         <v>30750.0</v>
       </c>
-      <c r="I85" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J85" s="13"/>
+      <c r="I85" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
       <c r="A86" s="7">
@@ -3782,13 +3782,13 @@
         <v>10</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D86" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F86" s="8">
         <v>5040.0</v>
@@ -3799,26 +3799,26 @@
       <c r="H86" s="8">
         <v>4680.0</v>
       </c>
-      <c r="I86" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J86" s="13"/>
+      <c r="I86" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
       <c r="A87" s="7">
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D87" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F87" s="8">
         <v>124423.0</v>
@@ -3829,11 +3829,11 @@
       <c r="H87" s="8">
         <v>69217.0</v>
       </c>
-      <c r="I87" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J87" s="13" t="s">
-        <v>130</v>
+      <c r="I87" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
@@ -3844,13 +3844,13 @@
         <v>10</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D88" s="8">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F88" s="8">
         <v>30750.0</v>
@@ -3861,26 +3861,26 @@
       <c r="H88" s="8">
         <v>36300.0</v>
       </c>
-      <c r="I88" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J88" s="13"/>
+      <c r="I88" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
       <c r="A89" s="7">
         <v>46239.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D89" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F89" s="8">
         <v>58320.0</v>
@@ -3891,11 +3891,11 @@
       <c r="H89" s="8">
         <v>12480.0</v>
       </c>
-      <c r="I89" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J89" s="13" t="s">
-        <v>132</v>
+      <c r="I89" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
@@ -3903,16 +3903,16 @@
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D90" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" s="8">
         <v>254880.0</v>
@@ -3923,11 +3923,11 @@
       <c r="H90" s="8">
         <v>27180.0</v>
       </c>
-      <c r="I90" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="13" t="s">
-        <v>133</v>
+      <c r="I90" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
@@ -3935,16 +3935,16 @@
         <v>46240.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D91" s="8">
         <v>112379.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F91" s="8">
         <v>13800.0</v>
@@ -3955,26 +3955,26 @@
       <c r="H91" s="8">
         <v>12132.0</v>
       </c>
-      <c r="I91" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J91" s="13"/>
+      <c r="I91" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="19">
         <v>46240.0</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D92" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F92" s="8">
         <v>4575.0</v>
@@ -3985,28 +3985,28 @@
       <c r="H92" s="8">
         <v>4213.0</v>
       </c>
-      <c r="I92" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" s="13" t="s">
-        <v>135</v>
+      <c r="I92" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
-      <c r="A93" s="21">
+      <c r="A93" s="22">
         <v>46244.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D93" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F93" s="8">
         <v>222000.0</v>
@@ -4017,28 +4017,28 @@
       <c r="H93" s="8">
         <v>312480.0</v>
       </c>
-      <c r="I93" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J93" s="13" t="s">
-        <v>136</v>
+      <c r="I93" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
-      <c r="A94" s="21">
+      <c r="A94" s="22">
         <v>46244.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D94" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" s="8">
         <v>300060.0</v>
@@ -4049,22 +4049,22 @@
       <c r="H94" s="8">
         <v>260696.0</v>
       </c>
-      <c r="I94" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J94" s="13" t="s">
-        <v>136</v>
+      <c r="I94" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
-      <c r="A95" s="21">
+      <c r="A95" s="22">
         <v>46244.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D95" s="8">
         <v>2110402.0</v>
@@ -4081,28 +4081,28 @@
       <c r="H95" s="8">
         <v>39840.0</v>
       </c>
-      <c r="I95" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J95" s="13" t="s">
-        <v>136</v>
+      <c r="I95" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
-      <c r="A96" s="21">
+      <c r="A96" s="22">
         <v>46244.0</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D96" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F96" s="8">
         <v>21690.0</v>
@@ -4113,26 +4113,26 @@
       <c r="H96" s="8">
         <v>26280.0</v>
       </c>
-      <c r="I96" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J96" s="13"/>
+      <c r="I96" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" s="12"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
       <c r="A97" s="7">
         <v>46245.0</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D97" s="8">
         <v>112271.0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F97" s="8">
         <v>20100.0</v>
@@ -4143,20 +4143,20 @@
       <c r="H97" s="8">
         <v>10800.0</v>
       </c>
-      <c r="I97" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J97" s="13"/>
+      <c r="I97" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" s="12"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
       <c r="A98" s="7">
         <v>46245.0</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D98" s="8">
         <v>2110402.0</v>
@@ -4173,11 +4173,11 @@
       <c r="H98" s="8">
         <v>23520.0</v>
       </c>
-      <c r="I98" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J98" s="13" t="s">
-        <v>137</v>
+      <c r="I98" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J98" s="12" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
@@ -4185,16 +4185,16 @@
         <v>46245.0</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D99" s="8">
         <v>152384.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F99" s="8">
         <v>18600.0</v>
@@ -4205,11 +4205,11 @@
       <c r="H99" s="8">
         <v>12900.0</v>
       </c>
-      <c r="I99" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J99" s="13" t="s">
-        <v>138</v>
+      <c r="I99" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
@@ -4220,13 +4220,13 @@
         <v>10</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D100" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F100" s="8">
         <v>225620.0</v>
@@ -4237,11 +4237,11 @@
       <c r="H100" s="8">
         <v>269040.0</v>
       </c>
-      <c r="I100" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="13" t="s">
-        <v>139</v>
+      <c r="I100" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
@@ -4249,10 +4249,10 @@
         <v>46246.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D101" s="8">
         <v>2110402.0</v>
@@ -4269,11 +4269,11 @@
       <c r="H101" s="8">
         <v>638764.0</v>
       </c>
-      <c r="I101" s="12" t="s">
+      <c r="I101" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J101" s="13" t="s">
-        <v>141</v>
+      <c r="J101" s="12" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="102" ht="22.5" hidden="1" customHeight="1">
@@ -4284,13 +4284,13 @@
         <v>10</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D102" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" s="8">
         <v>800120.0</v>
@@ -4301,11 +4301,11 @@
       <c r="H102" s="8">
         <v>655250.0</v>
       </c>
-      <c r="I102" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="13" t="s">
-        <v>142</v>
+      <c r="I102" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
@@ -4316,13 +4316,13 @@
         <v>10</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D103" s="8">
         <v>112271.0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F103" s="8">
         <v>10815.0</v>
@@ -4333,11 +4333,11 @@
       <c r="H103" s="8">
         <v>1935.0</v>
       </c>
-      <c r="I103" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J103" s="13" t="s">
-        <v>143</v>
+      <c r="I103" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
@@ -4345,16 +4345,16 @@
         <v>46246.0</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D104" s="8">
         <v>152384.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F104" s="8">
         <v>12900.0</v>
@@ -4365,11 +4365,11 @@
       <c r="H104" s="8">
         <v>19800.0</v>
       </c>
-      <c r="I104" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J104" s="13" t="s">
-        <v>136</v>
+      <c r="I104" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
@@ -4377,16 +4377,16 @@
         <v>46247.0</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="D105" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F105" s="8">
         <v>193026.0</v>
@@ -4397,11 +4397,11 @@
       <c r="H105" s="8">
         <v>63824.0</v>
       </c>
-      <c r="I105" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J105" s="13" t="s">
-        <v>147</v>
+      <c r="I105" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
@@ -4409,16 +4409,16 @@
         <v>46247.0</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D106" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F106" s="8">
         <v>245520.0</v>
@@ -4429,26 +4429,26 @@
       <c r="H106" s="8">
         <v>230580.0</v>
       </c>
-      <c r="I106" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J106" s="13"/>
+      <c r="I106" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J106" s="12"/>
     </row>
     <row r="107" ht="22.5" hidden="1" customHeight="1">
       <c r="A107" s="7">
         <v>46247.0</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D107" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F107" s="8">
         <v>21120.0</v>
@@ -4459,26 +4459,26 @@
       <c r="H107" s="8">
         <v>17280.0</v>
       </c>
-      <c r="I107" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J107" s="13"/>
+      <c r="I107" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J107" s="12"/>
     </row>
     <row r="108" ht="22.5" hidden="1" customHeight="1">
       <c r="A108" s="7">
         <v>46247.0</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D108" s="8">
         <v>112271.0</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F108" s="8">
         <v>16500.0</v>
@@ -4489,10 +4489,10 @@
       <c r="H108" s="8">
         <v>12600.0</v>
       </c>
-      <c r="I108" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J108" s="13"/>
+      <c r="I108" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J108" s="12"/>
     </row>
     <row r="109" ht="22.5" hidden="1" customHeight="1">
       <c r="A109" s="7">
@@ -4502,13 +4502,13 @@
         <v>10</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D109" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F109" s="8">
         <v>793976.0</v>
@@ -4519,11 +4519,11 @@
       <c r="H109" s="8">
         <v>584490.0</v>
       </c>
-      <c r="I109" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J109" s="13" t="s">
-        <v>150</v>
+      <c r="I109" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="110" ht="22.5" hidden="1" customHeight="1">
@@ -4531,16 +4531,16 @@
         <v>46248.0</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D110" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F110" s="8">
         <v>289920.0</v>
@@ -4551,26 +4551,26 @@
       <c r="H110" s="8">
         <v>247440.0</v>
       </c>
-      <c r="I110" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J110" s="13"/>
+      <c r="I110" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J110" s="12"/>
     </row>
     <row r="111" ht="22.5" hidden="1" customHeight="1">
       <c r="A111" s="7">
         <v>46248.0</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D111" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" s="8">
         <v>230580.0</v>
@@ -4581,11 +4581,11 @@
       <c r="H111" s="8">
         <v>298620.0</v>
       </c>
-      <c r="I111" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J111" s="13" t="s">
-        <v>153</v>
+      <c r="I111" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="112" ht="22.5" hidden="1" customHeight="1">
@@ -4593,16 +4593,16 @@
         <v>46248.0</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D112" s="8">
         <v>152384.0</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F112" s="8">
         <v>13200.0</v>
@@ -4613,11 +4613,11 @@
       <c r="H112" s="8">
         <v>7200.0</v>
       </c>
-      <c r="I112" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J112" s="13" t="s">
-        <v>154</v>
+      <c r="I112" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="113" ht="22.5" hidden="1" customHeight="1">
@@ -4625,16 +4625,16 @@
         <v>46248.0</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D113" s="8">
         <v>152384.0</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F113" s="8">
         <v>9900.0</v>
@@ -4645,11 +4645,11 @@
       <c r="H113" s="8">
         <v>8100.0</v>
       </c>
-      <c r="I113" s="12" t="s">
+      <c r="I113" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J113" s="13" t="s">
-        <v>157</v>
+      <c r="J113" s="12" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="114" ht="22.5" hidden="1" customHeight="1">
@@ -4657,16 +4657,16 @@
         <v>46252.0</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D114" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F114" s="8">
         <v>184290.0</v>
@@ -4677,11 +4677,11 @@
       <c r="H114" s="8">
         <v>68640.0</v>
       </c>
-      <c r="I114" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J114" s="13" t="s">
-        <v>158</v>
+      <c r="I114" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="115" ht="22.5" hidden="1" customHeight="1">
@@ -4689,10 +4689,10 @@
         <v>46252.0</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D115" s="8">
         <v>2110402.0</v>
@@ -4709,11 +4709,11 @@
       <c r="H115" s="8">
         <v>26880.0</v>
       </c>
-      <c r="I115" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J115" s="13" t="s">
-        <v>160</v>
+      <c r="I115" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="116" ht="22.5" hidden="1" customHeight="1">
@@ -4724,13 +4724,13 @@
         <v>10</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D116" s="8">
         <v>152384.0</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F116" s="8">
         <v>21585.0</v>
@@ -4741,11 +4741,11 @@
       <c r="H116" s="8">
         <v>12900.0</v>
       </c>
-      <c r="I116" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J116" s="13" t="s">
-        <v>161</v>
+      <c r="I116" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="117" ht="22.5" hidden="1" customHeight="1">
@@ -4753,16 +4753,16 @@
         <v>46253.0</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D117" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F117" s="8">
         <v>179640.0</v>
@@ -4774,19 +4774,19 @@
         <v>39060.0</v>
       </c>
       <c r="I117" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J117" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J117" s="12"/>
     </row>
     <row r="118" ht="22.5" hidden="1" customHeight="1">
       <c r="A118" s="7">
         <v>46253.0</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D118" s="8">
         <v>2110402.0</v>
@@ -4804,25 +4804,25 @@
         <v>25680.0</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J118" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J118" s="12"/>
     </row>
     <row r="119" ht="22.5" hidden="1" customHeight="1">
       <c r="A119" s="7">
         <v>46253.0</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D119" s="8">
         <v>152384.0</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F119" s="8">
         <v>14230.0</v>
@@ -4834,25 +4834,25 @@
         <v>13200.0</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J119" s="12"/>
     </row>
     <row r="120" ht="22.5" hidden="1" customHeight="1">
       <c r="A120" s="7">
         <v>46253.0</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D120" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F120" s="8">
         <v>26677.0</v>
@@ -4866,8 +4866,8 @@
       <c r="I120" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J120" s="13" t="s">
-        <v>164</v>
+      <c r="J120" s="12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="121" ht="22.5" hidden="1" customHeight="1">
@@ -4878,13 +4878,13 @@
         <v>10</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D121" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F121" s="8">
         <v>22500.0</v>
@@ -4896,10 +4896,10 @@
         <v>18300.0</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J121" s="13" t="s">
-        <v>165</v>
+        <v>44</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="122" ht="22.5" hidden="1" customHeight="1">
@@ -4910,13 +4910,13 @@
         <v>10</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D122" s="8">
         <v>112271.0</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F122" s="8">
         <v>16500.0</v>
@@ -4928,10 +4928,10 @@
         <v>8100.0</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J122" s="13" t="s">
-        <v>161</v>
+        <v>26</v>
+      </c>
+      <c r="J122" s="12" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="123" ht="22.5" hidden="1" customHeight="1">
@@ -4939,16 +4939,16 @@
         <v>46254.0</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D123" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F123" s="8">
         <v>21915.0</v>
@@ -4959,11 +4959,11 @@
       <c r="H123" s="8">
         <v>14235.0</v>
       </c>
-      <c r="I123" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J123" s="13" t="s">
-        <v>166</v>
+      <c r="I123" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="124" ht="22.5" hidden="1" customHeight="1">
@@ -4971,16 +4971,16 @@
         <v>46254.0</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D124" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F124" s="8">
         <v>10125.0</v>
@@ -4991,26 +4991,26 @@
       <c r="H124" s="8">
         <v>8565.0</v>
       </c>
-      <c r="I124" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J124" s="13"/>
+      <c r="I124" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J124" s="12"/>
     </row>
     <row r="125" ht="22.5" hidden="1" customHeight="1">
       <c r="A125" s="7">
         <v>46254.0</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D125" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F125" s="8">
         <v>6380.0</v>
@@ -5021,11 +5021,11 @@
       <c r="H125" s="8">
         <v>1980.0</v>
       </c>
-      <c r="I125" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J125" s="13" t="s">
-        <v>169</v>
+      <c r="I125" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J125" s="12" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="126" ht="22.5" hidden="1" customHeight="1">
@@ -5036,7 +5036,7 @@
         <v>10</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D126" s="8">
         <v>2110402.0</v>
@@ -5053,20 +5053,20 @@
       <c r="H126" s="8">
         <v>51080.0</v>
       </c>
-      <c r="I126" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J126" s="13"/>
+      <c r="I126" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J126" s="12"/>
     </row>
     <row r="127" ht="22.5" hidden="1" customHeight="1">
       <c r="A127" s="7">
         <v>46255.0</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D127" s="8">
         <v>2110402.0</v>
@@ -5083,11 +5083,11 @@
       <c r="H127" s="8">
         <v>17760.0</v>
       </c>
-      <c r="I127" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J127" s="13" t="s">
-        <v>171</v>
+      <c r="I127" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J127" s="12" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="128" ht="22.5" hidden="1" customHeight="1">
@@ -5095,16 +5095,16 @@
         <v>46255.0</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D128" s="8">
         <v>112268.0</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F128" s="8">
         <v>3300.0</v>
@@ -5115,11 +5115,11 @@
       <c r="H128" s="8">
         <v>5400.0</v>
       </c>
-      <c r="I128" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J128" s="13" t="s">
-        <v>173</v>
+      <c r="I128" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J128" s="12" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="129" ht="22.5" hidden="1" customHeight="1">
@@ -5127,16 +5127,16 @@
         <v>46255.0</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D129" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F129" s="8">
         <v>2130.0</v>
@@ -5147,11 +5147,11 @@
       <c r="H129" s="8">
         <v>1230.0</v>
       </c>
-      <c r="I129" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="13" t="s">
-        <v>176</v>
+      <c r="I129" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="130" ht="22.5" hidden="1" customHeight="1">
@@ -5162,13 +5162,13 @@
         <v>10</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D130" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F130" s="8">
         <v>341120.0</v>
@@ -5179,11 +5179,11 @@
       <c r="H130" s="8">
         <v>545850.0</v>
       </c>
-      <c r="I130" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J130" s="13" t="s">
-        <v>178</v>
+      <c r="I130" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J130" s="12" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="131" ht="22.5" hidden="1" customHeight="1">
@@ -5191,16 +5191,16 @@
         <v>46258.0</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D131" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F131" s="8">
         <v>11520.0</v>
@@ -5211,10 +5211,10 @@
       <c r="H131" s="8">
         <v>11880.0</v>
       </c>
-      <c r="I131" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J131" s="13"/>
+      <c r="I131" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J131" s="12"/>
     </row>
     <row r="132" ht="22.5" hidden="1" customHeight="1">
       <c r="A132" s="19">
@@ -5224,7 +5224,7 @@
         <v>10</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D132" s="8">
         <v>2110402.0</v>
@@ -5241,11 +5241,11 @@
       <c r="H132" s="8">
         <v>18000.0</v>
       </c>
-      <c r="I132" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J132" s="13" t="s">
-        <v>178</v>
+      <c r="I132" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J132" s="12" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="133" ht="22.5" hidden="1" customHeight="1">
@@ -5253,16 +5253,16 @@
         <v>46259.0</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D133" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F133" s="8">
         <v>64620.0</v>
@@ -5273,10 +5273,10 @@
       <c r="H133" s="8">
         <v>47685.0</v>
       </c>
-      <c r="I133" s="12" t="s">
+      <c r="I133" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J133" s="13"/>
+      <c r="J133" s="12"/>
     </row>
     <row r="134" ht="22.5" hidden="1" customHeight="1">
       <c r="A134" s="7">
@@ -5286,7 +5286,7 @@
         <v>10</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D134" s="8">
         <v>2110402.0</v>
@@ -5303,11 +5303,11 @@
       <c r="H134" s="8">
         <v>11510.0</v>
       </c>
-      <c r="I134" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="13" t="s">
-        <v>179</v>
+      <c r="I134" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="135" ht="22.5" hidden="1" customHeight="1">
@@ -5315,16 +5315,16 @@
         <v>46259.0</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D135" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F135" s="8">
         <v>48540.0</v>
@@ -5335,11 +5335,11 @@
       <c r="H135" s="8">
         <v>105048.0</v>
       </c>
-      <c r="I135" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J135" s="13" t="s">
-        <v>180</v>
+      <c r="I135" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J135" s="12" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="136" ht="22.5" hidden="1" customHeight="1">
@@ -5350,13 +5350,13 @@
         <v>10</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D136" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F136" s="8">
         <v>194198.0</v>
@@ -5367,11 +5367,11 @@
       <c r="H136" s="8">
         <v>140840.0</v>
       </c>
-      <c r="I136" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J136" s="13" t="s">
-        <v>182</v>
+      <c r="I136" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="137" ht="22.5" hidden="1" customHeight="1">
@@ -5382,7 +5382,7 @@
         <v>10</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D137" s="8">
         <v>2110402.0</v>
@@ -5399,11 +5399,11 @@
       <c r="H137" s="8">
         <v>10398.0</v>
       </c>
-      <c r="I137" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J137" s="13" t="s">
-        <v>183</v>
+      <c r="I137" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J137" s="12" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="138" ht="22.5" hidden="1" customHeight="1">
@@ -5411,16 +5411,16 @@
         <v>46260.0</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D138" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F138" s="8">
         <v>47685.0</v>
@@ -5431,11 +5431,11 @@
       <c r="H138" s="8">
         <v>107298.0</v>
       </c>
-      <c r="I138" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="13" t="s">
-        <v>184</v>
+      <c r="I138" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J138" s="12" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="139" ht="22.5" hidden="1" customHeight="1">
@@ -5446,13 +5446,13 @@
         <v>10</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D139" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F139" s="8">
         <v>30600.0</v>
@@ -5463,11 +5463,11 @@
       <c r="H139" s="8">
         <v>33440.0</v>
       </c>
-      <c r="I139" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J139" s="13" t="s">
-        <v>182</v>
+      <c r="I139" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J139" s="12" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="140" ht="22.5" hidden="1" customHeight="1">
@@ -5475,16 +5475,16 @@
         <v>46261.0</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D140" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F140" s="8">
         <v>38640.0</v>
@@ -5498,23 +5498,23 @@
       <c r="I140" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J140" s="13"/>
+      <c r="J140" s="12"/>
     </row>
     <row r="141" ht="22.5" hidden="1" customHeight="1">
       <c r="A141" s="19">
         <v>46261.0</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D141" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F141" s="8">
         <v>365280.0</v>
@@ -5528,23 +5528,23 @@
       <c r="I141" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J141" s="13"/>
+      <c r="J141" s="12"/>
     </row>
     <row r="142" ht="22.5" hidden="1" customHeight="1">
       <c r="A142" s="19">
         <v>46261.0</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D142" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F142" s="8">
         <v>192000.0</v>
@@ -5556,25 +5556,25 @@
         <v>91680.0</v>
       </c>
       <c r="I142" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J142" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J142" s="12"/>
     </row>
     <row r="143" ht="22.5" hidden="1" customHeight="1">
       <c r="A143" s="19">
         <v>46261.0</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D143" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F143" s="8">
         <v>10260.0</v>
@@ -5586,25 +5586,25 @@
         <v>7860.0</v>
       </c>
       <c r="I143" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J143" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J143" s="12"/>
     </row>
     <row r="144" ht="22.5" hidden="1" customHeight="1">
       <c r="A144" s="19">
         <v>46262.0</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D144" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F144" s="8">
         <v>10500.0</v>
@@ -5615,26 +5615,26 @@
       <c r="H144" s="8">
         <v>12930.0</v>
       </c>
-      <c r="I144" s="12" t="s">
+      <c r="I144" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J144" s="13"/>
+      <c r="J144" s="12"/>
     </row>
     <row r="145" ht="22.5" hidden="1" customHeight="1">
       <c r="A145" s="19">
         <v>46262.0</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D145" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F145" s="8">
         <v>91680.0</v>
@@ -5645,11 +5645,11 @@
       <c r="H145" s="8">
         <v>84480.0</v>
       </c>
-      <c r="I145" s="12" t="s">
+      <c r="I145" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J145" s="13" t="s">
-        <v>191</v>
+      <c r="J145" s="12" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="146" ht="22.5" hidden="1" customHeight="1">
@@ -5657,16 +5657,16 @@
         <v>46265.0</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D146" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F146" s="8">
         <v>17970.0</v>
@@ -5677,26 +5677,26 @@
       <c r="H146" s="8">
         <v>7020.0</v>
       </c>
-      <c r="I146" s="12" t="s">
+      <c r="I146" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J146" s="13"/>
+      <c r="J146" s="12"/>
     </row>
     <row r="147" ht="22.5" hidden="1" customHeight="1">
       <c r="A147" s="7">
         <v>46265.0</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D147" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F147" s="8">
         <v>9960.0</v>
@@ -5707,26 +5707,26 @@
       <c r="H147" s="8">
         <v>6330.0</v>
       </c>
-      <c r="I147" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J147" s="13"/>
+      <c r="I147" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J147" s="12"/>
     </row>
     <row r="148" ht="22.5" hidden="1" customHeight="1">
       <c r="A148" s="7">
         <v>46265.0</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D148" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F148" s="8">
         <v>10503.0</v>
@@ -5737,11 +5737,11 @@
       <c r="H148" s="8">
         <v>9063.0</v>
       </c>
-      <c r="I148" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J148" s="13" t="s">
-        <v>194</v>
+      <c r="I148" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="149" ht="22.5" hidden="1" customHeight="1">
@@ -5752,13 +5752,13 @@
         <v>10</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D149" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F149" s="8">
         <v>339300.0</v>
@@ -5769,11 +5769,11 @@
       <c r="H149" s="8">
         <v>349380.0</v>
       </c>
-      <c r="I149" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J149" s="13" t="s">
-        <v>195</v>
+      <c r="I149" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="150" ht="22.5" hidden="1" customHeight="1">
@@ -5781,16 +5781,16 @@
         <v>46266.0</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D150" s="8">
         <v>152384.0</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F150" s="8">
         <v>17100.0</v>
@@ -5801,26 +5801,26 @@
       <c r="H150" s="8">
         <v>8700.0</v>
       </c>
-      <c r="I150" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J150" s="13"/>
+      <c r="I150" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J150" s="12"/>
     </row>
     <row r="151" ht="22.5" hidden="1" customHeight="1">
       <c r="A151" s="7">
         <v>46266.0</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D151" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F151" s="8">
         <v>3240.0</v>
@@ -5831,11 +5831,11 @@
       <c r="H151" s="8">
         <v>2505.0</v>
       </c>
-      <c r="I151" s="12" t="s">
+      <c r="I151" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J151" s="13" t="s">
-        <v>197</v>
+      <c r="J151" s="12" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="152" ht="22.5" hidden="1" customHeight="1">
@@ -5846,13 +5846,13 @@
         <v>10</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D152" s="8">
         <v>152384.0</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F152" s="8">
         <v>25350.0</v>
@@ -5863,11 +5863,11 @@
       <c r="H152" s="8">
         <v>33150.0</v>
       </c>
-      <c r="I152" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J152" s="13" t="s">
-        <v>198</v>
+      <c r="I152" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="153" ht="22.5" hidden="1" customHeight="1">
@@ -5875,16 +5875,16 @@
         <v>46267.0</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D153" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F153" s="8">
         <v>15660.0</v>
@@ -5895,11 +5895,11 @@
       <c r="H153" s="8">
         <v>2520.0</v>
       </c>
-      <c r="I153" s="12" t="s">
+      <c r="I153" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J153" s="13" t="s">
-        <v>199</v>
+      <c r="J153" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="154" ht="22.5" hidden="1" customHeight="1">
@@ -5907,16 +5907,16 @@
         <v>46267.0</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D154" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F154" s="8">
         <v>8280.0</v>
@@ -5927,11 +5927,11 @@
       <c r="H154" s="8">
         <v>3375.0</v>
       </c>
-      <c r="I154" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J154" s="13" t="s">
-        <v>200</v>
+      <c r="I154" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="155" ht="22.5" hidden="1" customHeight="1">
@@ -5939,16 +5939,16 @@
         <v>46268.0</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D155" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F155" s="8">
         <v>205020.0</v>
@@ -5959,11 +5959,11 @@
       <c r="H155" s="8">
         <v>106200.0</v>
       </c>
-      <c r="I155" s="12" t="s">
+      <c r="I155" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J155" s="13" t="s">
-        <v>202</v>
+      <c r="J155" s="12" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="156" ht="22.5" hidden="1" customHeight="1">
@@ -5971,16 +5971,16 @@
         <v>46268.0</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D156" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F156" s="8">
         <v>7920.0</v>
@@ -5991,11 +5991,11 @@
       <c r="H156" s="8">
         <v>9720.0</v>
       </c>
-      <c r="I156" s="12" t="s">
+      <c r="I156" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J156" s="13" t="s">
-        <v>203</v>
+      <c r="J156" s="12" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="157" ht="22.5" hidden="1" customHeight="1">
@@ -6003,10 +6003,10 @@
         <v>46268.0</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D157" s="8">
         <v>2110402.0</v>
@@ -6023,11 +6023,11 @@
       <c r="H157" s="8">
         <v>12240.0</v>
       </c>
-      <c r="I157" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J157" s="13" t="s">
-        <v>204</v>
+      <c r="I157" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="158" ht="22.5" hidden="1" customHeight="1">
@@ -6038,13 +6038,13 @@
         <v>10</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D158" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F158" s="8">
         <v>287280.0</v>
@@ -6055,11 +6055,11 @@
       <c r="H158" s="8">
         <v>301320.0</v>
       </c>
-      <c r="I158" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J158" s="13" t="s">
-        <v>206</v>
+      <c r="I158" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="159" ht="22.5" hidden="1" customHeight="1">
@@ -6067,16 +6067,16 @@
         <v>46269.0</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D159" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F159" s="8">
         <v>6435.0</v>
@@ -6087,26 +6087,26 @@
       <c r="H159" s="8">
         <v>8040.0</v>
       </c>
-      <c r="I159" s="12" t="s">
+      <c r="I159" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J159" s="13"/>
+      <c r="J159" s="12"/>
     </row>
     <row r="160" ht="22.5" hidden="1" customHeight="1">
       <c r="A160" s="7">
         <v>46269.0</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D160" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F160" s="8">
         <v>440230.0</v>
@@ -6117,11 +6117,11 @@
       <c r="H160" s="8">
         <v>300589.0</v>
       </c>
-      <c r="I160" s="12" t="s">
+      <c r="I160" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J160" s="13" t="s">
-        <v>208</v>
+      <c r="J160" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="161" ht="22.5" hidden="1" customHeight="1">
@@ -6129,16 +6129,16 @@
         <v>46269.0</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D161" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F161" s="8">
         <v>8457.0</v>
@@ -6149,11 +6149,11 @@
       <c r="H161" s="8">
         <v>8097.0</v>
       </c>
-      <c r="I161" s="12" t="s">
+      <c r="I161" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J161" s="13" t="s">
-        <v>208</v>
+      <c r="J161" s="12" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="162" ht="22.5" hidden="1" customHeight="1">
@@ -6161,16 +6161,16 @@
         <v>46272.0</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D162" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F162" s="8">
         <v>96984.0</v>
@@ -6181,10 +6181,10 @@
       <c r="H162" s="8">
         <v>40143.0</v>
       </c>
-      <c r="I162" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J162" s="13" t="s">
+      <c r="I162" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J162" s="12" t="s">
         <v>211</v>
       </c>
     </row>
@@ -6196,13 +6196,13 @@
         <v>10</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D163" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F163" s="8">
         <v>345572.0</v>
@@ -6213,10 +6213,10 @@
       <c r="H163" s="8">
         <v>444960.0</v>
       </c>
-      <c r="I163" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J163" s="13" t="s">
+      <c r="I163" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J163" s="12" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6228,13 +6228,13 @@
         <v>10</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D164" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F164" s="8">
         <v>21960.0</v>
@@ -6245,10 +6245,10 @@
       <c r="H164" s="8">
         <v>18330.0</v>
       </c>
-      <c r="I164" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J164" s="13" t="s">
+      <c r="I164" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J164" s="12" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6257,10 +6257,10 @@
         <v>46273.0</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D165" s="8">
         <v>2110402.0</v>
@@ -6277,10 +6277,10 @@
       <c r="H165" s="8">
         <v>21840.0</v>
       </c>
-      <c r="I165" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J165" s="13" t="s">
+      <c r="I165" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J165" s="12" t="s">
         <v>213</v>
       </c>
     </row>
@@ -6289,16 +6289,16 @@
         <v>46273.0</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D166" s="8">
         <v>112271.0</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F166" s="8">
         <v>13200.0</v>
@@ -6309,26 +6309,26 @@
       <c r="H166" s="8">
         <v>6900.0</v>
       </c>
-      <c r="I166" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J166" s="13"/>
+      <c r="I166" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J166" s="12"/>
     </row>
     <row r="167" ht="22.5" hidden="1" customHeight="1">
       <c r="A167" s="7">
         <v>46273.0</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D167" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F167" s="8">
         <v>10620.0</v>
@@ -6339,10 +6339,10 @@
       <c r="H167" s="8">
         <v>8460.0</v>
       </c>
-      <c r="I167" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J167" s="13" t="s">
+      <c r="I167" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J167" s="12" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6351,16 +6351,16 @@
         <v>46273.0</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D168" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F168" s="8">
         <v>239040.0</v>
@@ -6371,10 +6371,10 @@
       <c r="H168" s="8">
         <v>123360.0</v>
       </c>
-      <c r="I168" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J168" s="13" t="s">
+      <c r="I168" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J168" s="12" t="s">
         <v>214</v>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         <v>46274.0</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D169" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F169" s="8">
         <v>123360.0</v>
@@ -6403,10 +6403,10 @@
       <c r="H169" s="8">
         <v>151680.0</v>
       </c>
-      <c r="I169" s="12" t="s">
+      <c r="I169" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J169" s="13" t="s">
+      <c r="J169" s="12" t="s">
         <v>215</v>
       </c>
     </row>
@@ -6415,16 +6415,16 @@
         <v>46274.0</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D170" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F170" s="8">
         <v>8460.0</v>
@@ -6435,10 +6435,10 @@
       <c r="H170" s="8">
         <v>12240.0</v>
       </c>
-      <c r="I170" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J170" s="13"/>
+      <c r="I170" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J170" s="12"/>
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="7">
@@ -6448,13 +6448,13 @@
         <v>10</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D171" s="8">
         <v>112271.0</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F171" s="8">
         <v>9900.0</v>
@@ -6465,10 +6465,10 @@
       <c r="H171" s="8">
         <v>8700.0</v>
       </c>
-      <c r="I171" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J171" s="13" t="s">
+      <c r="I171" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J171" s="12" t="s">
         <v>216</v>
       </c>
     </row>
@@ -6480,13 +6480,13 @@
         <v>10</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D172" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F172" s="8">
         <v>18330.0</v>
@@ -6497,10 +6497,10 @@
       <c r="H172" s="8">
         <v>17580.0</v>
       </c>
-      <c r="I172" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J172" s="13" t="s">
+      <c r="I172" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J172" s="12" t="s">
         <v>217</v>
       </c>
     </row>
@@ -6512,13 +6512,13 @@
         <v>10</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D173" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F173" s="8">
         <v>340260.0</v>
@@ -6529,10 +6529,10 @@
       <c r="H173" s="8">
         <v>422640.0</v>
       </c>
-      <c r="I173" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J173" s="13" t="s">
+      <c r="I173" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J173" s="12" t="s">
         <v>218</v>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
         <v>10</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D174" s="8">
         <v>2110402.0</v>
@@ -6561,10 +6561,10 @@
       <c r="H174" s="8">
         <v>43440.0</v>
       </c>
-      <c r="I174" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J174" s="13" t="s">
+      <c r="I174" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J174" s="12" t="s">
         <v>218</v>
       </c>
     </row>
@@ -6576,13 +6576,13 @@
         <v>10</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D175" s="8">
         <v>152384.0</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F175" s="8">
         <v>18585.0</v>
@@ -6593,10 +6593,10 @@
       <c r="H175" s="8">
         <v>22470.0</v>
       </c>
-      <c r="I175" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J175" s="13" t="s">
+      <c r="I175" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J175" s="12" t="s">
         <v>216</v>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
         <v>46275.0</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>219</v>
@@ -6614,7 +6614,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F176" s="8">
         <v>151680.0</v>
@@ -6625,10 +6625,10 @@
       <c r="H176" s="8">
         <v>67680.0</v>
       </c>
-      <c r="I176" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J176" s="13" t="s">
+      <c r="I176" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J176" s="12" t="s">
         <v>220</v>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
         <v>46275.0</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>219</v>
@@ -6657,10 +6657,10 @@
       <c r="H177" s="8">
         <v>18480.0</v>
       </c>
-      <c r="I177" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J177" s="13" t="s">
+      <c r="I177" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J177" s="12" t="s">
         <v>221</v>
       </c>
     </row>
@@ -6669,16 +6669,16 @@
         <v>46276.0</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D178" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F178" s="8">
         <v>2130.0</v>
@@ -6689,20 +6689,20 @@
       <c r="H178" s="8">
         <v>1740.0</v>
       </c>
-      <c r="I178" s="12" t="s">
+      <c r="I178" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J178" s="13"/>
+      <c r="J178" s="12"/>
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="7">
         <v>46276.0</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D179" s="8">
         <v>2110402.0</v>
@@ -6719,10 +6719,10 @@
       <c r="H179" s="8">
         <v>627558.0</v>
       </c>
-      <c r="I179" s="12" t="s">
+      <c r="I179" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J179" s="13" t="s">
+      <c r="J179" s="12" t="s">
         <v>222</v>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="8">
@@ -9304,10 +9304,10 @@
         <v>3712.0</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
@@ -9315,14 +9315,14 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="8">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" s="8">
         <v>60.0</v>
@@ -9334,10 +9334,10 @@
         <v>60.0</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
@@ -9345,14 +9345,14 @@
         <v>46225.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="8">
         <v>10501.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F4" s="8">
         <v>415093.0</v>
@@ -9364,10 +9364,10 @@
         <v>543038.0</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>36</v>
+        <v>20</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
@@ -9375,14 +9375,14 @@
         <v>46225.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="8">
         <v>112379.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8">
         <v>3000.0</v>
@@ -9394,10 +9394,10 @@
         <v>3000.0</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>43</v>
+        <v>16</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -9405,14 +9405,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="8">
         <v>112268.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F6" s="8">
         <v>3000.0</v>
@@ -9424,10 +9424,10 @@
         <v>3300.0</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>48</v>
+        <v>16</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -9435,14 +9435,14 @@
         <v>46225.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="8">
         <v>132357.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F7" s="8">
         <v>1560.0</v>
@@ -9454,10 +9454,10 @@
         <v>4560.0</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -9465,14 +9465,14 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="8">
         <v>720.0</v>
@@ -9484,10 +9484,10 @@
         <v>5940.0</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>54</v>
+        <v>16</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
@@ -9495,7 +9495,7 @@
         <v>46225.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="8">
@@ -9514,10 +9514,10 @@
         <v>213.0</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>57</v>
+        <v>16</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
@@ -9525,14 +9525,14 @@
         <v>46226.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="8">
         <v>73001.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="8">
         <v>73787.0</v>
@@ -9544,10 +9544,10 @@
         <v>109487.0</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
@@ -9555,14 +9555,14 @@
         <v>46226.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="8">
         <v>112268.0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F11" s="8">
         <v>3300.0</v>
@@ -9574,23 +9574,23 @@
         <v>3300.0</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
       <c r="A12" s="7">
         <v>46226.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="8">
         <v>112379.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" s="8">
         <v>4200.0</v>
@@ -9602,23 +9602,23 @@
         <v>3900.0</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
       <c r="A13" s="7">
         <v>46226.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="8">
         <v>379471.0</v>
@@ -9630,10 +9630,10 @@
         <v>357186.0</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -9641,14 +9641,14 @@
         <v>46227.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="8">
         <v>72001.0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F14" s="8">
         <v>21905.0</v>
@@ -9660,10 +9660,10 @@
         <v>38000.0</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>62</v>
+        <v>16</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -9671,14 +9671,14 @@
         <v>46227.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="8">
         <v>2110327.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F15" s="8">
         <v>69120.0</v>
@@ -9690,10 +9690,10 @@
         <v>40320.0</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>68</v>
+        <v>16</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -9701,14 +9701,14 @@
         <v>46227.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="8">
         <v>112379.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F16" s="8">
         <v>3900.0</v>
@@ -9720,23 +9720,23 @@
         <v>1500.0</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
       <c r="A17" s="7">
         <v>46227.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F17" s="8">
         <v>720.0</v>
@@ -9748,23 +9748,23 @@
         <v>2580.0</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
       <c r="A18" s="7">
         <v>46227.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="8">
         <v>112268.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F18" s="8">
         <v>3300.0</v>
@@ -9776,10 +9776,10 @@
         <v>600.0</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>74</v>
+        <v>16</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
@@ -9787,14 +9787,14 @@
         <v>46230.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="8">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F19" s="8">
         <v>136538.0</v>
@@ -9806,10 +9806,10 @@
         <v>213000.0</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>76</v>
+        <v>16</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -9817,14 +9817,14 @@
         <v>46231.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="8">
         <v>591750.0</v>
@@ -9836,10 +9836,10 @@
         <v>577207.0</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>76</v>
+        <v>16</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
@@ -9847,14 +9847,14 @@
         <v>46231.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="8">
         <v>10601.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F21" s="8">
         <v>1230.0</v>
@@ -9866,10 +9866,10 @@
         <v>1958.0</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -9877,14 +9877,14 @@
         <v>46231.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F22" s="8">
         <v>4320.0</v>
@@ -9896,23 +9896,23 @@
         <v>3420.0</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
       <c r="A23" s="7">
         <v>46231.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="8">
         <v>114357.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F23" s="8">
         <v>240.0</v>
@@ -9924,23 +9924,23 @@
         <v>240.0</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
       <c r="A24" s="7">
         <v>46232.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="8">
         <v>10501.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F24" s="8">
         <v>19663.0</v>
@@ -9952,23 +9952,23 @@
         <v>29632.0</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
       <c r="A25" s="7">
         <v>46232.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="8">
         <v>112268.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F25" s="8">
         <v>5700.0</v>
@@ -9980,23 +9980,23 @@
         <v>5100.0</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
       <c r="A26" s="7">
         <v>46232.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F26" s="8">
         <v>720.0</v>
@@ -10008,23 +10008,23 @@
         <v>720.0</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
       <c r="A27" s="7">
         <v>46232.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="8">
         <v>2114357.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F27" s="8">
         <v>432.0</v>
@@ -10036,23 +10036,23 @@
         <v>432.0</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
       <c r="A28" s="7">
         <v>46232.0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="8">
         <v>10501.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F28" s="8">
         <v>219540.0</v>
@@ -10064,23 +10064,23 @@
         <v>16698.0</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
       <c r="A29" s="7">
         <v>46233.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="8">
         <v>112268.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F29" s="8">
         <v>5100.0</v>
@@ -10092,23 +10092,23 @@
         <v>4800.0</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
       <c r="A30" s="7">
         <v>46233.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="8">
         <v>114357.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F30" s="8">
         <v>240.0</v>
@@ -10120,23 +10120,23 @@
         <v>1560.0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
       <c r="A31" s="7">
         <v>46233.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="8">
         <v>10601.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F31" s="8">
         <v>7717.0</v>
@@ -10148,10 +10148,10 @@
         <v>12867.0</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>97</v>
+        <v>16</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
@@ -10159,14 +10159,14 @@
         <v>46234.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="8">
         <v>79110.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F32" s="8">
         <v>48000.0</v>
@@ -10178,10 +10178,10 @@
         <v>36300.0</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
@@ -10189,14 +10189,14 @@
         <v>46234.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="8">
         <v>10501.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F33" s="8">
         <v>95574.0</v>
@@ -10208,10 +10208,10 @@
         <v>142801.0</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
@@ -10219,14 +10219,14 @@
         <v>46234.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="8">
         <v>73001.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F34" s="8">
         <v>73367.0</v>
@@ -10238,23 +10238,23 @@
         <v>39150.0</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
       <c r="A35" s="7">
         <v>46234.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="8">
         <v>112357.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F35" s="8">
         <v>840.0</v>
@@ -10266,23 +10266,23 @@
         <v>480.0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
       <c r="A36" s="19">
         <v>46237.0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="8">
         <v>10601.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F36" s="8">
         <v>17934.0</v>
@@ -10294,10 +10294,10 @@
         <v>21714.0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>108</v>
+        <v>16</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -10305,14 +10305,14 @@
         <v>46237.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="8">
         <v>194520.0</v>
@@ -10324,23 +10324,23 @@
         <v>122840.0</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
       <c r="A38" s="19">
         <v>46237.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="8">
         <v>114379.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F38" s="8">
         <v>52200.0</v>
@@ -10352,23 +10352,23 @@
         <v>7500.0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
       <c r="A39" s="19">
         <v>46237.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F39" s="8">
         <v>6450.0</v>
@@ -10380,23 +10380,23 @@
         <v>6480.0</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
       <c r="A40" s="19">
         <v>46237.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F40" s="8">
         <v>1398.0</v>
@@ -10408,23 +10408,23 @@
         <v>438.0</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
       <c r="A41" s="7">
         <v>46238.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F41" s="8">
         <v>2460.0</v>
@@ -10438,21 +10438,21 @@
       <c r="I41" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J41" s="13"/>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
       <c r="A42" s="7">
         <v>46238.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="8">
         <v>112268.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F42" s="8">
         <v>3600.0</v>
@@ -10464,23 +10464,23 @@
         <v>3900.0</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
       <c r="A43" s="7">
         <v>46238.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="8">
         <v>114379.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F43" s="8">
         <v>7500.0</v>
@@ -10492,23 +10492,23 @@
         <v>8400.0</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J43" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
       <c r="A44" s="7">
         <v>46238.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="8">
         <v>114357.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F44" s="8">
         <v>240.0</v>
@@ -10520,23 +10520,23 @@
         <v>360.0</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
       <c r="A45" s="7">
         <v>46239.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="8">
         <v>10601.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F45" s="8">
         <v>1115.0</v>
@@ -10548,10 +10548,10 @@
         <v>1590.0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>118</v>
+        <v>16</v>
+      </c>
+      <c r="J45" s="12" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -10559,14 +10559,14 @@
         <v>46239.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F46" s="8">
         <v>114240.0</v>
@@ -10578,23 +10578,23 @@
         <v>191130.0</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
       <c r="A47" s="7">
         <v>46239.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F47" s="8">
         <v>1800.0</v>
@@ -10606,23 +10606,23 @@
         <v>1980.0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
       <c r="A48" s="7">
         <v>46239.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="8">
         <v>112268.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F48" s="8">
         <v>3900.0</v>
@@ -10634,23 +10634,23 @@
         <v>1200.0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
       <c r="A49" s="7">
         <v>46239.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="8">
         <v>112357.0</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F49" s="8">
         <v>600.0</v>
@@ -10662,23 +10662,23 @@
         <v>600.0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J49" s="12"/>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
       <c r="A50" s="7">
         <v>46239.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="8">
         <v>114268.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F50" s="8">
         <v>2700.0</v>
@@ -10690,23 +10690,23 @@
         <v>300.0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J50" s="12"/>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
       <c r="A51" s="7">
         <v>46239.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="8">
         <v>10501.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F51" s="8">
         <v>68651.0</v>
@@ -10718,10 +10718,10 @@
         <v>13421.0</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>128</v>
+        <v>16</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
@@ -10729,14 +10729,14 @@
         <v>46239.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="8">
         <v>72003.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F52" s="8">
         <v>1391.0</v>
@@ -10750,14 +10750,14 @@
       <c r="I52" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
       <c r="A53" s="7">
         <v>46239.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="8">
@@ -10776,10 +10776,10 @@
         <v>3317.0</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>131</v>
+        <v>16</v>
+      </c>
+      <c r="J53" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
@@ -10787,14 +10787,14 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="8">
         <v>112379.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F54" s="8">
         <v>3600.0</v>
@@ -10806,23 +10806,23 @@
         <v>6900.0</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J54" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J54" s="12"/>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
       <c r="A55" s="19">
         <v>46240.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="8">
         <v>73001.0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F55" s="8">
         <v>2415.0</v>
@@ -10834,23 +10834,23 @@
         <v>2415.0</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
       <c r="A56" s="19">
         <v>46240.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="8">
         <v>112357.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F56" s="8">
         <v>600.0</v>
@@ -10862,23 +10862,23 @@
         <v>600.0</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
       <c r="A57" s="19">
         <v>46240.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="8">
         <v>114379.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F57" s="8">
         <v>2400.0</v>
@@ -10890,23 +10890,23 @@
         <v>300.0</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J57" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J57" s="12"/>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
       <c r="A58" s="19">
         <v>46244.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="8">
         <v>112379.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F58" s="8">
         <v>4800.0</v>
@@ -10918,23 +10918,23 @@
         <v>5100.0</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J58" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
       <c r="A59" s="7">
         <v>46245.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F59" s="8">
         <v>25574.0</v>
@@ -10946,23 +10946,23 @@
         <v>42960.0</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J59" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J59" s="12"/>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
       <c r="A60" s="7">
         <v>46246.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="8">
         <v>114379.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F60" s="8">
         <v>6900.0</v>
@@ -10974,23 +10974,23 @@
         <v>5400.0</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J60" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
       <c r="A61" s="7">
         <v>46247.0</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="8">
         <v>112379.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F61" s="8">
         <v>20100.0</v>
@@ -11002,23 +11002,23 @@
         <v>20100.0</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
       <c r="A62" s="7">
         <v>46247.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="8">
         <v>112268.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F62" s="8">
         <v>8400.0</v>
@@ -11030,23 +11030,23 @@
         <v>8400.0</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J62" s="12"/>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
       <c r="A63" s="7">
         <v>46247.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" s="8">
         <v>61250.0</v>
@@ -11058,23 +11058,23 @@
         <v>76033.0</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J63" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J63" s="12"/>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
       <c r="A64" s="7">
         <v>46247.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="8">
         <v>13358.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F64" s="8">
         <v>73728.0</v>
@@ -11086,10 +11086,10 @@
         <v>73440.0</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J64" s="13" t="s">
-        <v>146</v>
+        <v>16</v>
+      </c>
+      <c r="J64" s="12" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="65" ht="19.5" hidden="1" customHeight="1">
@@ -11097,14 +11097,14 @@
         <v>46248.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F65" s="8">
         <v>285596.0</v>
@@ -11116,10 +11116,10 @@
         <v>72480.0</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>148</v>
+        <v>32</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="66" ht="19.5" hidden="1" customHeight="1">
@@ -11127,14 +11127,14 @@
         <v>46248.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="8">
         <v>73001.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F66" s="8">
         <v>31772.0</v>
@@ -11146,10 +11146,10 @@
         <v>28820.0</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="13" t="s">
-        <v>149</v>
+        <v>16</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="67" ht="19.5" hidden="1" customHeight="1">
@@ -11157,14 +11157,14 @@
         <v>46254.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="8">
         <v>10601.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F67" s="8">
         <v>73085.0</v>
@@ -11176,10 +11176,10 @@
         <v>78125.0</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="13" t="s">
-        <v>151</v>
+        <v>16</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="68" ht="19.5" hidden="1" customHeight="1">
@@ -11187,14 +11187,14 @@
         <v>46254.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="8">
         <v>112379.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F68" s="8">
         <v>18000.0</v>
@@ -11206,10 +11206,10 @@
         <v>18000.0</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="22" t="s">
-        <v>152</v>
+        <v>16</v>
+      </c>
+      <c r="J68" s="21" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="69" ht="19.5" hidden="1" customHeight="1">
@@ -11217,14 +11217,14 @@
         <v>46254.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="8">
         <v>114357.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F69" s="8">
         <v>120.0</v>
@@ -11236,10 +11236,10 @@
         <v>120.0</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J69" s="13" t="s">
-        <v>155</v>
+        <v>32</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="70" ht="19.5" hidden="1" customHeight="1">
@@ -11247,14 +11247,14 @@
         <v>46254.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="8">
         <v>10601.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F70" s="8">
         <v>5700.0</v>
@@ -11266,10 +11266,10 @@
         <v>9270.0</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="13" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="J70" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="71" ht="19.5" hidden="1" customHeight="1">
@@ -11277,14 +11277,14 @@
         <v>46254.0</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="8">
         <v>114268.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F71" s="8">
         <v>2700.0</v>
@@ -11296,10 +11296,10 @@
         <v>5700.0</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="13" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="72" ht="19.5" hidden="1" customHeight="1">
@@ -11307,14 +11307,14 @@
         <v>46254.0</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="8">
         <v>2114379.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="F72" s="8">
         <v>2340.0</v>
@@ -11326,10 +11326,10 @@
         <v>2340.0</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="13" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
@@ -11337,14 +11337,14 @@
         <v>46255.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F73" s="8">
         <v>88073.0</v>
@@ -11356,10 +11356,10 @@
         <v>23165.0</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J73" s="13" t="s">
-        <v>163</v>
+        <v>20</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
@@ -11367,14 +11367,14 @@
         <v>46255.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F74" s="8">
         <v>72060.0</v>
@@ -11386,10 +11386,10 @@
         <v>133320.0</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="13" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
@@ -11397,14 +11397,14 @@
         <v>46255.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="8">
         <v>152384.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F75" s="8">
         <v>6600.0</v>
@@ -11416,25 +11416,25 @@
         <v>1200.0</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J75" s="13" t="s">
-        <v>159</v>
+        <v>16</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="21">
+      <c r="A76" s="22">
         <v>46256.0</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="8">
         <v>13358.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F76" s="8">
         <v>288.0</v>
@@ -11446,25 +11446,25 @@
         <v>288.0</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="13" t="s">
-        <v>168</v>
+        <v>16</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="21">
+      <c r="A77" s="22">
         <v>46261.0</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C77" s="14"/>
       <c r="D77" s="8">
         <v>10601.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F77" s="8">
         <v>16770.0</v>
@@ -11476,23 +11476,23 @@
         <v>2670.0</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J77" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J77" s="12"/>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="21">
+      <c r="A78" s="22">
         <v>46261.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C78" s="14"/>
       <c r="D78" s="8">
         <v>114379.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F78" s="8">
         <v>3600.0</v>
@@ -11504,23 +11504,23 @@
         <v>3600.0</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J78" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J78" s="12"/>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
       <c r="A79" s="19">
         <v>46262.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F79" s="8">
         <v>59670.0</v>
@@ -11532,23 +11532,23 @@
         <v>125400.0</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J79" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J79" s="12"/>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
       <c r="A80" s="19">
         <v>46262.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="8">
         <v>114268.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F80" s="8">
         <v>33000.0</v>
@@ -11560,23 +11560,23 @@
         <v>10800.0</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J80" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J80" s="12"/>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
       <c r="A81" s="19">
         <v>46262.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="8">
         <v>112379.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F81" s="8">
         <v>15000.0</v>
@@ -11588,23 +11588,23 @@
         <v>6300.0</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J81" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J81" s="12"/>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
       <c r="A82" s="19">
         <v>46262.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="8">
         <v>112357.0</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F82" s="8">
         <v>1560.0</v>
@@ -11616,23 +11616,23 @@
         <v>1560.0</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J82" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
       <c r="A83" s="19">
         <v>46262.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="8">
         <v>10103.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="F83" s="8">
         <v>200.0</v>
@@ -11644,23 +11644,23 @@
         <v>100.0</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J83" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J83" s="12"/>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
       <c r="A84" s="7">
         <v>46265.0</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="8">
         <v>112357.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F84" s="8">
         <v>1680.0</v>
@@ -11672,23 +11672,23 @@
         <v>1200.0</v>
       </c>
       <c r="I84" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J84" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
       <c r="A85" s="7">
         <v>46265.0</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="8">
         <v>112268.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F85" s="8">
         <v>1200.0</v>
@@ -11700,23 +11700,23 @@
         <v>1200.0</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J85" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
       <c r="A86" s="7">
         <v>46265.0</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="8">
         <v>13358.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F86" s="8">
         <v>73440.0</v>
@@ -11728,23 +11728,23 @@
         <v>36864.0</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J86" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
       <c r="A87" s="7">
         <v>46265.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="8">
         <v>13524.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="F87" s="8">
         <v>240.0</v>
@@ -11756,23 +11756,23 @@
         <v>138480.0</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J87" s="13"/>
+        <v>44</v>
+      </c>
+      <c r="J87" s="12"/>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
       <c r="A88" s="7">
         <v>46265.0</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="8">
         <v>114357.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F88" s="8">
         <v>120.0</v>
@@ -11784,23 +11784,23 @@
         <v>600.0</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J88" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
       <c r="A89" s="7">
         <v>46267.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="8">
         <v>73001.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F89" s="8">
         <v>82903.0</v>
@@ -11814,21 +11814,21 @@
       <c r="I89" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J89" s="13"/>
+      <c r="J89" s="12"/>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
       <c r="A90" s="7">
         <v>46268.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F90" s="8">
         <v>2938.0</v>
@@ -11840,23 +11840,23 @@
         <v>6058.0</v>
       </c>
       <c r="I90" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J90" s="13"/>
+        <v>26</v>
+      </c>
+      <c r="J90" s="12"/>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
       <c r="A91" s="7">
         <v>46269.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="8">
         <v>2110427.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="F91" s="8">
         <v>11520.0</v>
@@ -11870,21 +11870,21 @@
       <c r="I91" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J91" s="13"/>
+      <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
       <c r="A92" s="7">
         <v>46269.0</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F92" s="8">
         <v>281580.0</v>
@@ -11898,21 +11898,21 @@
       <c r="I92" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J92" s="13"/>
+      <c r="J92" s="12"/>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
       <c r="A93" s="7">
         <v>46269.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="8">
         <v>114379.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F93" s="8">
         <v>3900.0</v>
@@ -11926,21 +11926,21 @@
       <c r="I93" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J93" s="13"/>
+      <c r="J93" s="12"/>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
       <c r="A94" s="7">
         <v>46269.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F94" s="8">
         <v>5040.0</v>
@@ -11954,14 +11954,14 @@
       <c r="I94" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J94" s="13"/>
+      <c r="J94" s="12"/>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
       <c r="A95" s="7">
         <v>46272.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="8">
@@ -11982,21 +11982,21 @@
       <c r="I95" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J95" s="13"/>
+      <c r="J95" s="12"/>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
       <c r="A96" s="7">
         <v>46272.0</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F96" s="8">
         <v>340080.0</v>
@@ -12008,23 +12008,23 @@
         <v>302802.0</v>
       </c>
       <c r="I96" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J96" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J96" s="12"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
       <c r="A97" s="7">
         <v>46272.0</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="8">
         <v>272003.0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="F97" s="8">
         <v>25404.0</v>
@@ -12038,21 +12038,21 @@
       <c r="I97" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J97" s="13"/>
+      <c r="J97" s="12"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
       <c r="A98" s="7">
         <v>46272.0</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F98" s="8">
         <v>4140.0</v>
@@ -12066,21 +12066,21 @@
       <c r="I98" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J98" s="13"/>
+      <c r="J98" s="12"/>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
       <c r="A99" s="7">
         <v>46272.0</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="8">
         <v>273003.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="F99" s="8">
         <v>12100.0</v>
@@ -12092,23 +12092,23 @@
         <v>3900.0</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J99" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J99" s="12"/>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
       <c r="A100" s="7">
         <v>46272.0</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C100" s="14"/>
       <c r="D100" s="8">
         <v>2114268.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="F100" s="8">
         <v>180.0</v>
@@ -12120,23 +12120,23 @@
         <v>180.0</v>
       </c>
       <c r="I100" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J100" s="13"/>
+        <v>20</v>
+      </c>
+      <c r="J100" s="12"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="7">
         <v>46274.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="8">
         <v>114379.0</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F101" s="8">
         <v>6900.0</v>
@@ -12150,21 +12150,21 @@
       <c r="I101" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J101" s="13"/>
+      <c r="J101" s="12"/>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="7">
         <v>46274.0</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="8">
         <v>112357.0</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F102" s="8">
         <v>240.0</v>
@@ -12178,21 +12178,21 @@
       <c r="I102" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J102" s="13"/>
+      <c r="J102" s="12"/>
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="7">
         <v>46274.0</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="8">
         <v>2410401.0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F103" s="8">
         <v>118286.0</v>
@@ -12203,22 +12203,24 @@
       <c r="H103" s="8">
         <v>247766.0</v>
       </c>
-      <c r="I103" s="11"/>
-      <c r="J103" s="13"/>
+      <c r="I103" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J103" s="12"/>
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="7">
         <v>46276.0</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F104" s="8">
         <v>264061.0</v>
@@ -12230,23 +12232,23 @@
         <v>141318.0</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J104" s="12"/>
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="7">
         <v>46276.0</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="8">
         <v>273003.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="F105" s="8">
         <v>9106.0</v>
@@ -12258,23 +12260,23 @@
         <v>13876.0</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J105" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="J105" s="12"/>
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="7">
         <v>46276.0</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="8">
         <v>10501.0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F106" s="8">
         <v>3368.0</v>
@@ -12286,15 +12288,63 @@
         <v>7017.0</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J106" s="13"/>
-    </row>
-    <row r="107">
-      <c r="I107" s="23"/>
-    </row>
-    <row r="108">
-      <c r="I108" s="23"/>
+        <v>16</v>
+      </c>
+      <c r="J106" s="12"/>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="7">
+        <v>46279.0</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C107" s="14"/>
+      <c r="D107" s="8">
+        <v>2110202.0</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="8">
+        <v>445991.0</v>
+      </c>
+      <c r="G107" s="8">
+        <v>459000.0</v>
+      </c>
+      <c r="H107" s="8">
+        <v>221756.0</v>
+      </c>
+      <c r="I107" s="11"/>
+      <c r="J107" s="12"/>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="7">
+        <v>46279.0</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="14"/>
+      <c r="D108" s="8">
+        <v>2112207.0</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F108" s="8">
+        <v>360.0</v>
+      </c>
+      <c r="G108" s="8">
+        <v>360.0</v>
+      </c>
+      <c r="H108" s="8">
+        <v>180.0</v>
+      </c>
+      <c r="I108" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="12"/>
     </row>
     <row r="109">
       <c r="I109" s="23"/>
@@ -14848,13 +14898,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I106">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I108">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I107:I958">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I109:I958">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A106">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A108">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="224">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -50,24 +50,24 @@
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>ALKA2</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
     <t>7. Otro</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
@@ -77,21 +77,21 @@
     <t>3. Falla De Rotación</t>
   </si>
   <si>
+    <t>TAT MEDELLIN</t>
+  </si>
+  <si>
+    <t>FABIO GOMEZ</t>
+  </si>
+  <si>
+    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
+  </si>
+  <si>
     <t>LANZA</t>
   </si>
   <si>
-    <t>TAT MEDELLIN</t>
-  </si>
-  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
-    <t>FABIO GOMEZ</t>
-  </si>
-  <si>
-    <t>HUEVO XL X 30 CARTON VERDE AMARRADO SIN ETIQUETA CANASTA</t>
-  </si>
-  <si>
     <t>6. Transformación De Referencias</t>
   </si>
   <si>
@@ -104,84 +104,84 @@
     <t>Dilan Barraza</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>4. Exigencia Del Cliente (Edad)</t>
+  </si>
+  <si>
+    <t>Venta FS</t>
+  </si>
+  <si>
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
-    <t>4. Exigencia Del Cliente (Edad)</t>
-  </si>
-  <si>
-    <t>Venta FS</t>
-  </si>
-  <si>
     <t>se equivocaron al cargar una estiba</t>
   </si>
   <si>
+    <t>Se dejó lote para revisión por calidad</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
-    <t>Se dejó lote para revisión por calidad</t>
+    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
+    <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
     <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
+    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
-    <t>Se envía más fresco a Rionegro</t>
+    <t>1. Ingreso Por Devolución</t>
+  </si>
+  <si>
+    <t>TAT CALI</t>
   </si>
   <si>
     <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
+    <t>DIEGO ROJAS</t>
   </si>
   <si>
     <t>PALMAS</t>
   </si>
   <si>
-    <t>1. Ingreso Por Devolución</t>
-  </si>
-  <si>
     <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
-    <t>TAT CALI</t>
-  </si>
-  <si>
-    <t>DIEGO ROJAS</t>
+    <t>TAT CUCUTA</t>
+  </si>
+  <si>
+    <t>ALEXANDER PEÑA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
-    <t>TAT CUCUTA</t>
-  </si>
-  <si>
-    <t>ALEXANDER PEÑA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
     <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>Clientes FS</t>
   </si>
   <si>
+    <t>Envío huevo fresco a Sincelejo</t>
+  </si>
+  <si>
     <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
-    <t>Envío huevo fresco a Sincelejo</t>
-  </si>
-  <si>
     <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
@@ -206,34 +206,40 @@
     <t>HUEVO SUCIO DE JAULA</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
-  </si>
-  <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+  </si>
+  <si>
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+    <t>HUEVO CX30 CARTON GRIS</t>
   </si>
   <si>
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
     <t>ANDREA QUIROGA</t>
@@ -242,16 +248,13 @@
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -260,25 +263,31 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
-  </si>
-  <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
+    <t>ALKA1</t>
+  </si>
+  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
+  </si>
+  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
-    <t>ALKA1</t>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
   </si>
   <si>
     <t>TAT BARRANQUILLA</t>
@@ -287,18 +296,9 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
-  </si>
-  <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
     <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
   </si>
   <si>
@@ -308,18 +308,18 @@
     <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
+    <t>Pedido para villacicencio</t>
+  </si>
+  <si>
     <t>Cargo en incubación</t>
   </si>
   <si>
-    <t>Pedido para villacicencio</t>
+    <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Se envía huevo más fresco a Sincelejo</t>
-  </si>
-  <si>
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
@@ -335,45 +335,45 @@
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
+    <t>Devolucion de huevo de 12 dias en mal estado</t>
+  </si>
+  <si>
+    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
+  </si>
+  <si>
     <t>BELLAVISTA</t>
   </si>
   <si>
+    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
+  </si>
+  <si>
     <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
-    <t>Devolucion de huevo de 12 dias en mal estado</t>
+    <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
+  </si>
+  <si>
+    <t>Se envía producto a Sincelejo con menor edad</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
-    <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
-  </si>
-  <si>
-    <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
-  </si>
-  <si>
-    <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
+    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
+  </si>
+  <si>
+    <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
   </si>
   <si>
-    <t>Se envía producto a Sincelejo con menor edad</t>
-  </si>
-  <si>
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
-    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
-  </si>
-  <si>
     <t>HUEVO SUCIO ZF MARCADO</t>
   </si>
   <si>
-    <t>TAT VILLAVICENCIO</t>
-  </si>
-  <si>
     <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
@@ -392,134 +392,140 @@
     <t>Producto queda en CEDI por calidad</t>
   </si>
   <si>
+    <t>Producto devuelto clientes TAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDER PEÑA </t>
+  </si>
+  <si>
+    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
+  </si>
+  <si>
+    <t>ANDRES MEJA</t>
+  </si>
+  <si>
+    <t>Se envía lotemás nuevo a Sincelejo</t>
+  </si>
+  <si>
     <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
   </si>
   <si>
-    <t>Producto devuelto clientes TAT</t>
-  </si>
-  <si>
     <t>vehiculo pendiente pro llegar a planta</t>
   </si>
   <si>
-    <t xml:space="preserve">ALEXANDER PEÑA </t>
+    <t>Se envía huevo más fresco para clientes FS</t>
   </si>
   <si>
     <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
   </si>
   <si>
-    <t>Llegaron canastas combinados llegaron en la parte de abajo</t>
-  </si>
-  <si>
-    <t>ANDRES MEJA</t>
-  </si>
-  <si>
     <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
   </si>
   <si>
+    <t>Producto enviado a Rionegro y para FS más fresco</t>
+  </si>
+  <si>
     <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
   </si>
   <si>
-    <t>Se envía lotemás nuevo a Sincelejo</t>
+    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
+  </si>
+  <si>
+    <t>yOVANIS AREVALO</t>
   </si>
   <si>
     <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
   </si>
   <si>
+    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
+  </si>
+  <si>
     <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
   </si>
   <si>
+    <t>Se envía huevo fresco a Rionegro</t>
+  </si>
+  <si>
     <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
   </si>
   <si>
-    <t>Se envía huevo más fresco para clientes FS</t>
-  </si>
-  <si>
     <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
-    <t>Producto enviado a Rionegro y para FS más fresco</t>
   </si>
   <si>
     <t xml:space="preserve"> estaba programado para despacho a tat cali, planeación quito el pedido y se nos notificó que se debía dar rotación inmediatamente.
 En simultáneo, se cargó la mula y se desencadenaron las 18.000 unidades de 112379 para despachar para Medellín. En esta acción nos percatamos solo cuando la mula ya estaba en un 70 % cargada que se nos estaban quedando 21.525 de la referencia L canastas (2110302) con fecha de producción 19/08/2026.</t>
   </si>
   <si>
-    <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
-  </si>
-  <si>
-    <t>yOVANIS AREVALO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
-  </si>
-  <si>
-    <t>Se envía huevo fresco a Rionegro</t>
+    <t>Clientes Fs</t>
+  </si>
+  <si>
+    <t>Se envían para Rionegro con mejor fecha</t>
   </si>
   <si>
     <t>REPOSICION SIN SOLTAR</t>
   </si>
   <si>
-    <t>Clientes Fs</t>
-  </si>
-  <si>
-    <t>Se envían para Rionegro con mejor fecha</t>
-  </si>
-  <si>
     <t>Llega de planta bellavista</t>
   </si>
   <si>
     <t>Jhonathan Gomez</t>
   </si>
   <si>
+    <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
+  </si>
+  <si>
+    <t>LLegada de planta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asignado canal TAT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yovanis Arevalo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">salida de pedido especial </t>
+  </si>
+  <si>
     <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
-  </si>
-  <si>
-    <t>LLegada de planta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asignado canal TAT </t>
+    <t>novedad en lotes por calidad</t>
   </si>
   <si>
     <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yovanis Arevalo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">salida de pedido especial </t>
+    <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
+  </si>
+  <si>
+    <t>Productoenviado a Rionegro más fresco</t>
+  </si>
+  <si>
+    <t>DIANA VITERIA</t>
+  </si>
+  <si>
+    <t>ERROR EN DIGITACION DE LAS EDAD</t>
   </si>
   <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA - BUCAROS</t>
   </si>
   <si>
-    <t>novedad en lotes por calidad</t>
-  </si>
-  <si>
-    <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
-  </si>
-  <si>
-    <t>Productoenviado a Rionegro más fresco</t>
-  </si>
-  <si>
-    <t>DIANA VITERIA</t>
-  </si>
-  <si>
-    <t>ERROR EN DIGITACION DE LAS EDAD</t>
+    <t>Pedidos para FD más fresco</t>
+  </si>
+  <si>
+    <t>Padidos para FS con mayor frescura</t>
+  </si>
+  <si>
+    <t>Pendiente Transformacion a suelto</t>
   </si>
   <si>
     <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
   </si>
   <si>
-    <t>Pedidos para FD más fresco</t>
-  </si>
-  <si>
-    <t>Padidos para FS con mayor frescura</t>
-  </si>
-  <si>
-    <t>Pendiente Transformacion a suelto</t>
+    <t>se registra mal el dia de ayer el lote de 2 dias</t>
+  </si>
+  <si>
+    <t>Devolucion Blindar</t>
   </si>
   <si>
     <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
@@ -528,12 +534,6 @@
     <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
   </si>
   <si>
-    <t>se registra mal el dia de ayer el lote de 2 dias</t>
-  </si>
-  <si>
-    <t>Devolucion Blindar</t>
-  </si>
-  <si>
     <t>NO se evidencia ruptura de inventario, diferencia de 100 unidades en el lote mas fresco</t>
   </si>
   <si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t>Salio en sugeridos</t>
+  </si>
+  <si>
+    <t>El lote no se despachó el día anterior debido a que el envío se realizó en un vehículo compartido. Al ser Palmas la última bodega en la que se realizó la carga, solo se logró despachar la cantidad que la capacidad del vehículo permitió.</t>
   </si>
   <si>
     <t xml:space="preserve"> traslado de referencias</t>
@@ -905,7 +908,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J179" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J181" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -923,7 +926,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J108" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J108" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1199,7 +1202,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="8">
         <v>359100.0</v>
@@ -1219,7 +1222,7 @@
         <v>46205.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>18</v>
@@ -1249,16 +1252,16 @@
         <v>46205.0</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D4" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F4" s="8">
         <v>21120.0</v>
@@ -1288,7 +1291,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8">
         <v>75680.0</v>
@@ -1300,10 +1303,10 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -1311,16 +1314,16 @@
         <v>46206.0</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="8">
         <v>189540.0</v>
@@ -1332,10 +1335,10 @@
         <v>144720.0</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -1343,16 +1346,16 @@
         <v>46206.0</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D7" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="8">
         <v>20640.0</v>
@@ -1364,10 +1367,10 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -1375,16 +1378,16 @@
         <v>46206.0</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D8" s="8">
         <v>152384.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="8">
         <v>14700.0</v>
@@ -1396,7 +1399,7 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J8" s="12"/>
     </row>
@@ -1405,16 +1408,16 @@
         <v>46206.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" s="8">
         <v>228240.0</v>
@@ -1426,7 +1429,7 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" s="12"/>
     </row>
@@ -1435,16 +1438,16 @@
         <v>46206.0</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="D10" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="8">
         <v>7830.0</v>
@@ -1465,10 +1468,10 @@
         <v>46206.0</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D11" s="8">
         <v>2110402.0</v>
@@ -1486,7 +1489,7 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>53</v>
@@ -1497,7 +1500,7 @@
         <v>46206.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>18</v>
@@ -1506,7 +1509,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="8">
         <v>51387.0</v>
@@ -1518,10 +1521,10 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
@@ -1529,7 +1532,7 @@
         <v>46209.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>18</v>
@@ -1550,10 +1553,10 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -1593,7 +1596,7 @@
         <v>46209.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>59</v>
@@ -1602,7 +1605,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="8">
         <v>14160.0</v>
@@ -1614,7 +1617,7 @@
         <v>12360.0</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>60</v>
@@ -1634,7 +1637,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="8">
         <v>149040.0</v>
@@ -1655,16 +1658,16 @@
         <v>46210.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D17" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F17" s="8">
         <v>22770.0</v>
@@ -1685,16 +1688,16 @@
         <v>46210.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18" s="8">
         <v>222021.0</v>
@@ -1736,10 +1739,10 @@
         <v>401280.0</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -1747,7 +1750,7 @@
         <v>46211.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>18</v>
@@ -1777,16 +1780,16 @@
         <v>46211.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D21" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" s="8">
         <v>162125.0</v>
@@ -1798,7 +1801,7 @@
         <v>100687.0</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>67</v>
@@ -1818,7 +1821,7 @@
         <v>152384.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F22" s="8">
         <v>32850.0</v>
@@ -1830,7 +1833,7 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -1839,7 +1842,7 @@
         <v>46211.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>59</v>
@@ -1860,7 +1863,7 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -1869,16 +1872,16 @@
         <v>46212.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D24" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="8">
         <v>190047.0</v>
@@ -1890,7 +1893,7 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J24" s="12"/>
     </row>
@@ -1899,7 +1902,7 @@
         <v>46212.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>59</v>
@@ -1908,7 +1911,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" s="8">
         <v>178080.0</v>
@@ -1920,7 +1923,7 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J25" s="12"/>
     </row>
@@ -1929,7 +1932,7 @@
         <v>46212.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>59</v>
@@ -1950,10 +1953,10 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
@@ -1961,7 +1964,7 @@
         <v>46212.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>59</v>
@@ -1994,13 +1997,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" s="8">
         <v>208440.0</v>
@@ -2012,10 +2015,10 @@
         <v>150833.0</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
@@ -2026,13 +2029,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D29" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="8">
         <v>962820.0</v>
@@ -2044,10 +2047,10 @@
         <v>922140.0</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
@@ -2055,7 +2058,7 @@
         <v>46213.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>59</v>
@@ -2064,7 +2067,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" s="8">
         <v>335340.0</v>
@@ -2076,10 +2079,10 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
@@ -2096,7 +2099,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" s="8">
         <v>316800.0</v>
@@ -2117,16 +2120,16 @@
         <v>46213.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D32" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32" s="8">
         <v>176850.0</v>
@@ -2138,7 +2141,7 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -2177,16 +2180,16 @@
         <v>46217.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34" s="8">
         <v>481440.0</v>
@@ -2207,16 +2210,16 @@
         <v>46217.0</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D35" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="8">
         <v>355720.0</v>
@@ -2240,13 +2243,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D36" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" s="8">
         <v>35280.0</v>
@@ -2261,7 +2264,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -2272,13 +2275,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D37" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F37" s="8">
         <v>272073.0</v>
@@ -2290,7 +2293,7 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>85</v>
@@ -2304,13 +2307,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D38" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F38" s="8">
         <v>37926.0</v>
@@ -2325,7 +2328,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
@@ -2333,10 +2336,10 @@
         <v>46218.0</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D39" s="8">
         <v>2110402.0</v>
@@ -2354,10 +2357,10 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
@@ -2365,16 +2368,16 @@
         <v>46218.0</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D40" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F40" s="8">
         <v>10980.0</v>
@@ -2395,16 +2398,16 @@
         <v>46219.0</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>24</v>
       </c>
       <c r="D41" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" s="8">
         <v>130320.0</v>
@@ -2416,10 +2419,10 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
@@ -2427,16 +2430,16 @@
         <v>46219.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D42" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F42" s="8">
         <v>36225.0</v>
@@ -2457,16 +2460,16 @@
         <v>46219.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D43" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" s="8">
         <v>152833.0</v>
@@ -2478,10 +2481,10 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
@@ -2489,16 +2492,16 @@
         <v>46219.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D44" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44" s="8">
         <v>237828.0</v>
@@ -2522,13 +2525,13 @@
         <v>10</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D45" s="8">
         <v>152384.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F45" s="8">
         <v>31125.0</v>
@@ -2540,7 +2543,7 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>96</v>
@@ -2554,13 +2557,13 @@
         <v>10</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D46" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" s="8">
         <v>25746.0</v>
@@ -2575,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
@@ -2586,13 +2589,13 @@
         <v>10</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D47" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F47" s="8">
         <v>261166.0</v>
@@ -2604,10 +2607,10 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
@@ -2618,13 +2621,13 @@
         <v>10</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D48" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F48" s="8">
         <v>115289.0</v>
@@ -2645,7 +2648,7 @@
         <v>46224.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>18</v>
@@ -2666,10 +2669,10 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
@@ -2677,10 +2680,10 @@
         <v>46224.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D50" s="8">
         <v>2110402.0</v>
@@ -2698,7 +2701,7 @@
         <v>551645.0</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>102</v>
@@ -2709,7 +2712,7 @@
         <v>46225.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>59</v>
@@ -2718,7 +2721,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51" s="8">
         <v>130560.0</v>
@@ -2741,16 +2744,16 @@
         <v>46225.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D52" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52" s="8">
         <v>87447.0</v>
@@ -2774,7 +2777,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D53" s="8">
         <v>2110402.0</v>
@@ -2824,7 +2827,7 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J54" s="12" t="s">
         <v>106</v>
@@ -2835,7 +2838,7 @@
         <v>46226.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>59</v>
@@ -2844,7 +2847,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F55" s="8">
         <v>692280.0</v>
@@ -2856,7 +2859,7 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J55" s="12"/>
     </row>
@@ -2865,7 +2868,7 @@
         <v>46227.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>59</v>
@@ -2874,7 +2877,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F56" s="8">
         <v>700200.0</v>
@@ -2916,10 +2919,10 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
@@ -2927,16 +2930,16 @@
         <v>46227.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D58" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F58" s="8">
         <v>144637.0</v>
@@ -2948,7 +2951,7 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -2957,10 +2960,10 @@
         <v>46227.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D59" s="8">
         <v>2110402.0</v>
@@ -2978,10 +2981,10 @@
         <v>166642.0</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
@@ -2989,16 +2992,16 @@
         <v>46230.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D60" s="8">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F60" s="8">
         <v>9960.0</v>
@@ -3022,13 +3025,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D61" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F61" s="8">
         <v>306720.0</v>
@@ -3049,16 +3052,16 @@
         <v>46230.0</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D62" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F62" s="8">
         <v>437080.0</v>
@@ -3070,10 +3073,10 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
@@ -3081,7 +3084,7 @@
         <v>46231.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>18</v>
@@ -3102,10 +3105,10 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
@@ -3113,16 +3116,16 @@
         <v>46231.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D64" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F64" s="8">
         <v>238497.0</v>
@@ -3134,10 +3137,10 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
@@ -3145,16 +3148,16 @@
         <v>46231.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D65" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F65" s="8">
         <v>8190.0</v>
@@ -3166,10 +3169,10 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
@@ -3177,16 +3180,16 @@
         <v>46231.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D66" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F66" s="8">
         <v>146224.0</v>
@@ -3198,10 +3201,10 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
@@ -3209,14 +3212,14 @@
         <v>46232.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F67" s="8">
         <v>14599.0</v>
@@ -3228,7 +3231,7 @@
         <v>7263.0</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J67" s="12"/>
     </row>
@@ -3237,7 +3240,7 @@
         <v>46232.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68" s="20"/>
       <c r="D68" s="8">
@@ -3256,7 +3259,7 @@
         <v>36720.0</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" s="12"/>
     </row>
@@ -3284,7 +3287,7 @@
         <v>117570.0</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" s="12"/>
     </row>
@@ -3293,14 +3296,14 @@
         <v>46232.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F70" s="8">
         <v>5913.0</v>
@@ -3312,7 +3315,7 @@
         <v>5893.0</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J70" s="12"/>
     </row>
@@ -3328,7 +3331,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F71" s="8">
         <v>256613.0</v>
@@ -3340,7 +3343,7 @@
         <v>142320.0</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" s="12"/>
     </row>
@@ -3356,7 +3359,7 @@
         <v>152384.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F72" s="8">
         <v>21300.0</v>
@@ -3368,7 +3371,7 @@
         <v>18690.0</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" s="12"/>
     </row>
@@ -3377,7 +3380,7 @@
         <v>46232.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C73" s="20"/>
       <c r="D73" s="8">
@@ -3396,7 +3399,7 @@
         <v>200114.0</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -3405,16 +3408,16 @@
         <v>46233.0</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="D74" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F74" s="8">
         <v>158761.0</v>
@@ -3426,7 +3429,7 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>121</v>
@@ -3437,16 +3440,16 @@
         <v>46233.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D75" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F75" s="8">
         <v>117430.0</v>
@@ -3470,13 +3473,13 @@
         <v>10</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D76" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F76" s="8">
         <v>265693.0</v>
@@ -3518,7 +3521,7 @@
         <v>2040.0</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>124</v>
@@ -3529,16 +3532,16 @@
         <v>46234.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D78" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F78" s="8">
         <v>5580.0</v>
@@ -3550,7 +3553,7 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>125</v>
@@ -3561,16 +3564,16 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D79" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F79" s="8">
         <v>192903.0</v>
@@ -3582,10 +3585,10 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
@@ -3593,16 +3596,16 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D80" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F80" s="8">
         <v>152062.0</v>
@@ -3614,10 +3617,10 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J80" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
@@ -3625,16 +3628,16 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D81" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F81" s="8">
         <v>153692.0</v>
@@ -3646,10 +3649,10 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
@@ -3657,10 +3660,10 @@
         <v>46237.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D82" s="8">
         <v>2110402.0</v>
@@ -3687,7 +3690,7 @@
         <v>46237.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>18</v>
@@ -3696,7 +3699,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F83" s="8">
         <v>93517.0</v>
@@ -3708,10 +3711,10 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
@@ -3722,13 +3725,13 @@
         <v>10</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D84" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F84" s="8">
         <v>43200.0</v>
@@ -3752,13 +3755,13 @@
         <v>10</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D85" s="8">
         <v>152384.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F85" s="8">
         <v>25350.0</v>
@@ -3770,7 +3773,7 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -3782,13 +3785,13 @@
         <v>10</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D86" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F86" s="8">
         <v>5040.0</v>
@@ -3809,16 +3812,16 @@
         <v>46238.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D87" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F87" s="8">
         <v>124423.0</v>
@@ -3830,10 +3833,10 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
@@ -3844,13 +3847,13 @@
         <v>10</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D88" s="8">
         <v>152384.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F88" s="8">
         <v>30750.0</v>
@@ -3871,16 +3874,16 @@
         <v>46239.0</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D89" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F89" s="8">
         <v>58320.0</v>
@@ -3892,10 +3895,10 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
@@ -3903,16 +3906,16 @@
         <v>46240.0</v>
       </c>
       <c r="B90" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D90" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F90" s="8">
         <v>254880.0</v>
@@ -3924,10 +3927,10 @@
         <v>27180.0</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
@@ -3938,13 +3941,13 @@
         <v>28</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D91" s="8">
         <v>112379.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F91" s="8">
         <v>13800.0</v>
@@ -3956,7 +3959,7 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -3974,7 +3977,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F92" s="8">
         <v>4575.0</v>
@@ -3986,10 +3989,10 @@
         <v>4213.0</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
@@ -3997,16 +4000,16 @@
         <v>46244.0</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D93" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F93" s="8">
         <v>222000.0</v>
@@ -4018,10 +4021,10 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
@@ -4029,16 +4032,16 @@
         <v>46244.0</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D94" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F94" s="8">
         <v>300060.0</v>
@@ -4050,10 +4053,10 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
@@ -4061,10 +4064,10 @@
         <v>46244.0</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D95" s="8">
         <v>2110402.0</v>
@@ -4082,10 +4085,10 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
@@ -4096,13 +4099,13 @@
         <v>10</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D96" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F96" s="8">
         <v>21690.0</v>
@@ -4123,10 +4126,10 @@
         <v>46245.0</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D97" s="8">
         <v>112271.0</v>
@@ -4153,10 +4156,10 @@
         <v>46245.0</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D98" s="8">
         <v>2110402.0</v>
@@ -4174,10 +4177,10 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
@@ -4185,16 +4188,16 @@
         <v>46245.0</v>
       </c>
       <c r="B99" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D99" s="8">
         <v>152384.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F99" s="8">
         <v>18600.0</v>
@@ -4206,10 +4209,10 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
@@ -4220,13 +4223,13 @@
         <v>10</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D100" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F100" s="8">
         <v>225620.0</v>
@@ -4238,7 +4241,7 @@
         <v>269040.0</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J100" s="12" t="s">
         <v>150</v>
@@ -4249,7 +4252,7 @@
         <v>46246.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>151</v>
@@ -4273,7 +4276,7 @@
         <v>14</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" ht="22.5" hidden="1" customHeight="1">
@@ -4284,13 +4287,13 @@
         <v>10</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D102" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F102" s="8">
         <v>800120.0</v>
@@ -4302,10 +4305,10 @@
         <v>655250.0</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
@@ -4316,7 +4319,7 @@
         <v>10</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D103" s="8">
         <v>112271.0</v>
@@ -4337,7 +4340,7 @@
         <v>20</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
@@ -4345,16 +4348,16 @@
         <v>46246.0</v>
       </c>
       <c r="B104" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D104" s="8">
         <v>152384.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F104" s="8">
         <v>12900.0</v>
@@ -4366,10 +4369,10 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
@@ -4380,13 +4383,13 @@
         <v>28</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D105" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F105" s="8">
         <v>193026.0</v>
@@ -4398,10 +4401,10 @@
         <v>63824.0</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J105" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
@@ -4409,16 +4412,16 @@
         <v>46247.0</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D106" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F106" s="8">
         <v>245520.0</v>
@@ -4430,7 +4433,7 @@
         <v>230580.0</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -4439,16 +4442,16 @@
         <v>46247.0</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D107" s="8">
         <v>2110217.0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F107" s="8">
         <v>21120.0</v>
@@ -4469,10 +4472,10 @@
         <v>46247.0</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D108" s="8">
         <v>112271.0</v>
@@ -4490,7 +4493,7 @@
         <v>12600.0</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -4502,13 +4505,13 @@
         <v>10</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D109" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F109" s="8">
         <v>793976.0</v>
@@ -4520,10 +4523,10 @@
         <v>584490.0</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="110" ht="22.5" hidden="1" customHeight="1">
@@ -4531,16 +4534,16 @@
         <v>46248.0</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D110" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F110" s="8">
         <v>289920.0</v>
@@ -4561,16 +4564,16 @@
         <v>46248.0</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D111" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F111" s="8">
         <v>230580.0</v>
@@ -4582,10 +4585,10 @@
         <v>298620.0</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112" ht="22.5" hidden="1" customHeight="1">
@@ -4593,16 +4596,16 @@
         <v>46248.0</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D112" s="8">
         <v>152384.0</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F112" s="8">
         <v>13200.0</v>
@@ -4614,10 +4617,10 @@
         <v>7200.0</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="113" ht="22.5" hidden="1" customHeight="1">
@@ -4625,16 +4628,16 @@
         <v>46248.0</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D113" s="8">
         <v>152384.0</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F113" s="8">
         <v>9900.0</v>
@@ -4649,7 +4652,7 @@
         <v>14</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" ht="22.5" hidden="1" customHeight="1">
@@ -4657,7 +4660,7 @@
         <v>46252.0</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>59</v>
@@ -4666,7 +4669,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F114" s="8">
         <v>184290.0</v>
@@ -4678,10 +4681,10 @@
         <v>68640.0</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="115" ht="22.5" hidden="1" customHeight="1">
@@ -4689,7 +4692,7 @@
         <v>46252.0</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>59</v>
@@ -4710,10 +4713,10 @@
         <v>26880.0</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="116" ht="22.5" hidden="1" customHeight="1">
@@ -4724,13 +4727,13 @@
         <v>10</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D116" s="8">
         <v>152384.0</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F116" s="8">
         <v>21585.0</v>
@@ -4742,10 +4745,10 @@
         <v>12900.0</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J116" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117" ht="22.5" hidden="1" customHeight="1">
@@ -4753,7 +4756,7 @@
         <v>46253.0</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>59</v>
@@ -4762,7 +4765,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F117" s="8">
         <v>179640.0</v>
@@ -4783,7 +4786,7 @@
         <v>46253.0</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>59</v>
@@ -4813,7 +4816,7 @@
         <v>46253.0</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>59</v>
@@ -4822,7 +4825,7 @@
         <v>152384.0</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F119" s="8">
         <v>14230.0</v>
@@ -4852,7 +4855,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F120" s="8">
         <v>26677.0</v>
@@ -4867,7 +4870,7 @@
         <v>14</v>
       </c>
       <c r="J120" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="121" ht="22.5" hidden="1" customHeight="1">
@@ -4878,13 +4881,13 @@
         <v>10</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D121" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F121" s="8">
         <v>22500.0</v>
@@ -4896,10 +4899,10 @@
         <v>18300.0</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J121" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" ht="22.5" hidden="1" customHeight="1">
@@ -4910,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D122" s="8">
         <v>112271.0</v>
@@ -4931,7 +4934,7 @@
         <v>26</v>
       </c>
       <c r="J122" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" ht="22.5" hidden="1" customHeight="1">
@@ -4939,7 +4942,7 @@
         <v>46254.0</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>151</v>
@@ -4948,7 +4951,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F123" s="8">
         <v>21915.0</v>
@@ -4960,7 +4963,7 @@
         <v>14235.0</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J123" s="12" t="s">
         <v>173</v>
@@ -4971,16 +4974,16 @@
         <v>46254.0</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D124" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F124" s="8">
         <v>10125.0</v>
@@ -5001,7 +5004,7 @@
         <v>46254.0</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>174</v>
@@ -5010,7 +5013,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F125" s="8">
         <v>6380.0</v>
@@ -5022,7 +5025,7 @@
         <v>1980.0</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J125" s="12" t="s">
         <v>175</v>
@@ -5036,7 +5039,7 @@
         <v>10</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D126" s="8">
         <v>2110402.0</v>
@@ -5063,7 +5066,7 @@
         <v>46255.0</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>176</v>
@@ -5084,7 +5087,7 @@
         <v>17760.0</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J127" s="12" t="s">
         <v>177</v>
@@ -5095,7 +5098,7 @@
         <v>46255.0</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>178</v>
@@ -5104,7 +5107,7 @@
         <v>112268.0</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F128" s="8">
         <v>3300.0</v>
@@ -5136,7 +5139,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F129" s="8">
         <v>2130.0</v>
@@ -5148,7 +5151,7 @@
         <v>1230.0</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J129" s="12" t="s">
         <v>182</v>
@@ -5168,7 +5171,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F130" s="8">
         <v>341120.0</v>
@@ -5191,16 +5194,16 @@
         <v>46258.0</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D131" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F131" s="8">
         <v>11520.0</v>
@@ -5253,16 +5256,16 @@
         <v>46259.0</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D133" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F133" s="8">
         <v>64620.0</v>
@@ -5274,7 +5277,7 @@
         <v>47685.0</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J133" s="12"/>
     </row>
@@ -5304,10 +5307,10 @@
         <v>11510.0</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J134" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" ht="22.5" hidden="1" customHeight="1">
@@ -5315,7 +5318,7 @@
         <v>46259.0</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>18</v>
@@ -5324,7 +5327,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F135" s="8">
         <v>48540.0</v>
@@ -5336,10 +5339,10 @@
         <v>105048.0</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J135" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" ht="22.5" hidden="1" customHeight="1">
@@ -5356,7 +5359,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F136" s="8">
         <v>194198.0</v>
@@ -5368,10 +5371,10 @@
         <v>140840.0</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J136" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" ht="22.5" hidden="1" customHeight="1">
@@ -5403,7 +5406,7 @@
         <v>20</v>
       </c>
       <c r="J137" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138" ht="22.5" hidden="1" customHeight="1">
@@ -5411,16 +5414,16 @@
         <v>46260.0</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D138" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F138" s="8">
         <v>47685.0</v>
@@ -5432,10 +5435,10 @@
         <v>107298.0</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J138" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" ht="22.5" hidden="1" customHeight="1">
@@ -5452,7 +5455,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F139" s="8">
         <v>30600.0</v>
@@ -5467,7 +5470,7 @@
         <v>20</v>
       </c>
       <c r="J139" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" ht="22.5" hidden="1" customHeight="1">
@@ -5475,16 +5478,16 @@
         <v>46261.0</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D140" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F140" s="8">
         <v>38640.0</v>
@@ -5508,13 +5511,13 @@
         <v>61</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D141" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F141" s="8">
         <v>365280.0</v>
@@ -5535,16 +5538,16 @@
         <v>46261.0</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D142" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F142" s="8">
         <v>192000.0</v>
@@ -5565,16 +5568,16 @@
         <v>46261.0</v>
       </c>
       <c r="B143" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D143" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F143" s="8">
         <v>10260.0</v>
@@ -5595,16 +5598,16 @@
         <v>46262.0</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D144" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F144" s="8">
         <v>10500.0</v>
@@ -5625,16 +5628,16 @@
         <v>46262.0</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D145" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F145" s="8">
         <v>91680.0</v>
@@ -5646,10 +5649,10 @@
         <v>84480.0</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J145" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" ht="22.5" hidden="1" customHeight="1">
@@ -5657,7 +5660,7 @@
         <v>46265.0</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>151</v>
@@ -5666,7 +5669,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F146" s="8">
         <v>17970.0</v>
@@ -5687,16 +5690,16 @@
         <v>46265.0</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D147" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F147" s="8">
         <v>9960.0</v>
@@ -5717,16 +5720,16 @@
         <v>46265.0</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D148" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F148" s="8">
         <v>10503.0</v>
@@ -5738,10 +5741,10 @@
         <v>9063.0</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J148" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="149" ht="22.5" hidden="1" customHeight="1">
@@ -5752,13 +5755,13 @@
         <v>10</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D149" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F149" s="8">
         <v>339300.0</v>
@@ -5770,10 +5773,10 @@
         <v>349380.0</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J149" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="150" ht="22.5" hidden="1" customHeight="1">
@@ -5781,16 +5784,16 @@
         <v>46266.0</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D150" s="8">
         <v>152384.0</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F150" s="8">
         <v>17100.0</v>
@@ -5802,7 +5805,7 @@
         <v>8700.0</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J150" s="12"/>
     </row>
@@ -5820,7 +5823,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F151" s="8">
         <v>3240.0</v>
@@ -5835,7 +5838,7 @@
         <v>14</v>
       </c>
       <c r="J151" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="152" ht="22.5" hidden="1" customHeight="1">
@@ -5846,13 +5849,13 @@
         <v>10</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D152" s="8">
         <v>152384.0</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F152" s="8">
         <v>25350.0</v>
@@ -5867,7 +5870,7 @@
         <v>26</v>
       </c>
       <c r="J152" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="153" ht="22.5" hidden="1" customHeight="1">
@@ -5884,7 +5887,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F153" s="8">
         <v>15660.0</v>
@@ -5896,10 +5899,10 @@
         <v>2520.0</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J153" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="154" ht="22.5" hidden="1" customHeight="1">
@@ -5916,7 +5919,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F154" s="8">
         <v>8280.0</v>
@@ -5928,10 +5931,10 @@
         <v>3375.0</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J154" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" ht="22.5" hidden="1" customHeight="1">
@@ -5939,16 +5942,16 @@
         <v>46268.0</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D155" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F155" s="8">
         <v>205020.0</v>
@@ -5960,10 +5963,10 @@
         <v>106200.0</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J155" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" ht="22.5" hidden="1" customHeight="1">
@@ -5971,16 +5974,16 @@
         <v>46268.0</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D156" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F156" s="8">
         <v>7920.0</v>
@@ -5992,10 +5995,10 @@
         <v>9720.0</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J156" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="157" ht="22.5" hidden="1" customHeight="1">
@@ -6003,10 +6006,10 @@
         <v>46268.0</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D157" s="8">
         <v>2110402.0</v>
@@ -6024,10 +6027,10 @@
         <v>12240.0</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J157" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" ht="22.5" hidden="1" customHeight="1">
@@ -6038,13 +6041,13 @@
         <v>10</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D158" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F158" s="8">
         <v>287280.0</v>
@@ -6059,7 +6062,7 @@
         <v>20</v>
       </c>
       <c r="J158" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="159" ht="22.5" hidden="1" customHeight="1">
@@ -6067,16 +6070,16 @@
         <v>46269.0</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D159" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F159" s="8">
         <v>6435.0</v>
@@ -6097,16 +6100,16 @@
         <v>46269.0</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D160" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F160" s="8">
         <v>440230.0</v>
@@ -6118,10 +6121,10 @@
         <v>300589.0</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="161" ht="22.5" hidden="1" customHeight="1">
@@ -6129,16 +6132,16 @@
         <v>46269.0</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D161" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F161" s="8">
         <v>8457.0</v>
@@ -6150,10 +6153,10 @@
         <v>8097.0</v>
       </c>
       <c r="I161" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J161" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" ht="22.5" hidden="1" customHeight="1">
@@ -6161,16 +6164,16 @@
         <v>46272.0</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D162" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F162" s="8">
         <v>96984.0</v>
@@ -6182,10 +6185,10 @@
         <v>40143.0</v>
       </c>
       <c r="I162" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J162" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" ht="22.5" hidden="1" customHeight="1">
@@ -6196,13 +6199,13 @@
         <v>10</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D163" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F163" s="8">
         <v>345572.0</v>
@@ -6214,10 +6217,10 @@
         <v>444960.0</v>
       </c>
       <c r="I163" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J163" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" ht="22.5" hidden="1" customHeight="1">
@@ -6228,13 +6231,13 @@
         <v>10</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D164" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F164" s="8">
         <v>21960.0</v>
@@ -6246,10 +6249,10 @@
         <v>18330.0</v>
       </c>
       <c r="I164" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J164" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="165" ht="22.5" hidden="1" customHeight="1">
@@ -6257,10 +6260,10 @@
         <v>46273.0</v>
       </c>
       <c r="B165" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C165" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D165" s="8">
         <v>2110402.0</v>
@@ -6278,10 +6281,10 @@
         <v>21840.0</v>
       </c>
       <c r="I165" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J165" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="166" ht="22.5" hidden="1" customHeight="1">
@@ -6289,10 +6292,10 @@
         <v>46273.0</v>
       </c>
       <c r="B166" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C166" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D166" s="8">
         <v>112271.0</v>
@@ -6319,16 +6322,16 @@
         <v>46273.0</v>
       </c>
       <c r="B167" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D167" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F167" s="8">
         <v>10620.0</v>
@@ -6340,10 +6343,10 @@
         <v>8460.0</v>
       </c>
       <c r="I167" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J167" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="168" ht="22.5" hidden="1" customHeight="1">
@@ -6351,16 +6354,16 @@
         <v>46273.0</v>
       </c>
       <c r="B168" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C168" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D168" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F168" s="8">
         <v>239040.0</v>
@@ -6372,10 +6375,10 @@
         <v>123360.0</v>
       </c>
       <c r="I168" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J168" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
@@ -6383,7 +6386,7 @@
         <v>46274.0</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>59</v>
@@ -6392,7 +6395,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F169" s="8">
         <v>123360.0</v>
@@ -6407,7 +6410,7 @@
         <v>14</v>
       </c>
       <c r="J169" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
@@ -6415,7 +6418,7 @@
         <v>46274.0</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>59</v>
@@ -6424,7 +6427,7 @@
         <v>2110317.0</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F170" s="8">
         <v>8460.0</v>
@@ -6448,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D171" s="8">
         <v>112271.0</v>
@@ -6469,7 +6472,7 @@
         <v>26</v>
       </c>
       <c r="J171" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
@@ -6480,13 +6483,13 @@
         <v>10</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D172" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F172" s="8">
         <v>18330.0</v>
@@ -6501,7 +6504,7 @@
         <v>20</v>
       </c>
       <c r="J172" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
@@ -6512,13 +6515,13 @@
         <v>10</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D173" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F173" s="8">
         <v>340260.0</v>
@@ -6533,7 +6536,7 @@
         <v>20</v>
       </c>
       <c r="J173" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
@@ -6544,7 +6547,7 @@
         <v>10</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D174" s="8">
         <v>2110402.0</v>
@@ -6565,7 +6568,7 @@
         <v>20</v>
       </c>
       <c r="J174" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
@@ -6576,13 +6579,13 @@
         <v>10</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D175" s="8">
         <v>152384.0</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F175" s="8">
         <v>18585.0</v>
@@ -6597,7 +6600,7 @@
         <v>26</v>
       </c>
       <c r="J175" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
@@ -6605,16 +6608,16 @@
         <v>46275.0</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D176" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F176" s="8">
         <v>151680.0</v>
@@ -6626,10 +6629,10 @@
         <v>67680.0</v>
       </c>
       <c r="I176" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J176" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
@@ -6637,10 +6640,10 @@
         <v>46275.0</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D177" s="8">
         <v>2110402.0</v>
@@ -6658,10 +6661,10 @@
         <v>18480.0</v>
       </c>
       <c r="I177" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J177" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
@@ -6678,7 +6681,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F178" s="8">
         <v>2130.0</v>
@@ -6699,7 +6702,7 @@
         <v>46276.0</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>151</v>
@@ -6720,17 +6723,71 @@
         <v>627558.0</v>
       </c>
       <c r="I179" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J179" s="12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="I180" s="23"/>
-    </row>
-    <row r="181">
-      <c r="I181" s="23"/>
+        <v>223</v>
+      </c>
+    </row>
+    <row r="180" ht="22.5" customHeight="1">
+      <c r="A180" s="7">
+        <v>46280.0</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D180" s="8">
+        <v>2110402.0</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F180" s="8">
+        <v>653620.0</v>
+      </c>
+      <c r="G180" s="8">
+        <v>227800.0</v>
+      </c>
+      <c r="H180" s="8">
+        <v>382568.0</v>
+      </c>
+      <c r="I180" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J180" s="12"/>
+    </row>
+    <row r="181" ht="22.5" customHeight="1">
+      <c r="A181" s="7">
+        <v>46280.0</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D181" s="8">
+        <v>2110302.0</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F181" s="8">
+        <v>393840.0</v>
+      </c>
+      <c r="G181" s="8">
+        <v>121232.0</v>
+      </c>
+      <c r="H181" s="8">
+        <v>255600.0</v>
+      </c>
+      <c r="I181" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J181" s="12"/>
     </row>
     <row r="182">
       <c r="I182" s="23"/>
@@ -9212,13 +9269,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I179">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I181">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I180:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I182:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A179">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A181">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -9285,7 +9342,7 @@
         <v>46224.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="8">
@@ -9304,7 +9361,7 @@
         <v>3712.0</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>19</v>
@@ -9315,14 +9372,14 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="8">
         <v>2114158.0</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="8">
         <v>60.0</v>
@@ -9345,14 +9402,14 @@
         <v>46225.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="8">
         <v>10501.0</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F4" s="8">
         <v>415093.0</v>
@@ -9375,14 +9432,14 @@
         <v>46225.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="8">
         <v>112379.0</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" s="8">
         <v>3000.0</v>
@@ -9394,10 +9451,10 @@
         <v>3000.0</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -9405,14 +9462,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="8">
         <v>112268.0</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" s="8">
         <v>3000.0</v>
@@ -9424,10 +9481,10 @@
         <v>3300.0</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -9435,14 +9492,14 @@
         <v>46225.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="8">
         <v>132357.0</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8">
         <v>1560.0</v>
@@ -9454,10 +9511,10 @@
         <v>4560.0</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -9465,14 +9522,14 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="8">
         <v>720.0</v>
@@ -9484,7 +9541,7 @@
         <v>5940.0</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>52</v>
@@ -9495,7 +9552,7 @@
         <v>46225.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="8">
@@ -9514,10 +9571,10 @@
         <v>213.0</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
@@ -9525,7 +9582,7 @@
         <v>46226.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="8">
@@ -9544,7 +9601,7 @@
         <v>109487.0</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>57</v>
@@ -9555,14 +9612,14 @@
         <v>46226.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="8">
         <v>112268.0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="8">
         <v>3300.0</v>
@@ -9583,14 +9640,14 @@
         <v>46226.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="8">
         <v>112379.0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="8">
         <v>4200.0</v>
@@ -9611,14 +9668,14 @@
         <v>46226.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="8">
         <v>379471.0</v>
@@ -9630,7 +9687,7 @@
         <v>357186.0</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>57</v>
@@ -9641,7 +9698,7 @@
         <v>46227.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="8">
@@ -9660,7 +9717,7 @@
         <v>38000.0</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>57</v>
@@ -9671,14 +9728,14 @@
         <v>46227.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="8">
         <v>2110327.0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F15" s="8">
         <v>69120.0</v>
@@ -9690,10 +9747,10 @@
         <v>40320.0</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -9701,14 +9758,14 @@
         <v>46227.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="8">
         <v>112379.0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="8">
         <v>3900.0</v>
@@ -9729,14 +9786,14 @@
         <v>46227.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F17" s="8">
         <v>720.0</v>
@@ -9757,14 +9814,14 @@
         <v>46227.0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="8">
         <v>112268.0</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F18" s="8">
         <v>3300.0</v>
@@ -9776,10 +9833,10 @@
         <v>600.0</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
@@ -9787,14 +9844,14 @@
         <v>46230.0</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="8">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="8">
         <v>136538.0</v>
@@ -9806,10 +9863,10 @@
         <v>213000.0</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -9817,14 +9874,14 @@
         <v>46231.0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="8">
         <v>591750.0</v>
@@ -9836,10 +9893,10 @@
         <v>577207.0</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
@@ -9847,14 +9904,14 @@
         <v>46231.0</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="8">
         <v>10601.0</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F21" s="8">
         <v>1230.0</v>
@@ -9866,10 +9923,10 @@
         <v>1958.0</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -9877,14 +9934,14 @@
         <v>46231.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F22" s="8">
         <v>4320.0</v>
@@ -9896,7 +9953,7 @@
         <v>3420.0</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -9905,14 +9962,14 @@
         <v>46231.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="8">
         <v>114357.0</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="8">
         <v>240.0</v>
@@ -9924,7 +9981,7 @@
         <v>240.0</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -9933,14 +9990,14 @@
         <v>46232.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="8">
         <v>10501.0</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F24" s="8">
         <v>19663.0</v>
@@ -9952,7 +10009,7 @@
         <v>29632.0</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J24" s="12"/>
     </row>
@@ -9961,14 +10018,14 @@
         <v>46232.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="8">
         <v>112268.0</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F25" s="8">
         <v>5700.0</v>
@@ -9980,7 +10037,7 @@
         <v>5100.0</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J25" s="12"/>
     </row>
@@ -9989,14 +10046,14 @@
         <v>46232.0</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F26" s="8">
         <v>720.0</v>
@@ -10008,7 +10065,7 @@
         <v>720.0</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" s="12"/>
     </row>
@@ -10017,14 +10074,14 @@
         <v>46232.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="8">
         <v>2114357.0</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27" s="8">
         <v>432.0</v>
@@ -10036,7 +10093,7 @@
         <v>432.0</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="12"/>
     </row>
@@ -10045,14 +10102,14 @@
         <v>46232.0</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="8">
         <v>10501.0</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F28" s="8">
         <v>219540.0</v>
@@ -10064,7 +10121,7 @@
         <v>16698.0</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="12"/>
     </row>
@@ -10073,14 +10130,14 @@
         <v>46233.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="8">
         <v>112268.0</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F29" s="8">
         <v>5100.0</v>
@@ -10092,7 +10149,7 @@
         <v>4800.0</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -10101,14 +10158,14 @@
         <v>46233.0</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="8">
         <v>114357.0</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F30" s="8">
         <v>240.0</v>
@@ -10120,7 +10177,7 @@
         <v>1560.0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -10129,14 +10186,14 @@
         <v>46233.0</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="8">
         <v>10601.0</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F31" s="8">
         <v>7717.0</v>
@@ -10148,10 +10205,10 @@
         <v>12867.0</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
@@ -10159,14 +10216,14 @@
         <v>46234.0</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="8">
         <v>79110.0</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F32" s="8">
         <v>48000.0</v>
@@ -10181,7 +10238,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
@@ -10189,14 +10246,14 @@
         <v>46234.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="8">
         <v>10501.0</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F33" s="8">
         <v>95574.0</v>
@@ -10208,7 +10265,7 @@
         <v>142801.0</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J33" s="18" t="s">
         <v>95</v>
@@ -10219,7 +10276,7 @@
         <v>46234.0</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="8">
@@ -10238,7 +10295,7 @@
         <v>39150.0</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J34" s="12"/>
     </row>
@@ -10247,7 +10304,7 @@
         <v>46234.0</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="8">
@@ -10266,7 +10323,7 @@
         <v>480.0</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -10275,14 +10332,14 @@
         <v>46237.0</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="8">
         <v>10601.0</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F36" s="8">
         <v>17934.0</v>
@@ -10294,10 +10351,10 @@
         <v>21714.0</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
@@ -10305,14 +10362,14 @@
         <v>46237.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" s="8">
         <v>194520.0</v>
@@ -10333,14 +10390,14 @@
         <v>46237.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="8">
         <v>114379.0</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" s="8">
         <v>52200.0</v>
@@ -10352,7 +10409,7 @@
         <v>7500.0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -10361,14 +10418,14 @@
         <v>46237.0</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="8">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F39" s="8">
         <v>6450.0</v>
@@ -10389,14 +10446,14 @@
         <v>46237.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F40" s="8">
         <v>1398.0</v>
@@ -10417,14 +10474,14 @@
         <v>46238.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F41" s="8">
         <v>2460.0</v>
@@ -10445,14 +10502,14 @@
         <v>46238.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="8">
         <v>112268.0</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F42" s="8">
         <v>3600.0</v>
@@ -10473,14 +10530,14 @@
         <v>46238.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="8">
         <v>114379.0</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" s="8">
         <v>7500.0</v>
@@ -10501,14 +10558,14 @@
         <v>46238.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="8">
         <v>114357.0</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F44" s="8">
         <v>240.0</v>
@@ -10529,14 +10586,14 @@
         <v>46239.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="8">
         <v>10601.0</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F45" s="8">
         <v>1115.0</v>
@@ -10548,10 +10605,10 @@
         <v>1590.0</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -10559,14 +10616,14 @@
         <v>46239.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46" s="8">
         <v>114240.0</v>
@@ -10587,14 +10644,14 @@
         <v>46239.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F47" s="8">
         <v>1800.0</v>
@@ -10606,7 +10663,7 @@
         <v>1980.0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J47" s="12"/>
     </row>
@@ -10615,14 +10672,14 @@
         <v>46239.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="8">
         <v>112268.0</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F48" s="8">
         <v>3900.0</v>
@@ -10634,7 +10691,7 @@
         <v>1200.0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J48" s="12"/>
     </row>
@@ -10643,7 +10700,7 @@
         <v>46239.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="8">
@@ -10662,7 +10719,7 @@
         <v>600.0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J49" s="12"/>
     </row>
@@ -10671,14 +10728,14 @@
         <v>46239.0</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="8">
         <v>114268.0</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F50" s="8">
         <v>2700.0</v>
@@ -10690,7 +10747,7 @@
         <v>300.0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J50" s="12"/>
     </row>
@@ -10699,14 +10756,14 @@
         <v>46239.0</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="8">
         <v>10501.0</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F51" s="8">
         <v>68651.0</v>
@@ -10718,10 +10775,10 @@
         <v>13421.0</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
@@ -10729,14 +10786,14 @@
         <v>46239.0</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="8">
         <v>72003.0</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F52" s="8">
         <v>1391.0</v>
@@ -10757,7 +10814,7 @@
         <v>46239.0</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="8">
@@ -10776,7 +10833,7 @@
         <v>3317.0</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>120</v>
@@ -10787,14 +10844,14 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="8">
         <v>112379.0</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F54" s="8">
         <v>3600.0</v>
@@ -10815,7 +10872,7 @@
         <v>46240.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="8">
@@ -10843,7 +10900,7 @@
         <v>46240.0</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="8">
@@ -10871,14 +10928,14 @@
         <v>46240.0</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="8">
         <v>114379.0</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F57" s="8">
         <v>2400.0</v>
@@ -10899,14 +10956,14 @@
         <v>46244.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="8">
         <v>112379.0</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F58" s="8">
         <v>4800.0</v>
@@ -10927,14 +10984,14 @@
         <v>46245.0</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F59" s="8">
         <v>25574.0</v>
@@ -10955,14 +11012,14 @@
         <v>46246.0</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="8">
         <v>114379.0</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F60" s="8">
         <v>6900.0</v>
@@ -10983,14 +11040,14 @@
         <v>46247.0</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="8">
         <v>112379.0</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F61" s="8">
         <v>20100.0</v>
@@ -11002,7 +11059,7 @@
         <v>20100.0</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J61" s="12"/>
     </row>
@@ -11011,14 +11068,14 @@
         <v>46247.0</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="8">
         <v>112268.0</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F62" s="8">
         <v>8400.0</v>
@@ -11030,7 +11087,7 @@
         <v>8400.0</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J62" s="12"/>
     </row>
@@ -11039,14 +11096,14 @@
         <v>46247.0</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F63" s="8">
         <v>61250.0</v>
@@ -11058,7 +11115,7 @@
         <v>76033.0</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J63" s="12"/>
     </row>
@@ -11067,14 +11124,14 @@
         <v>46247.0</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="8">
         <v>13358.0</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F64" s="8">
         <v>73728.0</v>
@@ -11086,10 +11143,10 @@
         <v>73440.0</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" ht="19.5" hidden="1" customHeight="1">
@@ -11097,14 +11154,14 @@
         <v>46248.0</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" s="8">
         <v>285596.0</v>
@@ -11116,10 +11173,10 @@
         <v>72480.0</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" ht="19.5" hidden="1" customHeight="1">
@@ -11127,7 +11184,7 @@
         <v>46248.0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="8">
@@ -11146,10 +11203,10 @@
         <v>28820.0</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="67" ht="19.5" hidden="1" customHeight="1">
@@ -11157,14 +11214,14 @@
         <v>46254.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="8">
         <v>10601.0</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F67" s="8">
         <v>73085.0</v>
@@ -11176,10 +11233,10 @@
         <v>78125.0</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" ht="19.5" hidden="1" customHeight="1">
@@ -11187,14 +11244,14 @@
         <v>46254.0</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="8">
         <v>112379.0</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F68" s="8">
         <v>18000.0</v>
@@ -11206,10 +11263,10 @@
         <v>18000.0</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J68" s="21" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" ht="19.5" hidden="1" customHeight="1">
@@ -11217,14 +11274,14 @@
         <v>46254.0</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="8">
         <v>114357.0</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F69" s="8">
         <v>120.0</v>
@@ -11236,10 +11293,10 @@
         <v>120.0</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" ht="19.5" hidden="1" customHeight="1">
@@ -11247,14 +11304,14 @@
         <v>46254.0</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="8">
         <v>10601.0</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F70" s="8">
         <v>5700.0</v>
@@ -11266,10 +11323,10 @@
         <v>9270.0</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" ht="19.5" hidden="1" customHeight="1">
@@ -11277,14 +11334,14 @@
         <v>46254.0</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="8">
         <v>114268.0</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F71" s="8">
         <v>2700.0</v>
@@ -11296,10 +11353,10 @@
         <v>5700.0</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" ht="19.5" hidden="1" customHeight="1">
@@ -11307,14 +11364,14 @@
         <v>46254.0</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="8">
         <v>2114379.0</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F72" s="8">
         <v>2340.0</v>
@@ -11326,10 +11383,10 @@
         <v>2340.0</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
@@ -11337,14 +11394,14 @@
         <v>46255.0</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F73" s="8">
         <v>88073.0</v>
@@ -11359,7 +11416,7 @@
         <v>20</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
@@ -11367,14 +11424,14 @@
         <v>46255.0</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F74" s="8">
         <v>72060.0</v>
@@ -11386,10 +11443,10 @@
         <v>133320.0</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
@@ -11397,14 +11454,14 @@
         <v>46255.0</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="8">
         <v>152384.0</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F75" s="8">
         <v>6600.0</v>
@@ -11416,10 +11473,10 @@
         <v>1200.0</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J75" s="12" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
@@ -11427,14 +11484,14 @@
         <v>46256.0</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="8">
         <v>13358.0</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F76" s="8">
         <v>288.0</v>
@@ -11446,10 +11503,10 @@
         <v>288.0</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
@@ -11457,14 +11514,14 @@
         <v>46261.0</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C77" s="14"/>
       <c r="D77" s="8">
         <v>10601.0</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F77" s="8">
         <v>16770.0</v>
@@ -11485,14 +11542,14 @@
         <v>46261.0</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C78" s="14"/>
       <c r="D78" s="8">
         <v>114379.0</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F78" s="8">
         <v>3600.0</v>
@@ -11504,7 +11561,7 @@
         <v>3600.0</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -11513,14 +11570,14 @@
         <v>46262.0</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F79" s="8">
         <v>59670.0</v>
@@ -11532,7 +11589,7 @@
         <v>125400.0</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -11541,14 +11598,14 @@
         <v>46262.0</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="8">
         <v>114268.0</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F80" s="8">
         <v>33000.0</v>
@@ -11560,7 +11617,7 @@
         <v>10800.0</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -11569,14 +11626,14 @@
         <v>46262.0</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="8">
         <v>112379.0</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F81" s="8">
         <v>15000.0</v>
@@ -11588,7 +11645,7 @@
         <v>6300.0</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -11597,7 +11654,7 @@
         <v>46262.0</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="8">
@@ -11616,7 +11673,7 @@
         <v>1560.0</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -11625,14 +11682,14 @@
         <v>46262.0</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="8">
         <v>10103.0</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F83" s="8">
         <v>200.0</v>
@@ -11644,7 +11701,7 @@
         <v>100.0</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -11653,7 +11710,7 @@
         <v>46265.0</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="8">
@@ -11681,14 +11738,14 @@
         <v>46265.0</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="8">
         <v>112268.0</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F85" s="8">
         <v>1200.0</v>
@@ -11709,14 +11766,14 @@
         <v>46265.0</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="8">
         <v>13358.0</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F86" s="8">
         <v>73440.0</v>
@@ -11728,7 +11785,7 @@
         <v>36864.0</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -11737,14 +11794,14 @@
         <v>46265.0</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="8">
         <v>13524.0</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F87" s="8">
         <v>240.0</v>
@@ -11756,7 +11813,7 @@
         <v>138480.0</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -11765,14 +11822,14 @@
         <v>46265.0</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="8">
         <v>114357.0</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F88" s="8">
         <v>120.0</v>
@@ -11784,7 +11841,7 @@
         <v>600.0</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -11793,7 +11850,7 @@
         <v>46267.0</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="8">
@@ -11821,14 +11878,14 @@
         <v>46268.0</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="8">
         <v>2010102.0</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F90" s="8">
         <v>2938.0</v>
@@ -11849,14 +11906,14 @@
         <v>46269.0</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="8">
         <v>2110427.0</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F91" s="8">
         <v>11520.0</v>
@@ -11877,14 +11934,14 @@
         <v>46269.0</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F92" s="8">
         <v>281580.0</v>
@@ -11905,14 +11962,14 @@
         <v>46269.0</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="8">
         <v>114379.0</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F93" s="8">
         <v>3900.0</v>
@@ -11933,14 +11990,14 @@
         <v>46269.0</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F94" s="8">
         <v>5040.0</v>
@@ -11961,7 +12018,7 @@
         <v>46272.0</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="8">
@@ -11989,14 +12046,14 @@
         <v>46272.0</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="8">
         <v>2110302.0</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F96" s="8">
         <v>340080.0</v>
@@ -12017,14 +12074,14 @@
         <v>46272.0</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="8">
         <v>272003.0</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F97" s="8">
         <v>25404.0</v>
@@ -12045,14 +12102,14 @@
         <v>46272.0</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="8">
         <v>2152388.0</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F98" s="8">
         <v>4140.0</v>
@@ -12073,14 +12130,14 @@
         <v>46272.0</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="8">
         <v>273003.0</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F99" s="8">
         <v>12100.0</v>
@@ -12101,14 +12158,14 @@
         <v>46272.0</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C100" s="14"/>
       <c r="D100" s="8">
         <v>2114268.0</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F100" s="8">
         <v>180.0</v>
@@ -12129,14 +12186,14 @@
         <v>46274.0</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="8">
         <v>114379.0</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F101" s="8">
         <v>6900.0</v>
@@ -12157,7 +12214,7 @@
         <v>46274.0</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="8">
@@ -12185,14 +12242,14 @@
         <v>46274.0</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="8">
         <v>2410401.0</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F103" s="8">
         <v>118286.0</v>
@@ -12213,14 +12270,14 @@
         <v>46276.0</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F104" s="8">
         <v>264061.0</v>
@@ -12232,7 +12289,7 @@
         <v>141318.0</v>
       </c>
       <c r="I104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J104" s="12"/>
     </row>
@@ -12241,14 +12298,14 @@
         <v>46276.0</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="8">
         <v>273003.0</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F105" s="8">
         <v>9106.0</v>
@@ -12260,7 +12317,7 @@
         <v>13876.0</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J105" s="12"/>
     </row>
@@ -12269,14 +12326,14 @@
         <v>46276.0</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="8">
         <v>10501.0</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F106" s="8">
         <v>3368.0</v>
@@ -12288,7 +12345,7 @@
         <v>7017.0</v>
       </c>
       <c r="I106" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -12297,14 +12354,14 @@
         <v>46279.0</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="8">
         <v>2110202.0</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F107" s="8">
         <v>445991.0</v>
@@ -12315,22 +12372,26 @@
       <c r="H107" s="8">
         <v>221756.0</v>
       </c>
-      <c r="I107" s="11"/>
-      <c r="J107" s="12"/>
+      <c r="I107" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="12" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="7">
         <v>46279.0</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="8">
         <v>2112207.0</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F108" s="8">
         <v>360.0</v>
@@ -12342,7 +12403,7 @@
         <v>180.0</v>
       </c>
       <c r="I108" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J108" s="12"/>
     </row>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="232">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -53,12 +53,12 @@
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
-  </si>
-  <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
@@ -68,15 +68,15 @@
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
+    <t>TAT MONTERIA</t>
+  </si>
+  <si>
+    <t>LUIS LOPEZ</t>
+  </si>
+  <si>
     <t>LANZA</t>
   </si>
   <si>
-    <t>TAT MONTERIA</t>
-  </si>
-  <si>
-    <t>LUIS LOPEZ</t>
-  </si>
-  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
@@ -101,6 +101,9 @@
     <t>HUEVO B X30 CARTON GRIS</t>
   </si>
   <si>
+    <t>se equivocaron al cargar una estiba</t>
+  </si>
+  <si>
     <t>TAT CARTAGENA</t>
   </si>
   <si>
@@ -110,7 +113,7 @@
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>se equivocaron al cargar una estiba</t>
+    <t>HUEVO L X 30 PET CAJA X 300</t>
   </si>
   <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
@@ -119,37 +122,43 @@
     <t>Venta FS</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300</t>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
+    <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300</t>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
   </si>
   <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>PALMAS</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
   </si>
   <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>TAT CALI</t>
@@ -158,10 +167,7 @@
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
-  </si>
-  <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
   </si>
   <si>
     <t>TAT CUCUTA</t>
@@ -170,27 +176,30 @@
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
-  </si>
-  <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+    <t>HUEVO PICADO ROJO</t>
+  </si>
+  <si>
+    <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
     <t>Clientes FS</t>
   </si>
   <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
-    <t>No se carga todod por capacidad de Vehiculo</t>
-  </si>
-  <si>
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
+    <t>Esta para despacho hoy</t>
+  </si>
+  <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
@@ -203,37 +212,37 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
-  </si>
-  <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
-    <t>Cola de programación</t>
+    <t>HUEVO CX30 CARTON GRIS</t>
+  </si>
+  <si>
+    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
   </si>
   <si>
     <t>Producto con novedades de calidad, se está bandejeando</t>
   </si>
   <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
+    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
   </si>
   <si>
     <t>HUEVO XL X 15 PET CAJA X 300 - TAT</t>
   </si>
   <si>
-    <t>HUEVO CX30 CARTON GRIS</t>
-  </si>
-  <si>
-    <t>vehiculo compartido entre las 3 plantas / d ebaja capacidad / palma por ser la ultima panta en cargar quedo sin espacio para cargar</t>
+    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
     <t>5. Ingreso De Planta</t>
@@ -242,22 +251,31 @@
     <t>Se despacha par FS con producto más nuevo</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120 PV.</t>
-  </si>
-  <si>
     <t>ANDREA QUIROGA</t>
   </si>
   <si>
     <t>Descanastillado para clientes puntuales se presento rotura y mala calidad para el despacho por eso se salto la rotacion</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
+    <t>ALKA1</t>
+  </si>
+  <si>
+    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
+  </si>
+  <si>
+    <t>HUEVO ROTO - ZF</t>
   </si>
   <si>
     <t>Se despacha producto más nuevo para Rionegro</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
+    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
+  </si>
+  <si>
+    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
+  </si>
+  <si>
+    <t>HUEVO L X 12 PET CAJA X 120</t>
   </si>
   <si>
     <t>TAT PASTO</t>
@@ -266,33 +284,21 @@
     <t>CAROLINA VITERI</t>
   </si>
   <si>
-    <t>ALKA1</t>
+    <t>Cargo en incubación</t>
   </si>
   <si>
     <t>Asignacion a canal Tat para sugeridos de hoy</t>
   </si>
   <si>
-    <t>Ajuste desde los pedidos en planeación, la venta fue menor</t>
-  </si>
-  <si>
-    <t>HUEVO ROTO - ZF</t>
+    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
   </si>
   <si>
     <t>Pedido para villavicencio</t>
   </si>
   <si>
-    <t>Teniamos huevo en canastilla con fecha anterior, que no se evidencio al momento del alistamiento , este fue resuelto se despacho a ZF</t>
-  </si>
-  <si>
-    <t>teniamos huevo en canastilla con esa misma fecha, el cual planeacion envio a desencanastillar y ese fue el que se despacho (con esa fecha habian entonces 120.977)</t>
-  </si>
-  <si>
     <t>Se entrega inventario nuevo para FS</t>
   </si>
   <si>
-    <t>HUEVO L X 12 PET CAJA X 120</t>
-  </si>
-  <si>
     <t>Inventario de Asesor de Rionegro que renuncio</t>
   </si>
   <si>
@@ -302,106 +308,97 @@
     <t>Jhonatan Gomez</t>
   </si>
   <si>
-    <t>Cargo en incubación</t>
+    <t>BELLAVISTA</t>
+  </si>
+  <si>
+    <t>Traslado a cedi, producto de devolución</t>
   </si>
   <si>
     <t>Lote mezclado en la misma estiba</t>
   </si>
   <si>
-    <t>HUEVO L X 30 PET CAJA X 300 PV.</t>
+    <t>HUEVO XL X 15 PET CANASTA</t>
   </si>
   <si>
     <t>Supera edad solicitada clientes grandes superficies</t>
   </si>
   <si>
+    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
+  </si>
+  <si>
     <t>Pedido para villacicencio</t>
   </si>
   <si>
+    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
+  </si>
+  <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
     <t>Se envía huevo más fresco a Sincelejo</t>
   </si>
   <si>
+    <t>vehiculo con flata de capacidad / TAT cali</t>
+  </si>
+  <si>
     <t>Sugerido menor a la venta y se saca de un lote de mejor edad para 1 pedido de FS, llega huevo de 10 dias de planta</t>
   </si>
   <si>
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
-    <t>BELLAVISTA</t>
-  </si>
-  <si>
     <t>SalIO en sugeridos de hoy 22/07/2026</t>
   </si>
   <si>
     <t>Yovanis Arevalo</t>
   </si>
   <si>
-    <t>Traslado a cedi, producto de devolución</t>
-  </si>
-  <si>
     <t>mercancia de Barranquilla de 12 dias y llegadas de plantas con 9 dias</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CANASTA</t>
-  </si>
-  <si>
     <t>Devolucion de huevo de 12 dias en mal estado</t>
   </si>
   <si>
     <t>huevo recibido siniestro Barranquilla y devolución 12 dias en mal estado</t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CAJA X 300 PV.</t>
-  </si>
-  <si>
     <t>HUEVO M X30 CARTON VERDE AMARRADO CANASTA</t>
   </si>
   <si>
-    <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
-  </si>
-  <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
+    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
+  </si>
+  <si>
+    <t>vehiculo pendiente pro llegar a planta</t>
+  </si>
+  <si>
+    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
   </si>
   <si>
     <t>Se solicitó autorización para entregar un lote más nuevo a un cliente blindar</t>
   </si>
   <si>
-    <t>vehiculo con flata de capacidad / TAT cali</t>
-  </si>
-  <si>
     <t>Se envía producto a Sincelejo con menor edad</t>
   </si>
   <si>
+    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
+  </si>
+  <si>
+    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
+  </si>
+  <si>
     <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
+    <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
+  </si>
+  <si>
+    <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
+  </si>
+  <si>
     <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
-    <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
-  </si>
-  <si>
-    <t>vehiculo pendiente pro llegar a planta</t>
-  </si>
-  <si>
-    <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
-  </si>
-  <si>
-    <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
-  </si>
-  <si>
-    <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
-  </si>
-  <si>
-    <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
-  </si>
-  <si>
-    <t>Clasificación entrego una caja de más y no fue posible rotarla en cliente olimpica.</t>
-  </si>
-  <si>
     <t>NO SE PUEDE BAJAR DE LA ESTANTERIA POR DAÑO DE PANTOGRAFOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
   </si>
   <si>
     <t>HUEVO L X 30 PET CANASTA X 180 PV</t>
@@ -411,6 +408,12 @@
 En simultáneo, se cargó la mula y se desencadenaron las 18.000 unidades de 112379 para despachar para Medellín. En esta acción nos percatamos solo cuando la mula ya estaba en un 70 % cargada que se nos estaban quedando 21.525 de la referencia L canastas (2110302) con fecha de producción 19/08/2026.</t>
   </si>
   <si>
+    <t>REPOSICION SIN SOLTAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la estiba llegan lotes en la parte de abajo </t>
+  </si>
+  <si>
     <t>TAT BUCARAMANGA</t>
   </si>
   <si>
@@ -420,15 +423,15 @@
     <t xml:space="preserve">No salio la totalidad  de la mercancia y se roto el de 5 dias </t>
   </si>
   <si>
-    <t>REPOSICION SIN SOLTAR</t>
-  </si>
-  <si>
     <t>Producto queda en CEDI por calidad</t>
   </si>
   <si>
     <t>Producto devuelto clientes TAT</t>
   </si>
   <si>
+    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALEXANDER PEÑA </t>
   </si>
   <si>
@@ -441,9 +444,6 @@
     <t>Se envía lotemás nuevo a Sincelejo</t>
   </si>
   <si>
-    <t>HUEVO YUMBO X20 CARTON VERDE AMARRADO</t>
-  </si>
-  <si>
     <t>HUEVO B X 240 BANDEJA GRIS CAJA AMARRADO BUENASOS.</t>
   </si>
   <si>
@@ -459,36 +459,36 @@
     <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
   </si>
   <si>
+    <t>yOVANIS AREVALO</t>
+  </si>
+  <si>
     <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
   </si>
   <si>
-    <t>yOVANIS AREVALO</t>
+    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
+  </si>
+  <si>
+    <t>Se envía huevo fresco a Rionegro</t>
   </si>
   <si>
     <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
   </si>
   <si>
-    <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
   </si>
   <si>
-    <t>Se envía huevo fresco a Rionegro</t>
-  </si>
-  <si>
     <t>Clientes Fs</t>
   </si>
   <si>
     <t>Se envían para Rionegro con mejor fecha</t>
   </si>
   <si>
+    <t>Llega de planta bellavista</t>
+  </si>
+  <si>
     <t>El lote no se despachó el día anterior debido a que el envío se realizó en un vehículo compartido. Al ser Palmas la última bodega en la que se realizó la carga, solo se logró despachar la cantidad que la capacidad del vehículo permitió.</t>
   </si>
   <si>
-    <t>Llega de planta bellavista</t>
-  </si>
-  <si>
     <t>Jhonathan Gomez</t>
   </si>
   <si>
@@ -498,12 +498,12 @@
     <t>LLegada de planta</t>
   </si>
   <si>
+    <t xml:space="preserve">Asignado canal TAT </t>
+  </si>
+  <si>
     <t>HUEVO AA X30 CARTON GRIS CANASTA</t>
   </si>
   <si>
-    <t xml:space="preserve">Asignado canal TAT </t>
-  </si>
-  <si>
     <t>reportaron mal las edades</t>
   </si>
   <si>
@@ -699,7 +699,16 @@
     <t>En el cedi se le está dando la rotación bien,  producto nos llega con 5 días.</t>
   </si>
   <si>
+    <t xml:space="preserve">llega  de BELLAVISTA  </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sale en sugeridos de hoy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRES CAMILO MEJIA  </t>
+  </si>
+  <si>
+    <t>Lotes mezclados, se despacha en sugeridos</t>
   </si>
 </sst>
 </file>
@@ -739,14 +748,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -786,54 +795,54 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -894,13 +903,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="4" pivot="0" name="Cedis-style">
+    <tableStyle count="4" pivot="0" name="Plantas-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="4" pivot="0" name="Plantas-style">
+    <tableStyle count="4" pivot="0" name="Cedis-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -923,7 +932,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J188" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J190" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -941,7 +950,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J112" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J113" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1210,14 +1219,14 @@
       <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="9">
         <v>359100.0</v>
@@ -1237,16 +1246,16 @@
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D3" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="9">
         <v>298282.0</v>
@@ -1260,7 +1269,7 @@
       <c r="I3" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
       <c r="A4" s="5">
@@ -1269,7 +1278,7 @@
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="9">
@@ -1290,23 +1299,23 @@
       <c r="I4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="7"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
       <c r="A5" s="5">
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="8" t="s">
         <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D5" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="9">
         <v>75680.0</v>
@@ -1318,10 +1327,10 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -1331,14 +1340,14 @@
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="9">
         <v>189540.0</v>
@@ -1353,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -1363,14 +1372,14 @@
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -1382,10 +1391,10 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -1395,14 +1404,14 @@
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="9">
         <v>152384.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" s="9">
         <v>14700.0</v>
@@ -1414,7 +1423,7 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J8" s="12"/>
     </row>
@@ -1423,16 +1432,16 @@
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="9">
         <v>228240.0</v>
@@ -1444,7 +1453,7 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J9" s="12"/>
     </row>
@@ -1453,16 +1462,16 @@
         <v>46206.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="D10" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1485,14 +1494,14 @@
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="9">
         <v>31680.0</v>
@@ -1504,10 +1513,10 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
@@ -1515,16 +1524,16 @@
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D12" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>51387.0</v>
@@ -1536,7 +1545,7 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>57</v>
@@ -1547,16 +1556,16 @@
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D13" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="9">
         <v>195810.0</v>
@@ -1568,7 +1577,7 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>57</v>
@@ -1579,16 +1588,16 @@
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="8" t="s">
         <v>30</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="9">
         <v>526002.0</v>
@@ -1603,7 +1612,7 @@
         <v>23</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -1613,14 +1622,14 @@
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>59</v>
+      <c r="C15" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1635,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -1643,16 +1652,16 @@
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16" s="9">
         <v>149040.0</v>
@@ -1673,10 +1682,10 @@
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
@@ -1703,16 +1712,16 @@
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18" s="9">
         <v>222021.0</v>
@@ -1733,16 +1742,16 @@
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="8" t="s">
         <v>30</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="D19" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="9">
         <v>495833.0</v>
@@ -1757,7 +1766,7 @@
         <v>16</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -1765,16 +1774,16 @@
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D20" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="9">
         <v>139920.0</v>
@@ -1795,16 +1804,16 @@
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" s="9">
         <v>162125.0</v>
@@ -1819,7 +1828,7 @@
         <v>16</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -1829,14 +1838,14 @@
       <c r="B22" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="9">
         <v>152384.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F22" s="9">
         <v>32850.0</v>
@@ -1848,7 +1857,7 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J22" s="12"/>
     </row>
@@ -1859,14 +1868,14 @@
       <c r="B23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>59</v>
+      <c r="C23" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D23" s="9">
         <v>112271.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F23" s="9">
         <v>16500.0</v>
@@ -1878,7 +1887,7 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J23" s="12"/>
     </row>
@@ -1887,16 +1896,16 @@
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="9">
         <v>190047.0</v>
@@ -1908,7 +1917,7 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J24" s="12"/>
     </row>
@@ -1920,13 +1929,13 @@
         <v>25</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D25" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" s="9">
         <v>178080.0</v>
@@ -1938,7 +1947,7 @@
         <v>203520.0</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J25" s="12"/>
     </row>
@@ -1950,13 +1959,13 @@
         <v>25</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D26" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9">
         <v>10320.0</v>
@@ -1968,10 +1977,10 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
@@ -1982,13 +1991,13 @@
         <v>25</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D27" s="9">
         <v>112271.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F27" s="9">
         <v>18000.0</v>
@@ -2012,13 +2021,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" s="9">
         <v>208440.0</v>
@@ -2033,7 +2042,7 @@
         <v>16</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
@@ -2044,13 +2053,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="9">
         <v>962820.0</v>
@@ -2065,7 +2074,7 @@
         <v>16</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
@@ -2076,13 +2085,13 @@
         <v>25</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D30" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="9">
         <v>335340.0</v>
@@ -2094,10 +2103,10 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
@@ -2105,16 +2114,16 @@
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D31" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" s="9">
         <v>316800.0</v>
@@ -2135,16 +2144,16 @@
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F32" s="9">
         <v>176850.0</v>
@@ -2156,7 +2165,7 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J32" s="12"/>
     </row>
@@ -2165,16 +2174,16 @@
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D33" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="9">
         <v>58080.0</v>
@@ -2195,16 +2204,16 @@
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="D34" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F34" s="9">
         <v>481440.0</v>
@@ -2227,14 +2236,14 @@
       <c r="B35" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D35" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F35" s="9">
         <v>355720.0</v>
@@ -2258,13 +2267,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D36" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -2279,24 +2288,24 @@
         <v>22</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="17">
+      <c r="A37" s="19">
         <v>46218.0</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D37" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F37" s="9">
         <v>272073.0</v>
@@ -2308,27 +2317,27 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="17">
+      <c r="A38" s="19">
         <v>46218.0</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D38" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -2343,24 +2352,24 @@
         <v>22</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="17">
+      <c r="A39" s="19">
         <v>46218.0</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D39" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F39" s="9">
         <v>20640.0</v>
@@ -2372,27 +2381,27 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="17">
+      <c r="A40" s="19">
         <v>46218.0</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -2422,7 +2431,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" s="9">
         <v>130320.0</v>
@@ -2434,10 +2443,10 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
@@ -2445,16 +2454,16 @@
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D42" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2475,16 +2484,16 @@
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F43" s="9">
         <v>152833.0</v>
@@ -2496,10 +2505,10 @@
         <v>96472.0</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
@@ -2507,16 +2516,16 @@
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D44" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F44" s="9">
         <v>237828.0</v>
@@ -2540,13 +2549,13 @@
         <v>10</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D45" s="9">
         <v>152384.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F45" s="9">
         <v>31125.0</v>
@@ -2558,10 +2567,10 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -2572,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D46" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2593,7 +2602,7 @@
         <v>22</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
@@ -2604,13 +2613,13 @@
         <v>10</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D47" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F47" s="9">
         <v>261166.0</v>
@@ -2622,10 +2631,10 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
@@ -2636,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D48" s="9">
         <v>2110217.0</v>
@@ -2663,16 +2672,16 @@
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="D49" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" s="9">
         <v>398570.0</v>
@@ -2684,10 +2693,10 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
@@ -2695,16 +2704,16 @@
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D50" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F50" s="9">
         <v>745107.0</v>
@@ -2719,7 +2728,7 @@
         <v>16</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
@@ -2729,14 +2738,14 @@
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>59</v>
+      <c r="C51" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D51" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F51" s="9">
         <v>130560.0</v>
@@ -2751,7 +2760,7 @@
         <v>23</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
@@ -2759,16 +2768,16 @@
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F52" s="9">
         <v>87447.0</v>
@@ -2792,13 +2801,13 @@
         <v>10</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="9">
         <v>25200.0</v>
@@ -2813,7 +2822,7 @@
         <v>22</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
@@ -2821,16 +2830,16 @@
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="D54" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="9">
         <v>285405.0</v>
@@ -2842,10 +2851,10 @@
         <v>226069.0</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
@@ -2855,14 +2864,14 @@
       <c r="B55" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>59</v>
+      <c r="C55" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D55" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F55" s="9">
         <v>692280.0</v>
@@ -2874,7 +2883,7 @@
         <v>700200.0</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J55" s="12"/>
     </row>
@@ -2885,14 +2894,14 @@
       <c r="B56" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>59</v>
+      <c r="C56" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D56" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F56" s="9">
         <v>700200.0</v>
@@ -2913,16 +2922,16 @@
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="D57" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="9">
         <v>226069.0</v>
@@ -2934,10 +2943,10 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
@@ -2945,16 +2954,16 @@
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F58" s="9">
         <v>144637.0</v>
@@ -2966,7 +2975,7 @@
         <v>128160.0</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J58" s="12"/>
     </row>
@@ -2975,16 +2984,16 @@
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="9">
         <v>295359.0</v>
@@ -2999,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
@@ -3007,16 +3016,16 @@
         <v>46230.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D60" s="9">
         <v>2110403.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F60" s="9">
         <v>9960.0</v>
@@ -3040,13 +3049,13 @@
         <v>10</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D61" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F61" s="9">
         <v>306720.0</v>
@@ -3069,14 +3078,14 @@
       <c r="B62" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D62" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F62" s="9">
         <v>437080.0</v>
@@ -3088,10 +3097,10 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
@@ -3099,16 +3108,16 @@
         <v>46231.0</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D63" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" s="9">
         <v>165466.0</v>
@@ -3120,10 +3129,10 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
@@ -3131,16 +3140,16 @@
         <v>46231.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D64" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F64" s="9">
         <v>238497.0</v>
@@ -3152,10 +3161,10 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
@@ -3163,16 +3172,16 @@
         <v>46231.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D65" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F65" s="9">
         <v>8190.0</v>
@@ -3184,10 +3193,10 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
@@ -3195,16 +3204,16 @@
         <v>46231.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D66" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F66" s="9">
         <v>146224.0</v>
@@ -3216,10 +3225,10 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
@@ -3227,14 +3236,14 @@
         <v>46232.0</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C67" s="20"/>
+        <v>127</v>
+      </c>
+      <c r="C67" s="21"/>
       <c r="D67" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F67" s="9">
         <v>14599.0</v>
@@ -3257,12 +3266,12 @@
       <c r="B68" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C68" s="20"/>
+      <c r="C68" s="21"/>
       <c r="D68" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="9">
         <v>22080.0</v>
@@ -3283,14 +3292,14 @@
         <v>46232.0</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="20"/>
+        <v>30</v>
+      </c>
+      <c r="C69" s="21"/>
       <c r="D69" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" s="9">
         <v>353905.0</v>
@@ -3311,14 +3320,14 @@
         <v>46232.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" s="20"/>
+        <v>49</v>
+      </c>
+      <c r="C70" s="21"/>
       <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F70" s="9">
         <v>5913.0</v>
@@ -3341,12 +3350,12 @@
       <c r="B71" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="20"/>
+      <c r="C71" s="21"/>
       <c r="D71" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F71" s="9">
         <v>256613.0</v>
@@ -3369,12 +3378,12 @@
       <c r="B72" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C72" s="20"/>
+      <c r="C72" s="21"/>
       <c r="D72" s="9">
         <v>152384.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F72" s="9">
         <v>21300.0</v>
@@ -3395,14 +3404,14 @@
         <v>46232.0</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C73" s="20"/>
+        <v>96</v>
+      </c>
+      <c r="C73" s="21"/>
       <c r="D73" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" s="9">
         <v>351733.0</v>
@@ -3419,20 +3428,20 @@
       <c r="J73" s="12"/>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="17">
+      <c r="A74" s="19">
         <v>46233.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D74" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F74" s="9">
         <v>158761.0</v>
@@ -3444,27 +3453,27 @@
         <v>183014.0</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J74" s="12" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="17">
+      <c r="A75" s="19">
         <v>46233.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D75" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F75" s="9">
         <v>117430.0</v>
@@ -3487,14 +3496,14 @@
       <c r="B76" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>77</v>
+      <c r="C76" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D76" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F76" s="9">
         <v>265693.0</v>
@@ -3515,16 +3524,16 @@
         <v>46234.0</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" s="8" t="s">
         <v>133</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D77" s="9">
         <v>112357.0</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F77" s="9">
         <v>720.0</v>
@@ -3539,7 +3548,7 @@
         <v>16</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
@@ -3547,16 +3556,16 @@
         <v>46234.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D78" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F78" s="9">
         <v>5580.0</v>
@@ -3568,27 +3577,27 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>46237.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D79" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F79" s="9">
         <v>192903.0</v>
@@ -3600,27 +3609,27 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>46237.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D80" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F80" s="9">
         <v>152062.0</v>
@@ -3632,27 +3641,27 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>46237.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>138</v>
+        <v>52</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="D81" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F81" s="9">
         <v>153692.0</v>
@@ -3664,27 +3673,27 @@
         <v>63920.0</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>46237.0</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="8" t="s">
-        <v>140</v>
+      <c r="C82" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="D82" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" s="9">
         <v>45564.0</v>
@@ -3701,20 +3710,20 @@
       <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
-      <c r="A83" s="19">
+      <c r="A83" s="18">
         <v>46237.0</v>
       </c>
       <c r="B83" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D83" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F83" s="9">
         <v>93517.0</v>
@@ -3726,10 +3735,10 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
@@ -3739,14 +3748,14 @@
       <c r="B84" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>77</v>
+      <c r="C84" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D84" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F84" s="9">
         <v>43200.0</v>
@@ -3769,14 +3778,14 @@
       <c r="B85" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>77</v>
+      <c r="C85" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D85" s="9">
         <v>152384.0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F85" s="9">
         <v>25350.0</v>
@@ -3788,7 +3797,7 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J85" s="12"/>
     </row>
@@ -3799,14 +3808,14 @@
       <c r="B86" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C86" s="8" t="s">
-        <v>77</v>
+      <c r="C86" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F86" s="9">
         <v>5040.0</v>
@@ -3827,16 +3836,16 @@
         <v>46238.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D87" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F87" s="9">
         <v>124423.0</v>
@@ -3848,7 +3857,7 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>144</v>
@@ -3861,14 +3870,14 @@
       <c r="B88" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>77</v>
+      <c r="C88" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D88" s="9">
         <v>152384.0</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F88" s="9">
         <v>30750.0</v>
@@ -3891,14 +3900,14 @@
       <c r="B89" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D89" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F89" s="9">
         <v>58320.0</v>
@@ -3910,27 +3919,27 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J89" s="12" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
-      <c r="A90" s="19">
+      <c r="A90" s="18">
         <v>46240.0</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D90" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F90" s="9">
         <v>254880.0</v>
@@ -3949,20 +3958,20 @@
       </c>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
-      <c r="A91" s="19">
+      <c r="A91" s="18">
         <v>46240.0</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>149</v>
+        <v>30</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="D91" s="9">
         <v>112379.0</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F91" s="9">
         <v>13800.0</v>
@@ -3974,25 +3983,25 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
-      <c r="A92" s="19">
+      <c r="A92" s="18">
         <v>46240.0</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C92" s="8" t="s">
         <v>133</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F92" s="9">
         <v>4575.0</v>
@@ -4007,7 +4016,7 @@
         <v>16</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
@@ -4017,14 +4026,14 @@
       <c r="B93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D93" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F93" s="9">
         <v>222000.0</v>
@@ -4036,10 +4045,10 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
@@ -4049,14 +4058,14 @@
       <c r="B94" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D94" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F94" s="9">
         <v>300060.0</v>
@@ -4068,10 +4077,10 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
@@ -4081,14 +4090,14 @@
       <c r="B95" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D95" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F95" s="9">
         <v>36240.0</v>
@@ -4100,10 +4109,10 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
@@ -4113,14 +4122,14 @@
       <c r="B96" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>77</v>
+      <c r="C96" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D96" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F96" s="9">
         <v>21690.0</v>
@@ -4143,14 +4152,14 @@
       <c r="B97" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D97" s="9">
         <v>112271.0</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F97" s="9">
         <v>20100.0</v>
@@ -4173,14 +4182,14 @@
       <c r="B98" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D98" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F98" s="9">
         <v>39840.0</v>
@@ -4192,7 +4201,7 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J98" s="12" t="s">
         <v>154</v>
@@ -4205,14 +4214,14 @@
       <c r="B99" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D99" s="9">
         <v>152384.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F99" s="9">
         <v>18600.0</v>
@@ -4224,7 +4233,7 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J99" s="12" t="s">
         <v>155</v>
@@ -4237,14 +4246,14 @@
       <c r="B100" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>77</v>
+      <c r="C100" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D100" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F100" s="9">
         <v>225620.0</v>
@@ -4259,7 +4268,7 @@
         <v>16</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
@@ -4267,16 +4276,16 @@
         <v>46246.0</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C101" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D101" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F101" s="9">
         <v>423758.0</v>
@@ -4301,14 +4310,14 @@
       <c r="B102" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>77</v>
+      <c r="C102" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D102" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F102" s="9">
         <v>800120.0</v>
@@ -4333,14 +4342,14 @@
       <c r="B103" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="8" t="s">
-        <v>77</v>
+      <c r="C103" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D103" s="9">
         <v>112271.0</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F103" s="9">
         <v>10815.0</v>
@@ -4355,7 +4364,7 @@
         <v>22</v>
       </c>
       <c r="J103" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
@@ -4365,14 +4374,14 @@
       <c r="B104" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D104" s="9">
         <v>152384.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F104" s="9">
         <v>12900.0</v>
@@ -4384,10 +4393,10 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J104" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
@@ -4395,7 +4404,7 @@
         <v>46247.0</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>164</v>
@@ -4404,7 +4413,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F105" s="9">
         <v>193026.0</v>
@@ -4429,14 +4438,14 @@
       <c r="B106" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D106" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F106" s="9">
         <v>245520.0</v>
@@ -4448,7 +4457,7 @@
         <v>230580.0</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J106" s="12"/>
     </row>
@@ -4459,7 +4468,7 @@
       <c r="B107" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D107" s="9">
@@ -4489,14 +4498,14 @@
       <c r="B108" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D108" s="9">
         <v>112271.0</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F108" s="9">
         <v>16500.0</v>
@@ -4508,7 +4517,7 @@
         <v>12600.0</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J108" s="12"/>
     </row>
@@ -4519,14 +4528,14 @@
       <c r="B109" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>77</v>
+      <c r="C109" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D109" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F109" s="9">
         <v>793976.0</v>
@@ -4551,14 +4560,14 @@
       <c r="B110" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D110" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F110" s="9">
         <v>289920.0</v>
@@ -4581,14 +4590,14 @@
       <c r="B111" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D111" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F111" s="9">
         <v>230580.0</v>
@@ -4600,7 +4609,7 @@
         <v>298620.0</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>167</v>
@@ -4613,14 +4622,14 @@
       <c r="B112" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D112" s="9">
         <v>152384.0</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F112" s="9">
         <v>13200.0</v>
@@ -4632,7 +4641,7 @@
         <v>7200.0</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>168</v>
@@ -4643,16 +4652,16 @@
         <v>46248.0</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C113" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>169</v>
       </c>
       <c r="D113" s="9">
         <v>152384.0</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F113" s="9">
         <v>9900.0</v>
@@ -4677,14 +4686,14 @@
       <c r="B114" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>59</v>
+      <c r="C114" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D114" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F114" s="9">
         <v>184290.0</v>
@@ -4696,7 +4705,7 @@
         <v>68640.0</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J114" s="12" t="s">
         <v>171</v>
@@ -4709,14 +4718,14 @@
       <c r="B115" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>59</v>
+      <c r="C115" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D115" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F115" s="9">
         <v>26880.0</v>
@@ -4728,7 +4737,7 @@
         <v>26880.0</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J115" s="12" t="s">
         <v>172</v>
@@ -4741,14 +4750,14 @@
       <c r="B116" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>77</v>
+      <c r="C116" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D116" s="9">
         <v>152384.0</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F116" s="9">
         <v>21585.0</v>
@@ -4773,14 +4782,14 @@
       <c r="B117" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C117" s="8" t="s">
-        <v>59</v>
+      <c r="C117" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D117" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F117" s="9">
         <v>179640.0</v>
@@ -4803,14 +4812,14 @@
       <c r="B118" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>59</v>
+      <c r="C118" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D118" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" s="9">
         <v>26880.0</v>
@@ -4833,14 +4842,14 @@
       <c r="B119" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>59</v>
+      <c r="C119" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D119" s="9">
         <v>152384.0</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F119" s="9">
         <v>14230.0</v>
@@ -4861,16 +4870,16 @@
         <v>46253.0</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="D120" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F120" s="9">
         <v>26677.0</v>
@@ -4895,14 +4904,14 @@
       <c r="B121" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>77</v>
+      <c r="C121" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D121" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F121" s="9">
         <v>22500.0</v>
@@ -4914,7 +4923,7 @@
         <v>18300.0</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J121" s="12" t="s">
         <v>175</v>
@@ -4927,14 +4936,14 @@
       <c r="B122" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>77</v>
+      <c r="C122" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D122" s="9">
         <v>112271.0</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F122" s="9">
         <v>16500.0</v>
@@ -4957,16 +4966,16 @@
         <v>46254.0</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C123" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C123" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D123" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F123" s="9">
         <v>21915.0</v>
@@ -4989,16 +4998,16 @@
         <v>46254.0</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D124" s="9">
         <v>2112207.0</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F124" s="9">
         <v>10125.0</v>
@@ -5019,16 +5028,16 @@
         <v>46254.0</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C125" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C125" s="7" t="s">
         <v>177</v>
       </c>
       <c r="D125" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F125" s="9">
         <v>6380.0</v>
@@ -5053,14 +5062,14 @@
       <c r="B126" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>77</v>
+      <c r="C126" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D126" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F126" s="9">
         <v>28200.0</v>
@@ -5083,14 +5092,14 @@
       <c r="B127" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="7" t="s">
         <v>179</v>
       </c>
       <c r="D127" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F127" s="9">
         <v>23760.0</v>
@@ -5102,7 +5111,7 @@
         <v>17760.0</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J127" s="12" t="s">
         <v>180</v>
@@ -5113,16 +5122,16 @@
         <v>46255.0</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C128" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C128" s="7" t="s">
         <v>181</v>
       </c>
       <c r="D128" s="9">
         <v>112268.0</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F128" s="9">
         <v>3300.0</v>
@@ -5147,14 +5156,14 @@
       <c r="B129" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="7" t="s">
         <v>184</v>
       </c>
       <c r="D129" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F129" s="9">
         <v>2130.0</v>
@@ -5173,20 +5182,20 @@
       </c>
     </row>
     <row r="130" ht="22.5" hidden="1" customHeight="1">
-      <c r="A130" s="19">
+      <c r="A130" s="18">
         <v>46258.0</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D130" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F130" s="9">
         <v>341120.0</v>
@@ -5205,20 +5214,20 @@
       </c>
     </row>
     <row r="131" ht="22.5" hidden="1" customHeight="1">
-      <c r="A131" s="19">
+      <c r="A131" s="18">
         <v>46258.0</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D131" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F131" s="9">
         <v>11520.0</v>
@@ -5235,20 +5244,20 @@
       <c r="J131" s="12"/>
     </row>
     <row r="132" ht="22.5" hidden="1" customHeight="1">
-      <c r="A132" s="19">
+      <c r="A132" s="18">
         <v>46258.0</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D132" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F132" s="9">
         <v>35520.0</v>
@@ -5271,16 +5280,16 @@
         <v>46259.0</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D133" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F133" s="9">
         <v>64620.0</v>
@@ -5292,7 +5301,7 @@
         <v>47685.0</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J133" s="12"/>
     </row>
@@ -5303,14 +5312,14 @@
       <c r="B134" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D134" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F134" s="9">
         <v>18000.0</v>
@@ -5333,16 +5342,16 @@
         <v>46259.0</v>
       </c>
       <c r="B135" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="D135" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F135" s="9">
         <v>48540.0</v>
@@ -5354,7 +5363,7 @@
         <v>105048.0</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J135" s="12" t="s">
         <v>189</v>
@@ -5367,14 +5376,14 @@
       <c r="B136" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D136" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F136" s="9">
         <v>194198.0</v>
@@ -5386,7 +5395,7 @@
         <v>140840.0</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J136" s="12" t="s">
         <v>190</v>
@@ -5399,14 +5408,14 @@
       <c r="B137" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D137" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F137" s="9">
         <v>11510.0</v>
@@ -5429,16 +5438,16 @@
         <v>46260.0</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D138" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F138" s="9">
         <v>47685.0</v>
@@ -5463,14 +5472,14 @@
       <c r="B139" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D139" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F139" s="9">
         <v>30600.0</v>
@@ -5489,20 +5498,20 @@
       </c>
     </row>
     <row r="140" ht="22.5" hidden="1" customHeight="1">
-      <c r="A140" s="19">
+      <c r="A140" s="18">
         <v>46261.0</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="7" t="s">
         <v>194</v>
       </c>
       <c r="D140" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F140" s="9">
         <v>38640.0</v>
@@ -5519,20 +5528,20 @@
       <c r="J140" s="12"/>
     </row>
     <row r="141" ht="22.5" hidden="1" customHeight="1">
-      <c r="A141" s="19">
+      <c r="A141" s="18">
         <v>46261.0</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C141" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C141" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D141" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F141" s="9">
         <v>365280.0</v>
@@ -5549,20 +5558,20 @@
       <c r="J141" s="12"/>
     </row>
     <row r="142" ht="22.5" hidden="1" customHeight="1">
-      <c r="A142" s="19">
+      <c r="A142" s="18">
         <v>46261.0</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D142" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F142" s="9">
         <v>192000.0</v>
@@ -5579,20 +5588,20 @@
       <c r="J142" s="12"/>
     </row>
     <row r="143" ht="22.5" hidden="1" customHeight="1">
-      <c r="A143" s="19">
+      <c r="A143" s="18">
         <v>46261.0</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D143" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F143" s="9">
         <v>10260.0</v>
@@ -5609,20 +5618,20 @@
       <c r="J143" s="12"/>
     </row>
     <row r="144" ht="22.5" hidden="1" customHeight="1">
-      <c r="A144" s="19">
+      <c r="A144" s="18">
         <v>46262.0</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D144" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F144" s="9">
         <v>10500.0</v>
@@ -5639,20 +5648,20 @@
       <c r="J144" s="12"/>
     </row>
     <row r="145" ht="22.5" hidden="1" customHeight="1">
-      <c r="A145" s="19">
+      <c r="A145" s="18">
         <v>46262.0</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="7" t="s">
         <v>197</v>
       </c>
       <c r="D145" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F145" s="9">
         <v>91680.0</v>
@@ -5664,7 +5673,7 @@
         <v>84480.0</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J145" s="12" t="s">
         <v>198</v>
@@ -5675,16 +5684,16 @@
         <v>46265.0</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C146" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C146" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D146" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F146" s="9">
         <v>17970.0</v>
@@ -5705,16 +5714,16 @@
         <v>46265.0</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D147" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F147" s="9">
         <v>9960.0</v>
@@ -5735,16 +5744,16 @@
         <v>46265.0</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C148" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C148" s="7" t="s">
         <v>199</v>
       </c>
       <c r="D148" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F148" s="9">
         <v>10503.0</v>
@@ -5769,14 +5778,14 @@
       <c r="B149" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>77</v>
+      <c r="C149" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D149" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F149" s="9">
         <v>339300.0</v>
@@ -5788,7 +5797,7 @@
         <v>349380.0</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>201</v>
@@ -5801,14 +5810,14 @@
       <c r="B150" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="7" t="s">
         <v>202</v>
       </c>
       <c r="D150" s="9">
         <v>152384.0</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F150" s="9">
         <v>17100.0</v>
@@ -5820,7 +5829,7 @@
         <v>8700.0</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J150" s="12"/>
     </row>
@@ -5829,16 +5838,16 @@
         <v>46266.0</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C151" s="8" t="s">
         <v>133</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D151" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F151" s="9">
         <v>3240.0</v>
@@ -5863,14 +5872,14 @@
       <c r="B152" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C152" s="8" t="s">
-        <v>77</v>
+      <c r="C152" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D152" s="9">
         <v>152384.0</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F152" s="9">
         <v>25350.0</v>
@@ -5893,16 +5902,16 @@
         <v>46267.0</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D153" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F153" s="9">
         <v>15660.0</v>
@@ -5914,7 +5923,7 @@
         <v>2520.0</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J153" s="12" t="s">
         <v>205</v>
@@ -5925,16 +5934,16 @@
         <v>46267.0</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="D154" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F154" s="9">
         <v>8280.0</v>
@@ -5946,7 +5955,7 @@
         <v>3375.0</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>206</v>
@@ -5959,14 +5968,14 @@
       <c r="B155" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D155" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F155" s="9">
         <v>205020.0</v>
@@ -5978,7 +5987,7 @@
         <v>106200.0</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>208</v>
@@ -5991,14 +6000,14 @@
       <c r="B156" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D156" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F156" s="9">
         <v>7920.0</v>
@@ -6010,7 +6019,7 @@
         <v>9720.0</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J156" s="12" t="s">
         <v>209</v>
@@ -6023,14 +6032,14 @@
       <c r="B157" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="7" t="s">
         <v>207</v>
       </c>
       <c r="D157" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F157" s="9">
         <v>18240.0</v>
@@ -6042,7 +6051,7 @@
         <v>12240.0</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>210</v>
@@ -6055,14 +6064,14 @@
       <c r="B158" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C158" s="8" t="s">
-        <v>77</v>
+      <c r="C158" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D158" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F158" s="9">
         <v>287280.0</v>
@@ -6085,16 +6094,16 @@
         <v>46269.0</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D159" s="9">
         <v>2112207.0</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F159" s="9">
         <v>6435.0</v>
@@ -6115,16 +6124,16 @@
         <v>46269.0</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C160" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C160" s="7" t="s">
         <v>212</v>
       </c>
       <c r="D160" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F160" s="9">
         <v>440230.0</v>
@@ -6136,7 +6145,7 @@
         <v>300589.0</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J160" s="12" t="s">
         <v>213</v>
@@ -6147,16 +6156,16 @@
         <v>46269.0</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C161" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C161" s="7" t="s">
         <v>212</v>
       </c>
       <c r="D161" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F161" s="9">
         <v>8457.0</v>
@@ -6168,7 +6177,7 @@
         <v>8097.0</v>
       </c>
       <c r="I161" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J161" s="12" t="s">
         <v>213</v>
@@ -6179,16 +6188,16 @@
         <v>46272.0</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="D162" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F162" s="9">
         <v>96984.0</v>
@@ -6200,7 +6209,7 @@
         <v>40143.0</v>
       </c>
       <c r="I162" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J162" s="12" t="s">
         <v>214</v>
@@ -6213,14 +6222,14 @@
       <c r="B163" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>77</v>
+      <c r="C163" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D163" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F163" s="9">
         <v>345572.0</v>
@@ -6232,7 +6241,7 @@
         <v>444960.0</v>
       </c>
       <c r="I163" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>215</v>
@@ -6245,14 +6254,14 @@
       <c r="B164" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C164" s="8" t="s">
-        <v>77</v>
+      <c r="C164" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D164" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F164" s="9">
         <v>21960.0</v>
@@ -6264,7 +6273,7 @@
         <v>18330.0</v>
       </c>
       <c r="I164" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>215</v>
@@ -6277,14 +6286,14 @@
       <c r="B165" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D165" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F165" s="9">
         <v>35040.0</v>
@@ -6296,7 +6305,7 @@
         <v>21840.0</v>
       </c>
       <c r="I165" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>216</v>
@@ -6309,14 +6318,14 @@
       <c r="B166" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D166" s="9">
         <v>112271.0</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F166" s="9">
         <v>13200.0</v>
@@ -6339,14 +6348,14 @@
       <c r="B167" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D167" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F167" s="9">
         <v>10620.0</v>
@@ -6358,7 +6367,7 @@
         <v>8460.0</v>
       </c>
       <c r="I167" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>217</v>
@@ -6371,14 +6380,14 @@
       <c r="B168" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D168" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F168" s="9">
         <v>239040.0</v>
@@ -6390,7 +6399,7 @@
         <v>123360.0</v>
       </c>
       <c r="I168" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>217</v>
@@ -6403,14 +6412,14 @@
       <c r="B169" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C169" s="8" t="s">
-        <v>59</v>
+      <c r="C169" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D169" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F169" s="9">
         <v>123360.0</v>
@@ -6435,14 +6444,14 @@
       <c r="B170" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C170" s="8" t="s">
-        <v>59</v>
+      <c r="C170" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D170" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F170" s="9">
         <v>8460.0</v>
@@ -6465,14 +6474,14 @@
       <c r="B171" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C171" s="8" t="s">
-        <v>77</v>
+      <c r="C171" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D171" s="9">
         <v>112271.0</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F171" s="9">
         <v>9900.0</v>
@@ -6497,14 +6506,14 @@
       <c r="B172" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C172" s="8" t="s">
-        <v>77</v>
+      <c r="C172" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D172" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F172" s="9">
         <v>18330.0</v>
@@ -6523,20 +6532,20 @@
       </c>
     </row>
     <row r="173" ht="22.5" hidden="1" customHeight="1">
-      <c r="A173" s="19">
+      <c r="A173" s="18">
         <v>46275.0</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C173" s="8" t="s">
-        <v>77</v>
+      <c r="C173" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D173" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F173" s="9">
         <v>340260.0</v>
@@ -6555,20 +6564,20 @@
       </c>
     </row>
     <row r="174" ht="22.5" hidden="1" customHeight="1">
-      <c r="A174" s="19">
+      <c r="A174" s="18">
         <v>46275.0</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C174" s="8" t="s">
-        <v>77</v>
+      <c r="C174" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D174" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F174" s="9">
         <v>52453.0</v>
@@ -6587,20 +6596,20 @@
       </c>
     </row>
     <row r="175" ht="22.5" hidden="1" customHeight="1">
-      <c r="A175" s="19">
+      <c r="A175" s="18">
         <v>46275.0</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C175" s="8" t="s">
-        <v>77</v>
+      <c r="C175" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D175" s="9">
         <v>152384.0</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F175" s="9">
         <v>18585.0</v>
@@ -6619,7 +6628,7 @@
       </c>
     </row>
     <row r="176" ht="22.5" hidden="1" customHeight="1">
-      <c r="A176" s="19">
+      <c r="A176" s="18">
         <v>46275.0</v>
       </c>
       <c r="B176" s="6" t="s">
@@ -6632,7 +6641,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F176" s="9">
         <v>151680.0</v>
@@ -6644,14 +6653,14 @@
         <v>67680.0</v>
       </c>
       <c r="I176" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J176" s="12" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="177" ht="22.5" hidden="1" customHeight="1">
-      <c r="A177" s="19">
+      <c r="A177" s="18">
         <v>46275.0</v>
       </c>
       <c r="B177" s="6" t="s">
@@ -6664,7 +6673,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F177" s="9">
         <v>23520.0</v>
@@ -6687,16 +6696,16 @@
         <v>46276.0</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C178" s="8" t="s">
         <v>133</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="D178" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F178" s="9">
         <v>2130.0</v>
@@ -6717,16 +6726,16 @@
         <v>46276.0</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C179" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C179" s="7" t="s">
         <v>158</v>
       </c>
       <c r="D179" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F179" s="9">
         <v>456945.0</v>
@@ -6738,7 +6747,7 @@
         <v>627558.0</v>
       </c>
       <c r="I179" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J179" s="12" t="s">
         <v>225</v>
@@ -6749,16 +6758,16 @@
         <v>46280.0</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>106</v>
+        <v>30</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="D180" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F180" s="9">
         <v>653620.0</v>
@@ -6779,16 +6788,16 @@
         <v>46280.0</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C181" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C181" s="7" t="s">
         <v>195</v>
       </c>
       <c r="D181" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F181" s="9">
         <v>393840.0</v>
@@ -6811,14 +6820,14 @@
       <c r="B182" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C182" s="8" t="s">
-        <v>77</v>
+      <c r="C182" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D182" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F182" s="9">
         <v>13800.0</v>
@@ -6841,14 +6850,14 @@
       <c r="B183" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C183" s="8" t="s">
-        <v>59</v>
+      <c r="C183" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D183" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F183" s="9">
         <v>226980.0</v>
@@ -6860,25 +6869,27 @@
         <v>187100.0</v>
       </c>
       <c r="I183" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J183" s="12" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
-      <c r="A184" s="19">
+      <c r="A184" s="18">
         <v>46282.0</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C184" s="20"/>
+      <c r="C184" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="D184" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F184" s="9">
         <v>616880.0</v>
@@ -6889,24 +6900,28 @@
       <c r="H184" s="9">
         <v>515700.0</v>
       </c>
-      <c r="I184" s="13"/>
-      <c r="J184" s="12"/>
+      <c r="I184" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
-      <c r="A185" s="19">
+      <c r="A185" s="18">
         <v>46282.0</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="7" t="s">
         <v>184</v>
       </c>
       <c r="D185" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F185" s="9">
         <v>118254.0</v>
@@ -6918,25 +6933,27 @@
         <v>39054.0</v>
       </c>
       <c r="I185" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J185" s="12" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
-      <c r="A186" s="19">
+      <c r="A186" s="18">
         <v>46282.0</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C186" s="20"/>
+      <c r="C186" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="D186" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F186" s="9">
         <v>187100.0</v>
@@ -6947,22 +6964,28 @@
       <c r="H186" s="9">
         <v>294480.0</v>
       </c>
-      <c r="I186" s="13"/>
-      <c r="J186" s="12"/>
+      <c r="I186" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
-      <c r="A187" s="19">
+      <c r="A187" s="18">
         <v>46282.0</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C187" s="20"/>
+      <c r="C187" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="D187" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E187" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F187" s="9">
         <v>103200.0</v>
@@ -6973,24 +6996,28 @@
       <c r="H187" s="9">
         <v>40320.0</v>
       </c>
-      <c r="I187" s="13"/>
-      <c r="J187" s="12"/>
+      <c r="I187" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
-      <c r="A188" s="19">
+      <c r="A188" s="18">
         <v>46282.0</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C188" s="8" t="s">
-        <v>77</v>
+      <c r="C188" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D188" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F188" s="9">
         <v>16680.0</v>
@@ -7005,14 +7032,70 @@
         <v>22</v>
       </c>
       <c r="J188" s="12" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="I189" s="23"/>
-    </row>
-    <row r="190">
-      <c r="I190" s="23"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="A189" s="5">
+        <v>46283.0</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D189" s="9">
+        <v>112271.0</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F189" s="9">
+        <v>11400.0</v>
+      </c>
+      <c r="G189" s="9">
+        <v>5640.0</v>
+      </c>
+      <c r="H189" s="9">
+        <v>1800.0</v>
+      </c>
+      <c r="I189" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J189" s="12"/>
+    </row>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="A190" s="5">
+        <v>46283.0</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D190" s="9">
+        <v>2010102.0</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F190" s="9">
+        <v>13320.0</v>
+      </c>
+      <c r="G190" s="9">
+        <v>5139.0</v>
+      </c>
+      <c r="H190" s="9">
+        <v>14400.0</v>
+      </c>
+      <c r="I190" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="191">
       <c r="I191" s="23"/>
@@ -9467,13 +9550,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I188">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I190">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I189:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I191:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A188">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A190">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -9542,12 +9625,12 @@
       <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="8"/>
       <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="9">
         <v>333.0</v>
@@ -9570,9 +9653,9 @@
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="C3" s="8"/>
       <c r="D3" s="9">
         <v>2114158.0</v>
       </c>
@@ -9622,7 +9705,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
@@ -9637,7 +9720,7 @@
         <v>112379.0</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="9">
         <v>3000.0</v>
@@ -9652,7 +9735,7 @@
         <v>16</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
@@ -9660,14 +9743,14 @@
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
         <v>112268.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" s="9">
         <v>3000.0</v>
@@ -9682,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
@@ -9690,14 +9773,14 @@
         <v>46225.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
         <v>132357.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7" s="9">
         <v>1560.0</v>
@@ -9712,7 +9795,7 @@
         <v>16</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
@@ -9720,14 +9803,14 @@
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -9742,7 +9825,7 @@
         <v>16</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
@@ -9757,7 +9840,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="9">
         <v>3712.0</v>
@@ -9772,7 +9855,7 @@
         <v>16</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
@@ -9780,14 +9863,14 @@
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -9802,7 +9885,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
@@ -9810,14 +9893,14 @@
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
         <v>112268.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F11" s="9">
         <v>3300.0</v>
@@ -9838,14 +9921,14 @@
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
         <v>112379.0</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>4200.0</v>
@@ -9866,14 +9949,14 @@
         <v>46226.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="9">
         <v>379471.0</v>
@@ -9888,7 +9971,7 @@
         <v>16</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
@@ -9896,14 +9979,14 @@
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="9">
         <v>72001.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F14" s="9">
         <v>21905.0</v>
@@ -9918,7 +10001,7 @@
         <v>16</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
@@ -9926,14 +10009,14 @@
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="9">
         <v>2110327.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F15" s="9">
         <v>69120.0</v>
@@ -9948,7 +10031,7 @@
         <v>16</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
@@ -9956,14 +10039,14 @@
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="9">
         <v>112379.0</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F16" s="9">
         <v>3900.0</v>
@@ -9984,14 +10067,14 @@
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -10012,14 +10095,14 @@
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="9">
         <v>112268.0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F18" s="9">
         <v>3300.0</v>
@@ -10034,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
@@ -10042,14 +10125,14 @@
         <v>46230.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F19" s="9">
         <v>136538.0</v>
@@ -10064,7 +10147,7 @@
         <v>16</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
@@ -10072,14 +10155,14 @@
         <v>46231.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="9">
         <v>591750.0</v>
@@ -10094,7 +10177,7 @@
         <v>16</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
@@ -10102,14 +10185,14 @@
         <v>46231.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="9">
         <v>10601.0</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F21" s="9">
         <v>1230.0</v>
@@ -10124,7 +10207,7 @@
         <v>16</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
@@ -10132,14 +10215,14 @@
         <v>46231.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F22" s="9">
         <v>4320.0</v>
@@ -10160,14 +10243,14 @@
         <v>46231.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="9">
         <v>114357.0</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9">
         <v>240.0</v>
@@ -10188,7 +10271,7 @@
         <v>46232.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="9">
@@ -10216,14 +10299,14 @@
         <v>46232.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
         <v>112268.0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F25" s="9">
         <v>5700.0</v>
@@ -10244,14 +10327,14 @@
         <v>46232.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F26" s="9">
         <v>720.0</v>
@@ -10272,14 +10355,14 @@
         <v>46232.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
         <v>2114357.0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F27" s="9">
         <v>432.0</v>
@@ -10328,14 +10411,14 @@
         <v>46233.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
         <v>112268.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F29" s="9">
         <v>5100.0</v>
@@ -10347,7 +10430,7 @@
         <v>4800.0</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J29" s="12"/>
     </row>
@@ -10356,14 +10439,14 @@
         <v>46233.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
         <v>114357.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F30" s="9">
         <v>240.0</v>
@@ -10375,7 +10458,7 @@
         <v>1560.0</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12"/>
     </row>
@@ -10384,14 +10467,14 @@
         <v>46233.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="9">
         <v>10601.0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F31" s="9">
         <v>7717.0</v>
@@ -10406,7 +10489,7 @@
         <v>16</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
@@ -10414,14 +10497,14 @@
         <v>46234.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="9">
         <v>79110.0</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F32" s="9">
         <v>48000.0</v>
@@ -10435,8 +10518,8 @@
       <c r="I32" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J32" s="18" t="s">
-        <v>89</v>
+      <c r="J32" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
@@ -10465,8 +10548,8 @@
       <c r="I33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="18" t="s">
-        <v>90</v>
+      <c r="J33" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
@@ -10474,14 +10557,14 @@
         <v>46234.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="9">
         <v>73001.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34" s="9">
         <v>73367.0</v>
@@ -10502,14 +10585,14 @@
         <v>46234.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="9">
         <v>112357.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F35" s="9">
         <v>840.0</v>
@@ -10526,18 +10609,18 @@
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="19">
+      <c r="A36" s="18">
         <v>46237.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="9">
         <v>10601.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" s="9">
         <v>17934.0</v>
@@ -10552,22 +10635,22 @@
         <v>16</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="22.5" hidden="1" customHeight="1">
-      <c r="A37" s="19">
+      <c r="A37" s="18">
         <v>46237.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F37" s="9">
         <v>194520.0</v>
@@ -10584,18 +10667,18 @@
       <c r="J37" s="12"/>
     </row>
     <row r="38" ht="22.5" hidden="1" customHeight="1">
-      <c r="A38" s="19">
+      <c r="A38" s="18">
         <v>46237.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="9">
         <v>114379.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F38" s="9">
         <v>52200.0</v>
@@ -10607,23 +10690,23 @@
         <v>7500.0</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J38" s="12"/>
     </row>
     <row r="39" ht="22.5" hidden="1" customHeight="1">
-      <c r="A39" s="19">
+      <c r="A39" s="18">
         <v>46237.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F39" s="9">
         <v>6450.0</v>
@@ -10640,18 +10723,18 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" ht="22.5" hidden="1" customHeight="1">
-      <c r="A40" s="19">
+      <c r="A40" s="18">
         <v>46237.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F40" s="9">
         <v>1398.0</v>
@@ -10672,14 +10755,14 @@
         <v>46238.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F41" s="9">
         <v>2460.0</v>
@@ -10700,14 +10783,14 @@
         <v>46238.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="9">
         <v>112268.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F42" s="9">
         <v>3600.0</v>
@@ -10728,14 +10811,14 @@
         <v>46238.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="9">
         <v>114379.0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F43" s="9">
         <v>7500.0</v>
@@ -10756,14 +10839,14 @@
         <v>46238.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
         <v>114357.0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F44" s="9">
         <v>240.0</v>
@@ -10784,14 +10867,14 @@
         <v>46239.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C45" s="14"/>
       <c r="D45" s="9">
         <v>10601.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F45" s="9">
         <v>1115.0</v>
@@ -10806,7 +10889,7 @@
         <v>16</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
@@ -10814,14 +10897,14 @@
         <v>46239.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F46" s="9">
         <v>114240.0</v>
@@ -10842,14 +10925,14 @@
         <v>46239.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
         <v>2112207.0</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F47" s="9">
         <v>1800.0</v>
@@ -10861,7 +10944,7 @@
         <v>1980.0</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J47" s="12"/>
     </row>
@@ -10870,14 +10953,14 @@
         <v>46239.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
         <v>112268.0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F48" s="9">
         <v>3900.0</v>
@@ -10889,7 +10972,7 @@
         <v>1200.0</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J48" s="12"/>
     </row>
@@ -10898,14 +10981,14 @@
         <v>46239.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
         <v>112357.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F49" s="9">
         <v>600.0</v>
@@ -10917,7 +11000,7 @@
         <v>600.0</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J49" s="12"/>
     </row>
@@ -10926,14 +11009,14 @@
         <v>46239.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
         <v>114268.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F50" s="9">
         <v>2700.0</v>
@@ -10945,7 +11028,7 @@
         <v>300.0</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J50" s="12"/>
     </row>
@@ -10954,7 +11037,7 @@
         <v>46239.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="9">
@@ -10976,7 +11059,7 @@
         <v>16</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
@@ -10984,14 +11067,14 @@
         <v>46239.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="9">
         <v>72003.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F52" s="9">
         <v>1391.0</v>
@@ -11012,14 +11095,14 @@
         <v>46239.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="9">
         <v>2974.0</v>
@@ -11034,22 +11117,22 @@
         <v>16</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="19">
+      <c r="A54" s="18">
         <v>46240.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="9">
         <v>112379.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F54" s="9">
         <v>3600.0</v>
@@ -11066,18 +11149,18 @@
       <c r="J54" s="12"/>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="19">
+      <c r="A55" s="18">
         <v>46240.0</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="9">
         <v>73001.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F55" s="9">
         <v>2415.0</v>
@@ -11094,18 +11177,18 @@
       <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="19">
+      <c r="A56" s="18">
         <v>46240.0</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="9">
         <v>112357.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F56" s="9">
         <v>600.0</v>
@@ -11122,18 +11205,18 @@
       <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="19">
+      <c r="A57" s="18">
         <v>46240.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="9">
         <v>114379.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F57" s="9">
         <v>2400.0</v>
@@ -11150,18 +11233,18 @@
       <c r="J57" s="12"/>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="19">
+      <c r="A58" s="18">
         <v>46244.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="9">
         <v>112379.0</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F58" s="9">
         <v>4800.0</v>
@@ -11182,14 +11265,14 @@
         <v>46245.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F59" s="9">
         <v>25574.0</v>
@@ -11210,14 +11293,14 @@
         <v>46246.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="9">
         <v>114379.0</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F60" s="9">
         <v>6900.0</v>
@@ -11245,7 +11328,7 @@
         <v>112379.0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F61" s="9">
         <v>20100.0</v>
@@ -11273,7 +11356,7 @@
         <v>112268.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F62" s="9">
         <v>8400.0</v>
@@ -11301,7 +11384,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F63" s="9">
         <v>61250.0</v>
@@ -11322,14 +11405,14 @@
         <v>46247.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
         <v>13358.0</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F64" s="9">
         <v>73728.0</v>
@@ -11344,7 +11427,7 @@
         <v>16</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" ht="19.5" hidden="1" customHeight="1">
@@ -11352,14 +11435,14 @@
         <v>46248.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C65" s="14"/>
       <c r="D65" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F65" s="9">
         <v>285596.0</v>
@@ -11371,10 +11454,10 @@
         <v>72480.0</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" ht="19.5" hidden="1" customHeight="1">
@@ -11382,14 +11465,14 @@
         <v>46248.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
         <v>73001.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F66" s="9">
         <v>31772.0</v>
@@ -11404,7 +11487,7 @@
         <v>16</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" ht="19.5" hidden="1" customHeight="1">
@@ -11419,7 +11502,7 @@
         <v>10601.0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F67" s="9">
         <v>73085.0</v>
@@ -11434,7 +11517,7 @@
         <v>16</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" ht="19.5" hidden="1" customHeight="1">
@@ -11449,7 +11532,7 @@
         <v>112379.0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F68" s="9">
         <v>18000.0</v>
@@ -11463,8 +11546,8 @@
       <c r="I68" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J68" s="21" t="s">
-        <v>126</v>
+      <c r="J68" s="20" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="69" ht="19.5" hidden="1" customHeight="1">
@@ -11472,14 +11555,14 @@
         <v>46254.0</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C69" s="14"/>
       <c r="D69" s="9">
         <v>114357.0</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F69" s="9">
         <v>120.0</v>
@@ -11491,10 +11574,10 @@
         <v>120.0</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" ht="19.5" hidden="1" customHeight="1">
@@ -11502,14 +11585,14 @@
         <v>46254.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="9">
         <v>10601.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F70" s="9">
         <v>5700.0</v>
@@ -11532,14 +11615,14 @@
         <v>46254.0</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="9">
         <v>114268.0</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F71" s="9">
         <v>2700.0</v>
@@ -11562,14 +11645,14 @@
         <v>46254.0</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="9">
         <v>2114379.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F72" s="9">
         <v>2340.0</v>
@@ -11599,7 +11682,7 @@
         <v>2110302.0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F73" s="9">
         <v>88073.0</v>
@@ -11614,7 +11697,7 @@
         <v>22</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
@@ -11622,14 +11705,14 @@
         <v>46255.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F74" s="9">
         <v>72060.0</v>
@@ -11652,14 +11735,14 @@
         <v>46255.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="9">
         <v>152384.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F75" s="9">
         <v>6600.0</v>
@@ -11682,14 +11765,14 @@
         <v>46256.0</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="9">
         <v>13358.0</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F76" s="9">
         <v>288.0</v>
@@ -11704,7 +11787,7 @@
         <v>16</v>
       </c>
       <c r="J76" s="12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
@@ -11712,14 +11795,14 @@
         <v>46261.0</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C77" s="14"/>
       <c r="D77" s="9">
         <v>10601.0</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F77" s="9">
         <v>16770.0</v>
@@ -11740,14 +11823,14 @@
         <v>46261.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" s="14"/>
       <c r="D78" s="9">
         <v>114379.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F78" s="9">
         <v>3600.0</v>
@@ -11759,23 +11842,23 @@
         <v>3600.0</v>
       </c>
       <c r="I78" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J78" s="12"/>
     </row>
     <row r="79" ht="22.5" hidden="1" customHeight="1">
-      <c r="A79" s="19">
+      <c r="A79" s="18">
         <v>46262.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F79" s="9">
         <v>59670.0</v>
@@ -11787,23 +11870,23 @@
         <v>125400.0</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J79" s="12"/>
     </row>
     <row r="80" ht="22.5" hidden="1" customHeight="1">
-      <c r="A80" s="19">
+      <c r="A80" s="18">
         <v>46262.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="9">
         <v>114268.0</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F80" s="9">
         <v>33000.0</v>
@@ -11815,23 +11898,23 @@
         <v>10800.0</v>
       </c>
       <c r="I80" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J80" s="12"/>
     </row>
     <row r="81" ht="22.5" hidden="1" customHeight="1">
-      <c r="A81" s="19">
+      <c r="A81" s="18">
         <v>46262.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="9">
         <v>112379.0</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F81" s="9">
         <v>15000.0</v>
@@ -11843,23 +11926,23 @@
         <v>6300.0</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J81" s="12"/>
     </row>
     <row r="82" ht="22.5" hidden="1" customHeight="1">
-      <c r="A82" s="19">
+      <c r="A82" s="18">
         <v>46262.0</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="9">
         <v>112357.0</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F82" s="9">
         <v>1560.0</v>
@@ -11871,23 +11954,23 @@
         <v>1560.0</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J82" s="12"/>
     </row>
     <row r="83" ht="22.5" hidden="1" customHeight="1">
-      <c r="A83" s="19">
+      <c r="A83" s="18">
         <v>46262.0</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="9">
         <v>10103.0</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F83" s="9">
         <v>200.0</v>
@@ -11899,7 +11982,7 @@
         <v>100.0</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J83" s="12"/>
     </row>
@@ -11908,14 +11991,14 @@
         <v>46265.0</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="9">
         <v>112357.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F84" s="9">
         <v>1680.0</v>
@@ -11936,14 +12019,14 @@
         <v>46265.0</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="9">
         <v>112268.0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F85" s="9">
         <v>1200.0</v>
@@ -11964,14 +12047,14 @@
         <v>46265.0</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="9">
         <v>13358.0</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F86" s="9">
         <v>73440.0</v>
@@ -11983,7 +12066,7 @@
         <v>36864.0</v>
       </c>
       <c r="I86" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J86" s="12"/>
     </row>
@@ -11992,7 +12075,7 @@
         <v>46265.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="9">
@@ -12011,7 +12094,7 @@
         <v>138480.0</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J87" s="12"/>
     </row>
@@ -12020,14 +12103,14 @@
         <v>46265.0</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="9">
         <v>114357.0</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F88" s="9">
         <v>120.0</v>
@@ -12039,7 +12122,7 @@
         <v>600.0</v>
       </c>
       <c r="I88" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J88" s="12"/>
     </row>
@@ -12048,14 +12131,14 @@
         <v>46267.0</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="9">
         <v>73001.0</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F89" s="9">
         <v>82903.0</v>
@@ -12076,14 +12159,14 @@
         <v>46268.0</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F90" s="9">
         <v>2938.0</v>
@@ -12104,7 +12187,7 @@
         <v>46269.0</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="9">
@@ -12132,14 +12215,14 @@
         <v>46269.0</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F92" s="9">
         <v>281580.0</v>
@@ -12160,14 +12243,14 @@
         <v>46269.0</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="9">
         <v>114379.0</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F93" s="9">
         <v>3900.0</v>
@@ -12188,14 +12271,14 @@
         <v>46269.0</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F94" s="9">
         <v>5040.0</v>
@@ -12216,14 +12299,14 @@
         <v>46272.0</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F95" s="9">
         <v>420158.0</v>
@@ -12244,14 +12327,14 @@
         <v>46272.0</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="9">
         <v>2110302.0</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F96" s="9">
         <v>340080.0</v>
@@ -12272,14 +12355,14 @@
         <v>46272.0</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="9">
         <v>272003.0</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F97" s="9">
         <v>25404.0</v>
@@ -12300,14 +12383,14 @@
         <v>46272.0</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F98" s="9">
         <v>4140.0</v>
@@ -12328,14 +12411,14 @@
         <v>46272.0</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="9">
         <v>273003.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F99" s="9">
         <v>12100.0</v>
@@ -12356,14 +12439,14 @@
         <v>46272.0</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C100" s="14"/>
       <c r="D100" s="9">
         <v>2114268.0</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F100" s="9">
         <v>180.0</v>
@@ -12384,14 +12467,14 @@
         <v>46274.0</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="9">
         <v>114379.0</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F101" s="9">
         <v>6900.0</v>
@@ -12412,14 +12495,14 @@
         <v>46274.0</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="9">
         <v>112357.0</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F102" s="9">
         <v>240.0</v>
@@ -12440,14 +12523,14 @@
         <v>46274.0</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C103" s="14"/>
       <c r="D103" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F103" s="9">
         <v>118286.0</v>
@@ -12468,14 +12551,14 @@
         <v>46276.0</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F104" s="9">
         <v>264061.0</v>
@@ -12496,14 +12579,14 @@
         <v>46276.0</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="9">
         <v>273003.0</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F105" s="9">
         <v>9106.0</v>
@@ -12524,7 +12607,7 @@
         <v>46276.0</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="9">
@@ -12552,14 +12635,14 @@
         <v>46279.0</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F107" s="9">
         <v>445991.0</v>
@@ -12574,7 +12657,7 @@
         <v>16</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
@@ -12582,14 +12665,14 @@
         <v>46279.0</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="9">
         <v>2112207.0</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F108" s="9">
         <v>360.0</v>
@@ -12610,14 +12693,14 @@
         <v>46281.0</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F109" s="9">
         <v>35.0</v>
@@ -12643,7 +12726,7 @@
         <v>2010301.0</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F110" s="9">
         <v>213392.0</v>
@@ -12666,14 +12749,14 @@
         <v>46281.0</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F111" s="9">
         <v>34327.0</v>
@@ -12685,7 +12768,7 @@
         <v>132072.0</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J111" s="12"/>
     </row>
@@ -12694,14 +12777,14 @@
         <v>46281.0</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F112" s="9">
         <v>177481.0</v>
@@ -12712,11 +12795,36 @@
       <c r="H112" s="9">
         <v>12301.0</v>
       </c>
-      <c r="I112" s="11"/>
+      <c r="I112" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="J112" s="12"/>
     </row>
-    <row r="113">
-      <c r="I113" s="23"/>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="A113" s="5">
+        <v>46283.0</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="14"/>
+      <c r="D113" s="9">
+        <v>2152388.0</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F113" s="9">
+        <v>9720.0</v>
+      </c>
+      <c r="G113" s="9">
+        <v>6840.0</v>
+      </c>
+      <c r="H113" s="9">
+        <v>5220.0</v>
+      </c>
+      <c r="I113" s="11"/>
+      <c r="J113" s="12"/>
     </row>
     <row r="114">
       <c r="I114" s="23"/>
@@ -15255,13 +15363,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I112">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I113">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I113:I958">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I114:I958">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A112">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A113">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>

--- a/BD Rupturas.xlsx
+++ b/BD Rupturas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="243">
   <si>
     <t>Fecha corte</t>
   </si>
@@ -44,39 +44,39 @@
     <t xml:space="preserve">Otro </t>
   </si>
   <si>
+    <t>ALKA2</t>
+  </si>
+  <si>
     <t>TAT BOGOTA MONTEVIDEO</t>
   </si>
   <si>
-    <t>ALKA2</t>
-  </si>
-  <si>
     <t>Daniel Castro</t>
   </si>
   <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+  </si>
+  <si>
     <t>HUEVO XL X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA</t>
+    <t>7. Otro</t>
   </si>
   <si>
     <t>2. Error De Registro De Inventario</t>
   </si>
   <si>
-    <t>7. Otro</t>
-  </si>
-  <si>
     <t>el huevo ya tenia 9 dias , no se despacho por alta edad</t>
   </si>
   <si>
+    <t>LANZA</t>
+  </si>
+  <si>
     <t>TAT MONTERIA</t>
   </si>
   <si>
     <t>LUIS LOPEZ</t>
   </si>
   <si>
-    <t>LANZA</t>
-  </si>
-  <si>
     <t>HUEVO XXL X 10 PET CANASTA X 100 PV</t>
   </si>
   <si>
@@ -116,45 +116,48 @@
     <t>HUEVO L X 30 CARTON VERDE CANASTA</t>
   </si>
   <si>
+    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
+  </si>
+  <si>
     <t>4. Exigencia Del Cliente (Edad)</t>
   </si>
   <si>
     <t>Venta FS</t>
   </si>
   <si>
-    <t xml:space="preserve">10x300 y 7x120  cajas, estan de mas desde el dia 18 de julio no cabian en el carro, , los pedidos vienen precisos, es necesario un pedido adicional para despachar a un cedi o dejarlos de fabricar desde clasificacion </t>
-  </si>
-  <si>
     <t>HUEVO XL X 15 PET CAJA X 300</t>
   </si>
   <si>
+    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+  </si>
+  <si>
+    <t>PALMAS</t>
+  </si>
+  <si>
     <t>Se dejó lote para revisión por calidad</t>
   </si>
   <si>
-    <t>Ing ayer solo se despacho las del exito BQ , esas se envian maximo 2 dias porque estarian entregando al cliente con 4 dias, las que me dice hoy se le cambian las etiquetas al 114268 y s enevian a TAT</t>
+    <t>HCP L X 12 PET VERDE CAJA X 120</t>
+  </si>
+  <si>
+    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
   </si>
   <si>
     <t>HUEVO YUMBO X20 CARTON VERDE CANASTA</t>
   </si>
   <si>
-    <t>PALMAS</t>
-  </si>
-  <si>
-    <t>HCP L X 12 PET VERDE CAJA X 120</t>
-  </si>
-  <si>
     <t>Se envía más fresco a Rionegro</t>
   </si>
   <si>
-    <t>no se despacho por temas de transporte - inventario alto poruque llego mas producto del mismo item, tampoco depsachado por temas de transprote</t>
+    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
+  </si>
+  <si>
+    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
   </si>
   <si>
     <t>HUEVO L X 15 PAGUE 14 PET CAJA X 300.</t>
   </si>
   <si>
-    <t>HUEVO L X 15 PAGUE 14 PET EN CANASTA.</t>
-  </si>
-  <si>
     <t>1. Ingreso Por Devolución</t>
   </si>
   <si>
@@ -164,7 +167,10 @@
     <t>DIEGO ROJAS</t>
   </si>
   <si>
-    <t>COLA DE DESPACHO, PET 4 DIAS DE EDAD NO SE PUEDE DESPACHAR</t>
+    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ROJO</t>
   </si>
   <si>
     <t>TAT CUCUTA</t>
@@ -173,12 +179,6 @@
     <t>ALEXANDER PEÑA</t>
   </si>
   <si>
-    <t>Es el mismo huevo reportado el dia de ayer, tiene alta edad 11 dias y esta marcado</t>
-  </si>
-  <si>
-    <t>HUEVO PICADO ROJO</t>
-  </si>
-  <si>
     <t>No se carga todod por capacidad de Vehiculo</t>
   </si>
   <si>
@@ -188,13 +188,19 @@
     <t>Envío huevo fresco a Sincelejo</t>
   </si>
   <si>
+    <t>HUEVO SUCIO DE JAULA</t>
+  </si>
+  <si>
     <t>Transformación de PET</t>
   </si>
   <si>
+    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
     <t>ANDRES MEJIA</t>
   </si>
   <si>
-    <t>HUEVO SUCIO DE JAULA</t>
+    <t>Esta para despacho hoy</t>
   </si>
   <si>
     <t>El Asesor de la ruta H3023 no cargó el sábado por malestar pero ya cargó hoy</t>
@@ -206,21 +212,15 @@
     <t>JONATHAN MOSQUERA</t>
   </si>
   <si>
-    <t>HUEVO L X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
-    <t>Esta para despacho hoy</t>
+    <t>Cola de programación</t>
+  </si>
+  <si>
+    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
   </si>
   <si>
     <t>cargue en la mañana (partido Colombia) y error reporte lote de 5 dias</t>
   </si>
   <si>
-    <t>Cola de programación</t>
-  </si>
-  <si>
-    <t>HUEVO CE X 30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
     <t>Se despachó una cantidad menor a la solicitada por planeación debido a que la mula era de menor capacidad.</t>
   </si>
   <si>
@@ -242,12 +242,12 @@
     <t>5. Ingreso De Planta</t>
   </si>
   <si>
+    <t>Se despacha par FS con producto más nuevo</t>
+  </si>
+  <si>
     <t>HUEVO L X 30 CARTON VERDE AMARRADO SIN ETIQUETA</t>
   </si>
   <si>
-    <t>Se despacha par FS con producto más nuevo</t>
-  </si>
-  <si>
     <t>HUEVO L X 12 PET CANASTA X 144 PV</t>
   </si>
   <si>
@@ -338,12 +338,12 @@
     <t>unidades con olores fuertes / se deja de cargar para evitar devolucion en mayorista</t>
   </si>
   <si>
+    <t>HUEVO SUCIO ZF MARCADO</t>
+  </si>
+  <si>
     <t>Cajas que llegaron de más LX12 se pasan a Suelto</t>
   </si>
   <si>
-    <t>HUEVO SUCIO ZF MARCADO</t>
-  </si>
-  <si>
     <t>vehiculo con flata de capacidad / TAT cali</t>
   </si>
   <si>
@@ -371,25 +371,25 @@
     <t>HUEVO AA ROJO X 288 CARTON GRIS CAJA-EN DOCENERA-SOL NACIENT.</t>
   </si>
   <si>
+    <t>Se envía producto a Sincelejo con menor edad</t>
+  </si>
+  <si>
     <t>vehiculo pendiente pro llegar a planta</t>
   </si>
   <si>
-    <t>Se envía producto a Sincelejo con menor edad</t>
+    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
   </si>
   <si>
     <t>Despacho de producto hacia villavicencio - Recomiendan despachar de 1 dia</t>
   </si>
   <si>
-    <t>Producto que queda de clientes de preventa - TAT, que el cliente no recibe</t>
-  </si>
-  <si>
     <t>vehiculo sin capacidad poruq eestaba compartido con ALKA1 elcual no dejo el espacio suficiente</t>
   </si>
   <si>
+    <t>TAT VILLAVICENCIO</t>
+  </si>
+  <si>
     <t>no salio el dia progrmado por falta de flota, se corre despacho para el dia siguiente en la tarde</t>
-  </si>
-  <si>
-    <t>TAT VILLAVICENCIO</t>
   </si>
   <si>
     <t>anularon pedidos y por orden de planeacion se autorizo soltar para enviar a medellin</t>
@@ -456,22 +456,28 @@
     <t>Identificación producto averiado en el momento de la entrega del TAT, se bandejea</t>
   </si>
   <si>
+    <t>HUEVO M X 30 CARTON VERDE CANASTA - BUCAROS</t>
+  </si>
+  <si>
     <t>yOVANIS AREVALO</t>
   </si>
   <si>
     <t xml:space="preserve">DEV CLIENTE MAS POR MENOS </t>
   </si>
   <si>
-    <t>HUEVO M X 30 CARTON VERDE CANASTA - BUCAROS</t>
-  </si>
-  <si>
     <t>Se envía huevo fresco a Rionegro</t>
   </si>
   <si>
+    <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
+  </si>
+  <si>
     <t>Clientes Fs</t>
   </si>
   <si>
-    <t>HUEVO SUCIO ZF MARCADO X 30 BANDEJA GRIS CANASTA</t>
+    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
   </si>
   <si>
     <t>Se envían para Rionegro con mejor fecha</t>
@@ -483,15 +489,9 @@
     <t>Jhonathan Gomez</t>
   </si>
   <si>
-    <t>HUEVO PICADO ZF MARCADO X 30 BANDEJAS GRIS CANASTA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Se registraron edades antes de sacar el sugerido del dia </t>
   </si>
   <si>
-    <t>HUEVO XL X 15 PET CANASTA X 180 PV</t>
-  </si>
-  <si>
     <t>LLegada de planta</t>
   </si>
   <si>
@@ -507,16 +507,16 @@
     <t>El lote no se despachó el día anterior debido a que el envío se realizó en un vehículo compartido. Al ser Palmas la última bodega en la que se realizó la carga, solo se logró despachar la cantidad que la capacidad del vehículo permitió.</t>
   </si>
   <si>
+    <t>Se programó por encima de la cantidad  disponible y se traslado a la VR para habilitación de pedido al siguiente dia.</t>
+  </si>
+  <si>
+    <t>HUEVO AA X30 CARTON GRIS CANASTA</t>
+  </si>
+  <si>
+    <t>reportaron mal las edades</t>
+  </si>
+  <si>
     <t>novedad en lotes por calidad</t>
-  </si>
-  <si>
-    <t>Se programó por encima de la cantidad  disponible y se traslado a la VR para habilitación de pedido al siguiente dia.</t>
-  </si>
-  <si>
-    <t>HUEVO AA X30 CARTON GRIS CANASTA</t>
-  </si>
-  <si>
-    <t>reportaron mal las edades</t>
   </si>
   <si>
     <t>Producto no recibido en Rionegro pr calidad, se va a revisar</t>
@@ -781,14 +781,14 @@
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -819,48 +819,48 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -869,13 +869,13 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -965,7 +965,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J212" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J213" displayName="Rupturas_Rotación_CEDIS" name="Rupturas_Rotación_CEDIS" id="1">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -983,7 +983,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J117" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J117" displayName="Rupturas_Rotación_Plantas" name="Rupturas_Rotación_Plantas" id="2">
   <tableColumns count="10">
     <tableColumn name="Fecha corte" id="1"/>
     <tableColumn name="Destino" id="2"/>
@@ -1246,20 +1246,20 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46204.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="9">
         <v>359100.0</v>
@@ -1270,25 +1270,25 @@
       <c r="H2" s="9">
         <v>206140.0</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>15</v>
+      <c r="I2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46205.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="9">
         <v>298282.0</v>
@@ -1302,16 +1302,16 @@
       <c r="I3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46205.0</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="9">
@@ -1330,18 +1330,18 @@
         <v>16920.0</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46205.0</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="9">
@@ -1360,27 +1360,27 @@
         <v>3134.0</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46206.0</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="9">
         <v>189540.0</v>
@@ -1392,27 +1392,27 @@
         <v>144720.0</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>46206.0</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9">
         <v>20640.0</v>
@@ -1424,27 +1424,27 @@
         <v>13920.0</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46206.0</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="9">
         <v>152384.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" s="9">
         <v>14700.0</v>
@@ -1456,25 +1456,25 @@
         <v>9600.0</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46206.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D9" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="9">
         <v>228240.0</v>
@@ -1486,25 +1486,25 @@
         <v>124260.0</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46206.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="D10" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="9">
         <v>7830.0</v>
@@ -1521,20 +1521,20 @@
       <c r="J10" s="15"/>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46206.0</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" s="9">
         <v>31680.0</v>
@@ -1546,21 +1546,21 @@
         <v>23040.0</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J11" s="12" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46206.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D12" s="9">
         <v>2110302.0</v>
@@ -1578,27 +1578,27 @@
         <v>12170.0</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46209.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="9">
         <v>195810.0</v>
@@ -1610,27 +1610,27 @@
         <v>133410.0</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46209.0</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9">
         <v>526002.0</v>
@@ -1645,24 +1645,24 @@
         <v>22</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46209.0</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>59</v>
+      <c r="C15" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D15" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F15" s="9">
         <v>14160.0</v>
@@ -1674,21 +1674,21 @@
         <v>12360.0</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46210.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="D16" s="9">
         <v>2110302.0</v>
@@ -1706,19 +1706,19 @@
         <v>289680.0</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46210.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D17" s="9">
         <v>2110217.0</v>
@@ -1736,19 +1736,19 @@
         <v>19770.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46210.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="9">
         <v>2110302.0</v>
@@ -1766,25 +1766,25 @@
         <v>162125.0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="12"/>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>46211.0</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="9">
         <v>495833.0</v>
@@ -1796,27 +1796,27 @@
         <v>401280.0</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>46211.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="9">
         <v>139920.0</v>
@@ -1828,19 +1828,19 @@
         <v>74040.0</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="12"/>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>46211.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D21" s="9">
         <v>2110302.0</v>
@@ -1858,27 +1858,27 @@
         <v>100687.0</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>46211.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="9">
         <v>152384.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F22" s="9">
         <v>32850.0</v>
@@ -1890,19 +1890,19 @@
         <v>32700.0</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46211.0</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>59</v>
+      <c r="C23" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D23" s="9">
         <v>112271.0</v>
@@ -1920,25 +1920,25 @@
         <v>18000.0</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46212.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="9">
         <v>190047.0</v>
@@ -1950,19 +1950,19 @@
         <v>248481.0</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46212.0</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="9">
         <v>2110302.0</v>
@@ -1985,20 +1985,20 @@
       <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46212.0</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D26" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="9">
         <v>10320.0</v>
@@ -2010,21 +2010,21 @@
         <v>13200.0</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46212.0</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D27" s="9">
         <v>112271.0</v>
@@ -2047,11 +2047,11 @@
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46213.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>79</v>
@@ -2072,18 +2072,18 @@
         <v>150833.0</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>46213.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>79</v>
@@ -2092,7 +2092,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="9">
         <v>962820.0</v>
@@ -2104,27 +2104,27 @@
         <v>922140.0</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>46213.0</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D30" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="9">
         <v>335340.0</v>
@@ -2136,21 +2136,21 @@
         <v>381600.0</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J30" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>46213.0</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D31" s="9">
         <v>2110302.0</v>
@@ -2173,14 +2173,14 @@
       <c r="J31" s="12"/>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>46213.0</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="9">
         <v>2110302.0</v>
@@ -2198,25 +2198,25 @@
         <v>128971.0</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J32" s="12"/>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>46213.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D33" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33" s="9">
         <v>58080.0</v>
@@ -2233,13 +2233,13 @@
       <c r="J33" s="12"/>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>46217.0</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>87</v>
       </c>
       <c r="D34" s="9">
@@ -2263,20 +2263,20 @@
       <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>46217.0</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D35" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="9">
         <v>355720.0</v>
@@ -2288,16 +2288,16 @@
         <v>302760.0</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" s="12"/>
     </row>
     <row r="36" ht="22.5" hidden="1" customHeight="1">
-      <c r="A36" s="5">
+      <c r="A36" s="4">
         <v>46217.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>79</v>
@@ -2306,7 +2306,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F36" s="9">
         <v>35280.0</v>
@@ -2329,7 +2329,7 @@
         <v>46218.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>79</v>
@@ -2350,7 +2350,7 @@
         <v>275205.0</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J37" s="12" t="s">
         <v>92</v>
@@ -2361,7 +2361,7 @@
         <v>46218.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>79</v>
@@ -2370,7 +2370,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F38" s="9">
         <v>37926.0</v>
@@ -2395,14 +2395,14 @@
       <c r="B39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D39" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F39" s="9">
         <v>20640.0</v>
@@ -2414,7 +2414,7 @@
         <v>16320.0</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>94</v>
@@ -2427,14 +2427,14 @@
       <c r="B40" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D40" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F40" s="9">
         <v>10980.0</v>
@@ -2451,7 +2451,7 @@
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>46219.0</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -2476,14 +2476,14 @@
         <v>90480.0</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>46219.0</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -2496,7 +2496,7 @@
         <v>2152388.0</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="9">
         <v>36225.0</v>
@@ -2508,19 +2508,19 @@
         <v>27570.0</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>46219.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="9">
         <v>2110302.0</v>
@@ -2545,7 +2545,7 @@
       </c>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>46219.0</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -2575,11 +2575,11 @@
       <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>46219.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>79</v>
@@ -2588,7 +2588,7 @@
         <v>152384.0</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F45" s="9">
         <v>31125.0</v>
@@ -2600,18 +2600,18 @@
         <v>31845.0</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>46219.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>79</v>
@@ -2620,7 +2620,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F46" s="9">
         <v>25746.0</v>
@@ -2639,11 +2639,11 @@
       </c>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46220.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>79</v>
@@ -2664,18 +2664,18 @@
         <v>221549.0</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>46220.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>79</v>
@@ -2701,20 +2701,20 @@
       <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>46224.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F49" s="9">
         <v>398570.0</v>
@@ -2726,14 +2726,14 @@
         <v>287235.0</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J49" s="12" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>46224.0</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -2746,7 +2746,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F50" s="9">
         <v>745107.0</v>
@@ -2758,21 +2758,21 @@
         <v>551645.0</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>46225.0</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>59</v>
+      <c r="C51" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D51" s="9">
         <v>2110302.0</v>
@@ -2793,18 +2793,18 @@
         <v>22</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>46225.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D52" s="9">
         <v>2110302.0</v>
@@ -2827,11 +2827,11 @@
       <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>46225.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>79</v>
@@ -2840,7 +2840,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F53" s="9">
         <v>25200.0</v>
@@ -2859,20 +2859,20 @@
       </c>
     </row>
     <row r="54" ht="22.5" hidden="1" customHeight="1">
-      <c r="A54" s="5">
+      <c r="A54" s="4">
         <v>46226.0</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D54" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F54" s="9">
         <v>285405.0</v>
@@ -2891,20 +2891,20 @@
       </c>
     </row>
     <row r="55" ht="22.5" hidden="1" customHeight="1">
-      <c r="A55" s="5">
+      <c r="A55" s="4">
         <v>46226.0</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>59</v>
+      <c r="C55" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D55" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="9">
         <v>692280.0</v>
@@ -2921,20 +2921,20 @@
       <c r="J55" s="12"/>
     </row>
     <row r="56" ht="22.5" hidden="1" customHeight="1">
-      <c r="A56" s="5">
+      <c r="A56" s="4">
         <v>46227.0</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>59</v>
+      <c r="C56" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D56" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="9">
         <v>700200.0</v>
@@ -2951,20 +2951,20 @@
       <c r="J56" s="12"/>
     </row>
     <row r="57" ht="22.5" hidden="1" customHeight="1">
-      <c r="A57" s="5">
+      <c r="A57" s="4">
         <v>46227.0</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D57" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F57" s="9">
         <v>226069.0</v>
@@ -2976,27 +2976,27 @@
         <v>326391.0</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J57" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="58" ht="22.5" hidden="1" customHeight="1">
-      <c r="A58" s="5">
+      <c r="A58" s="4">
         <v>46227.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D58" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F58" s="9">
         <v>144637.0</v>
@@ -3013,20 +3013,20 @@
       <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>46227.0</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D59" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F59" s="9">
         <v>295359.0</v>
@@ -3038,20 +3038,20 @@
         <v>166642.0</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <v>46230.0</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D60" s="9">
@@ -3075,11 +3075,11 @@
       <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>46230.0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>79</v>
@@ -3105,20 +3105,20 @@
       <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>46230.0</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D62" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="9">
         <v>437080.0</v>
@@ -3130,27 +3130,27 @@
         <v>353700.0</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J62" s="12" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>46231.0</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D63" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F63" s="9">
         <v>165466.0</v>
@@ -3162,21 +3162,21 @@
         <v>375549.0</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <v>46231.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D64" s="9">
         <v>2110302.0</v>
@@ -3194,27 +3194,27 @@
         <v>181858.0</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" ht="22.5" hidden="1" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>46231.0</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C65" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D65" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F65" s="9">
         <v>8190.0</v>
@@ -3226,27 +3226,27 @@
         <v>7200.0</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" ht="22.5" hidden="1" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>46231.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D66" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" s="9">
         <v>146224.0</v>
@@ -3258,25 +3258,25 @@
         <v>98850.0</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" ht="22.5" hidden="1" customHeight="1">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>46232.0</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C67" s="20"/>
       <c r="D67" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" s="9">
         <v>14599.0</v>
@@ -3288,12 +3288,12 @@
         <v>7263.0</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J67" s="12"/>
     </row>
     <row r="68" ht="22.5" hidden="1" customHeight="1">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <v>46232.0</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -3304,7 +3304,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F68" s="9">
         <v>22080.0</v>
@@ -3316,12 +3316,12 @@
         <v>36720.0</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J68" s="12"/>
     </row>
     <row r="69" ht="22.5" hidden="1" customHeight="1">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>46232.0</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -3332,7 +3332,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F69" s="9">
         <v>353905.0</v>
@@ -3344,23 +3344,23 @@
         <v>117570.0</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J69" s="12"/>
     </row>
     <row r="70" ht="22.5" hidden="1" customHeight="1">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <v>46232.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C70" s="20"/>
       <c r="D70" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F70" s="9">
         <v>5913.0</v>
@@ -3372,16 +3372,16 @@
         <v>5893.0</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J70" s="12"/>
     </row>
     <row r="71" ht="22.5" hidden="1" customHeight="1">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>46232.0</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="9">
@@ -3400,23 +3400,23 @@
         <v>142320.0</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J71" s="12"/>
     </row>
     <row r="72" ht="22.5" hidden="1" customHeight="1">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <v>46232.0</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C72" s="20"/>
       <c r="D72" s="9">
         <v>152384.0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F72" s="9">
         <v>21300.0</v>
@@ -3428,12 +3428,12 @@
         <v>18690.0</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J72" s="12"/>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>46232.0</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -3444,7 +3444,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F73" s="9">
         <v>351733.0</v>
@@ -3456,7 +3456,7 @@
         <v>200114.0</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J73" s="12"/>
     </row>
@@ -3465,10 +3465,10 @@
         <v>46233.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D74" s="9">
         <v>2110302.0</v>
@@ -3497,10 +3497,10 @@
         <v>46233.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D75" s="9">
         <v>2110302.0</v>
@@ -3523,13 +3523,13 @@
       <c r="J75" s="12"/>
     </row>
     <row r="76" ht="22.5" hidden="1" customHeight="1">
-      <c r="A76" s="5">
+      <c r="A76" s="4">
         <v>46234.0</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D76" s="9">
@@ -3553,13 +3553,13 @@
       <c r="J76" s="12"/>
     </row>
     <row r="77" ht="22.5" hidden="1" customHeight="1">
-      <c r="A77" s="5">
+      <c r="A77" s="4">
         <v>46234.0</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D77" s="9">
@@ -3578,27 +3578,27 @@
         <v>2040.0</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J77" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="78" ht="22.5" hidden="1" customHeight="1">
-      <c r="A78" s="5">
+      <c r="A78" s="4">
         <v>46234.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C78" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D78" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F78" s="9">
         <v>5580.0</v>
@@ -3610,7 +3610,7 @@
         <v>3984.0</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J78" s="12" t="s">
         <v>136</v>
@@ -3621,16 +3621,16 @@
         <v>46237.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C79" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D79" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F79" s="9">
         <v>192903.0</v>
@@ -3642,7 +3642,7 @@
         <v>77501.0</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J79" s="12" t="s">
         <v>137</v>
@@ -3653,10 +3653,10 @@
         <v>46237.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C80" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D80" s="9">
         <v>2110302.0</v>
@@ -3674,7 +3674,7 @@
         <v>124423.0</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J80" s="12" t="s">
         <v>137</v>
@@ -3685,9 +3685,9 @@
         <v>46237.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C81" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>138</v>
       </c>
       <c r="D81" s="9">
@@ -3719,14 +3719,14 @@
       <c r="B82" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="8" t="s">
         <v>140</v>
       </c>
       <c r="D82" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F82" s="9">
         <v>45564.0</v>
@@ -3738,7 +3738,7 @@
         <v>40560.0</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -3747,10 +3747,10 @@
         <v>46237.0</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C83" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D83" s="9">
         <v>2110302.0</v>
@@ -3768,27 +3768,27 @@
         <v>48804.0</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J83" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <v>46238.0</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D84" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F84" s="9">
         <v>43200.0</v>
@@ -3805,20 +3805,20 @@
       <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <v>46238.0</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D85" s="9">
         <v>152384.0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F85" s="9">
         <v>25350.0</v>
@@ -3830,25 +3830,25 @@
         <v>30750.0</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <v>46238.0</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D86" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F86" s="9">
         <v>5040.0</v>
@@ -3865,14 +3865,14 @@
       <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <v>46238.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C87" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D87" s="9">
         <v>2110302.0</v>
@@ -3890,27 +3890,27 @@
         <v>69217.0</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J87" s="12" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <v>46239.0</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D88" s="9">
         <v>152384.0</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F88" s="9">
         <v>30750.0</v>
@@ -3927,13 +3927,13 @@
       <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <v>46239.0</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D89" s="9">
@@ -3952,7 +3952,7 @@
         <v>12480.0</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J89" s="12" t="s">
         <v>145</v>
@@ -3965,14 +3965,14 @@
       <c r="B90" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D90" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F90" s="9">
         <v>254880.0</v>
@@ -3984,7 +3984,7 @@
         <v>27180.0</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J90" s="12" t="s">
         <v>146</v>
@@ -3997,8 +3997,8 @@
       <c r="B91" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C91" s="7" t="s">
-        <v>147</v>
+      <c r="C91" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="D91" s="9">
         <v>112379.0</v>
@@ -4016,7 +4016,7 @@
         <v>12132.0</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J91" s="12"/>
     </row>
@@ -4027,14 +4027,14 @@
       <c r="B92" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D92" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F92" s="9">
         <v>4575.0</v>
@@ -4046,10 +4046,10 @@
         <v>4213.0</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
@@ -4059,7 +4059,7 @@
       <c r="B93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D93" s="9">
@@ -4078,7 +4078,7 @@
         <v>312480.0</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J93" s="12" t="s">
         <v>150</v>
@@ -4091,14 +4091,14 @@
       <c r="B94" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D94" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F94" s="9">
         <v>300060.0</v>
@@ -4110,7 +4110,7 @@
         <v>260696.0</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J94" s="12" t="s">
         <v>150</v>
@@ -4123,14 +4123,14 @@
       <c r="B95" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D95" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F95" s="9">
         <v>36240.0</v>
@@ -4142,7 +4142,7 @@
         <v>39840.0</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J95" s="12" t="s">
         <v>150</v>
@@ -4153,16 +4153,16 @@
         <v>46244.0</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D96" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F96" s="9">
         <v>21690.0</v>
@@ -4179,13 +4179,13 @@
       <c r="J96" s="12"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <v>46245.0</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D97" s="9">
@@ -4209,20 +4209,20 @@
       <c r="J97" s="12"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <v>46245.0</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D98" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F98" s="9">
         <v>39840.0</v>
@@ -4234,27 +4234,27 @@
         <v>23520.0</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <v>46245.0</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C99" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D99" s="9">
         <v>152384.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F99" s="9">
         <v>18600.0</v>
@@ -4266,20 +4266,20 @@
         <v>12900.0</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <v>46245.0</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C100" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D100" s="9">
@@ -4298,27 +4298,27 @@
         <v>269040.0</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <v>46246.0</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C101" s="7" t="s">
-        <v>155</v>
+      <c r="C101" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="D101" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F101" s="9">
         <v>423758.0</v>
@@ -4330,27 +4330,27 @@
         <v>638764.0</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="102" ht="22.5" hidden="1" customHeight="1">
-      <c r="A102" s="5">
+      <c r="A102" s="4">
         <v>46246.0</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D102" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F102" s="9">
         <v>800120.0</v>
@@ -4362,20 +4362,20 @@
         <v>655250.0</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J102" s="12" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <v>46246.0</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D103" s="9">
@@ -4401,20 +4401,20 @@
       </c>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
-      <c r="A104" s="5">
+      <c r="A104" s="4">
         <v>46246.0</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D104" s="9">
         <v>152384.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F104" s="9">
         <v>12900.0</v>
@@ -4426,14 +4426,14 @@
         <v>19800.0</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J104" s="12" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <v>46247.0</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -4458,27 +4458,27 @@
         <v>63824.0</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J105" s="12" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
-      <c r="A106" s="5">
+      <c r="A106" s="4">
         <v>46247.0</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D106" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F106" s="9">
         <v>245520.0</v>
@@ -4490,18 +4490,18 @@
         <v>230580.0</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J106" s="12"/>
     </row>
     <row r="107" ht="22.5" hidden="1" customHeight="1">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <v>46247.0</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D107" s="9">
@@ -4525,13 +4525,13 @@
       <c r="J107" s="12"/>
     </row>
     <row r="108" ht="22.5" hidden="1" customHeight="1">
-      <c r="A108" s="5">
+      <c r="A108" s="4">
         <v>46247.0</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D108" s="9">
@@ -4550,25 +4550,25 @@
         <v>12600.0</v>
       </c>
       <c r="I108" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J108" s="12"/>
     </row>
     <row r="109" ht="22.5" hidden="1" customHeight="1">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <v>46248.0</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C109" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D109" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F109" s="9">
         <v>793976.0</v>
@@ -4580,20 +4580,20 @@
         <v>584490.0</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110" ht="22.5" hidden="1" customHeight="1">
-      <c r="A110" s="5">
+      <c r="A110" s="4">
         <v>46248.0</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D110" s="9">
@@ -4617,20 +4617,20 @@
       <c r="J110" s="12"/>
     </row>
     <row r="111" ht="22.5" hidden="1" customHeight="1">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <v>46248.0</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D111" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F111" s="9">
         <v>230580.0</v>
@@ -4642,27 +4642,27 @@
         <v>298620.0</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J111" s="12" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="112" ht="22.5" hidden="1" customHeight="1">
-      <c r="A112" s="5">
+      <c r="A112" s="4">
         <v>46248.0</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D112" s="9">
         <v>152384.0</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F112" s="9">
         <v>13200.0</v>
@@ -4674,27 +4674,27 @@
         <v>7200.0</v>
       </c>
       <c r="I112" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J112" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="113" ht="22.5" hidden="1" customHeight="1">
-      <c r="A113" s="5">
+      <c r="A113" s="4">
         <v>46248.0</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="8" t="s">
         <v>170</v>
       </c>
       <c r="D113" s="9">
         <v>152384.0</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F113" s="9">
         <v>9900.0</v>
@@ -4706,21 +4706,21 @@
         <v>8100.0</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J113" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="114" ht="22.5" hidden="1" customHeight="1">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <v>46252.0</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C114" s="7" t="s">
-        <v>59</v>
+      <c r="C114" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D114" s="9">
         <v>2110302.0</v>
@@ -4738,27 +4738,27 @@
         <v>68640.0</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J114" s="12" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="115" ht="22.5" hidden="1" customHeight="1">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <v>46252.0</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C115" s="7" t="s">
-        <v>59</v>
+      <c r="C115" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D115" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F115" s="9">
         <v>26880.0</v>
@@ -4770,27 +4770,27 @@
         <v>26880.0</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J115" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="116" ht="22.5" hidden="1" customHeight="1">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <v>46252.0</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C116" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D116" s="9">
         <v>152384.0</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F116" s="9">
         <v>21585.0</v>
@@ -4802,27 +4802,27 @@
         <v>12900.0</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J116" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="117" ht="22.5" hidden="1" customHeight="1">
-      <c r="A117" s="5">
+      <c r="A117" s="4">
         <v>46253.0</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C117" s="7" t="s">
-        <v>59</v>
+      <c r="C117" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D117" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F117" s="9">
         <v>179640.0</v>
@@ -4833,26 +4833,26 @@
       <c r="H117" s="9">
         <v>39060.0</v>
       </c>
-      <c r="I117" s="10" t="s">
+      <c r="I117" s="11" t="s">
         <v>23</v>
       </c>
       <c r="J117" s="12"/>
     </row>
     <row r="118" ht="22.5" hidden="1" customHeight="1">
-      <c r="A118" s="5">
+      <c r="A118" s="4">
         <v>46253.0</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C118" s="7" t="s">
-        <v>59</v>
+      <c r="C118" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D118" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F118" s="9">
         <v>26880.0</v>
@@ -4863,26 +4863,26 @@
       <c r="H118" s="9">
         <v>25680.0</v>
       </c>
-      <c r="I118" s="10" t="s">
+      <c r="I118" s="11" t="s">
         <v>23</v>
       </c>
       <c r="J118" s="12"/>
     </row>
     <row r="119" ht="22.5" hidden="1" customHeight="1">
-      <c r="A119" s="5">
+      <c r="A119" s="4">
         <v>46253.0</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C119" s="7" t="s">
-        <v>59</v>
+      <c r="C119" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D119" s="9">
         <v>152384.0</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F119" s="9">
         <v>14230.0</v>
@@ -4893,26 +4893,26 @@
       <c r="H119" s="9">
         <v>13200.0</v>
       </c>
-      <c r="I119" s="10" t="s">
+      <c r="I119" s="11" t="s">
         <v>23</v>
       </c>
       <c r="J119" s="12"/>
     </row>
     <row r="120" ht="22.5" hidden="1" customHeight="1">
-      <c r="A120" s="5">
+      <c r="A120" s="4">
         <v>46253.0</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="C120" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D120" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F120" s="9">
         <v>26677.0</v>
@@ -4923,28 +4923,28 @@
       <c r="H120" s="9">
         <v>11790.0</v>
       </c>
-      <c r="I120" s="10" t="s">
-        <v>15</v>
+      <c r="I120" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="J120" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="121" ht="22.5" hidden="1" customHeight="1">
-      <c r="A121" s="5">
+      <c r="A121" s="4">
         <v>46253.0</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C121" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D121" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F121" s="9">
         <v>22500.0</v>
@@ -4955,21 +4955,21 @@
       <c r="H121" s="9">
         <v>18300.0</v>
       </c>
-      <c r="I121" s="10" t="s">
-        <v>47</v>
+      <c r="I121" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="J121" s="12" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="122" ht="22.5" hidden="1" customHeight="1">
-      <c r="A122" s="5">
+      <c r="A122" s="4">
         <v>46253.0</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C122" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D122" s="9">
@@ -4987,7 +4987,7 @@
       <c r="H122" s="9">
         <v>8100.0</v>
       </c>
-      <c r="I122" s="10" t="s">
+      <c r="I122" s="11" t="s">
         <v>22</v>
       </c>
       <c r="J122" s="12" t="s">
@@ -4995,20 +4995,20 @@
       </c>
     </row>
     <row r="123" ht="22.5" hidden="1" customHeight="1">
-      <c r="A123" s="5">
+      <c r="A123" s="4">
         <v>46254.0</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C123" s="7" t="s">
-        <v>155</v>
+      <c r="C123" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="D123" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F123" s="9">
         <v>21915.0</v>
@@ -5020,21 +5020,21 @@
         <v>14235.0</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J123" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="124" ht="22.5" hidden="1" customHeight="1">
-      <c r="A124" s="5">
+      <c r="A124" s="4">
         <v>46254.0</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C124" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D124" s="9">
         <v>2112207.0</v>
@@ -5057,20 +5057,20 @@
       <c r="J124" s="12"/>
     </row>
     <row r="125" ht="22.5" hidden="1" customHeight="1">
-      <c r="A125" s="5">
+      <c r="A125" s="4">
         <v>46254.0</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C125" s="8" t="s">
         <v>178</v>
       </c>
       <c r="D125" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F125" s="9">
         <v>6380.0</v>
@@ -5082,27 +5082,27 @@
         <v>1980.0</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J125" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="126" ht="22.5" hidden="1" customHeight="1">
-      <c r="A126" s="5">
+      <c r="A126" s="4">
         <v>46255.0</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C126" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D126" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F126" s="9">
         <v>28200.0</v>
@@ -5119,20 +5119,20 @@
       <c r="J126" s="12"/>
     </row>
     <row r="127" ht="22.5" hidden="1" customHeight="1">
-      <c r="A127" s="5">
+      <c r="A127" s="4">
         <v>46255.0</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D127" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F127" s="9">
         <v>23760.0</v>
@@ -5144,20 +5144,20 @@
         <v>17760.0</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J127" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="128" ht="22.5" hidden="1" customHeight="1">
-      <c r="A128" s="5">
+      <c r="A128" s="4">
         <v>46255.0</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D128" s="9">
@@ -5183,20 +5183,20 @@
       </c>
     </row>
     <row r="129" ht="22.5" hidden="1" customHeight="1">
-      <c r="A129" s="5">
+      <c r="A129" s="4">
         <v>46255.0</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C129" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D129" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F129" s="9">
         <v>2130.0</v>
@@ -5208,7 +5208,7 @@
         <v>1230.0</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J129" s="12" t="s">
         <v>186</v>
@@ -5219,16 +5219,16 @@
         <v>46258.0</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C130" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D130" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F130" s="9">
         <v>341120.0</v>
@@ -5251,16 +5251,16 @@
         <v>46258.0</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C131" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D131" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F131" s="9">
         <v>11520.0</v>
@@ -5281,16 +5281,16 @@
         <v>46258.0</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C132" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D132" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F132" s="9">
         <v>35520.0</v>
@@ -5309,14 +5309,14 @@
       </c>
     </row>
     <row r="133" ht="22.5" hidden="1" customHeight="1">
-      <c r="A133" s="5">
+      <c r="A133" s="4">
         <v>46259.0</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C133" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D133" s="9">
         <v>2110302.0</v>
@@ -5339,20 +5339,20 @@
       <c r="J133" s="12"/>
     </row>
     <row r="134" ht="22.5" hidden="1" customHeight="1">
-      <c r="A134" s="5">
+      <c r="A134" s="4">
         <v>46259.0</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D134" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F134" s="9">
         <v>18000.0</v>
@@ -5364,21 +5364,21 @@
         <v>11510.0</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J134" s="12" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="135" ht="22.5" hidden="1" customHeight="1">
-      <c r="A135" s="5">
+      <c r="A135" s="4">
         <v>46259.0</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C135" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D135" s="9">
         <v>2110302.0</v>
@@ -5396,20 +5396,20 @@
         <v>105048.0</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J135" s="12" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="136" ht="22.5" hidden="1" customHeight="1">
-      <c r="A136" s="5">
+      <c r="A136" s="4">
         <v>46260.0</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C136" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D136" s="9">
@@ -5428,27 +5428,27 @@
         <v>140840.0</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J136" s="12" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="137" ht="22.5" hidden="1" customHeight="1">
-      <c r="A137" s="5">
+      <c r="A137" s="4">
         <v>46260.0</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D137" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F137" s="9">
         <v>11510.0</v>
@@ -5467,14 +5467,14 @@
       </c>
     </row>
     <row r="138" ht="22.5" hidden="1" customHeight="1">
-      <c r="A138" s="5">
+      <c r="A138" s="4">
         <v>46260.0</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C138" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D138" s="9">
         <v>2110302.0</v>
@@ -5492,27 +5492,27 @@
         <v>107298.0</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J138" s="12" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="139" ht="22.5" hidden="1" customHeight="1">
-      <c r="A139" s="5">
+      <c r="A139" s="4">
         <v>46260.0</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C139" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>187</v>
       </c>
       <c r="D139" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F139" s="9">
         <v>30600.0</v>
@@ -5537,7 +5537,7 @@
       <c r="B140" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" s="8" t="s">
         <v>195</v>
       </c>
       <c r="D140" s="9">
@@ -5555,8 +5555,8 @@
       <c r="H140" s="9">
         <v>22800.0</v>
       </c>
-      <c r="I140" s="10" t="s">
-        <v>15</v>
+      <c r="I140" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="J140" s="12"/>
     </row>
@@ -5565,9 +5565,9 @@
         <v>46261.0</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C141" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C141" s="8" t="s">
         <v>196</v>
       </c>
       <c r="D141" s="9">
@@ -5585,8 +5585,8 @@
       <c r="H141" s="9">
         <v>283680.0</v>
       </c>
-      <c r="I141" s="10" t="s">
-        <v>15</v>
+      <c r="I141" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="J141" s="12"/>
     </row>
@@ -5597,7 +5597,7 @@
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="8" t="s">
         <v>197</v>
       </c>
       <c r="D142" s="9">
@@ -5615,7 +5615,7 @@
       <c r="H142" s="9">
         <v>91680.0</v>
       </c>
-      <c r="I142" s="10" t="s">
+      <c r="I142" s="11" t="s">
         <v>23</v>
       </c>
       <c r="J142" s="12"/>
@@ -5627,14 +5627,14 @@
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D143" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F143" s="9">
         <v>10260.0</v>
@@ -5645,7 +5645,7 @@
       <c r="H143" s="9">
         <v>7860.0</v>
       </c>
-      <c r="I143" s="10" t="s">
+      <c r="I143" s="11" t="s">
         <v>23</v>
       </c>
       <c r="J143" s="12"/>
@@ -5655,16 +5655,16 @@
         <v>46262.0</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C144" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D144" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F144" s="9">
         <v>10500.0</v>
@@ -5676,7 +5676,7 @@
         <v>12930.0</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J144" s="12"/>
     </row>
@@ -5687,7 +5687,7 @@
       <c r="B145" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="8" t="s">
         <v>198</v>
       </c>
       <c r="D145" s="9">
@@ -5713,20 +5713,20 @@
       </c>
     </row>
     <row r="146" ht="22.5" hidden="1" customHeight="1">
-      <c r="A146" s="5">
+      <c r="A146" s="4">
         <v>46265.0</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C146" s="7" t="s">
-        <v>155</v>
+      <c r="C146" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="D146" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F146" s="9">
         <v>17970.0</v>
@@ -5738,25 +5738,25 @@
         <v>7020.0</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J146" s="12"/>
     </row>
     <row r="147" ht="22.5" hidden="1" customHeight="1">
-      <c r="A147" s="5">
+      <c r="A147" s="4">
         <v>46265.0</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C147" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D147" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F147" s="9">
         <v>9960.0</v>
@@ -5773,20 +5773,20 @@
       <c r="J147" s="12"/>
     </row>
     <row r="148" ht="22.5" hidden="1" customHeight="1">
-      <c r="A148" s="5">
+      <c r="A148" s="4">
         <v>46265.0</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C148" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>200</v>
       </c>
       <c r="D148" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F148" s="9">
         <v>10503.0</v>
@@ -5798,27 +5798,27 @@
         <v>9063.0</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J148" s="12" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="149" ht="22.5" hidden="1" customHeight="1">
-      <c r="A149" s="5">
+      <c r="A149" s="4">
         <v>46266.0</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C149" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D149" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F149" s="9">
         <v>339300.0</v>
@@ -5830,27 +5830,27 @@
         <v>349380.0</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J149" s="12" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="150" ht="22.5" hidden="1" customHeight="1">
-      <c r="A150" s="5">
+      <c r="A150" s="4">
         <v>46266.0</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="C150" s="8" t="s">
         <v>203</v>
       </c>
       <c r="D150" s="9">
         <v>152384.0</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F150" s="9">
         <v>17100.0</v>
@@ -5862,25 +5862,25 @@
         <v>8700.0</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J150" s="12"/>
     </row>
     <row r="151" ht="22.5" hidden="1" customHeight="1">
-      <c r="A151" s="5">
+      <c r="A151" s="4">
         <v>46266.0</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D151" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F151" s="9">
         <v>3240.0</v>
@@ -5892,27 +5892,27 @@
         <v>2505.0</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="152" ht="22.5" hidden="1" customHeight="1">
-      <c r="A152" s="5">
+      <c r="A152" s="4">
         <v>46267.0</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C152" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D152" s="9">
         <v>152384.0</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F152" s="9">
         <v>25350.0</v>
@@ -5931,20 +5931,20 @@
       </c>
     </row>
     <row r="153" ht="22.5" hidden="1" customHeight="1">
-      <c r="A153" s="5">
+      <c r="A153" s="4">
         <v>46267.0</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="D153" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F153" s="9">
         <v>15660.0</v>
@@ -5963,20 +5963,20 @@
       </c>
     </row>
     <row r="154" ht="22.5" hidden="1" customHeight="1">
-      <c r="A154" s="5">
+      <c r="A154" s="4">
         <v>46267.0</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D154" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F154" s="9">
         <v>8280.0</v>
@@ -5988,27 +5988,27 @@
         <v>3375.0</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J154" s="12" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="155" ht="22.5" hidden="1" customHeight="1">
-      <c r="A155" s="5">
+      <c r="A155" s="4">
         <v>46268.0</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="C155" s="8" t="s">
         <v>208</v>
       </c>
       <c r="D155" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F155" s="9">
         <v>205020.0</v>
@@ -6027,20 +6027,20 @@
       </c>
     </row>
     <row r="156" ht="22.5" hidden="1" customHeight="1">
-      <c r="A156" s="5">
+      <c r="A156" s="4">
         <v>46268.0</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C156" s="7" t="s">
+      <c r="C156" s="8" t="s">
         <v>208</v>
       </c>
       <c r="D156" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F156" s="9">
         <v>7920.0</v>
@@ -6059,20 +6059,20 @@
       </c>
     </row>
     <row r="157" ht="22.5" hidden="1" customHeight="1">
-      <c r="A157" s="5">
+      <c r="A157" s="4">
         <v>46268.0</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C157" s="7" t="s">
+      <c r="C157" s="8" t="s">
         <v>208</v>
       </c>
       <c r="D157" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F157" s="9">
         <v>18240.0</v>
@@ -6084,27 +6084,27 @@
         <v>12240.0</v>
       </c>
       <c r="I157" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J157" s="12" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="158" ht="22.5" hidden="1" customHeight="1">
-      <c r="A158" s="5">
+      <c r="A158" s="4">
         <v>46269.0</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C158" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D158" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F158" s="9">
         <v>287280.0</v>
@@ -6123,14 +6123,14 @@
       </c>
     </row>
     <row r="159" ht="22.5" hidden="1" customHeight="1">
-      <c r="A159" s="5">
+      <c r="A159" s="4">
         <v>46269.0</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C159" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D159" s="9">
         <v>2112207.0</v>
@@ -6148,18 +6148,18 @@
         <v>8040.0</v>
       </c>
       <c r="I159" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J159" s="12"/>
     </row>
     <row r="160" ht="22.5" hidden="1" customHeight="1">
-      <c r="A160" s="5">
+      <c r="A160" s="4">
         <v>46269.0</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C160" s="8" t="s">
         <v>213</v>
       </c>
       <c r="D160" s="9">
@@ -6185,20 +6185,20 @@
       </c>
     </row>
     <row r="161" ht="22.5" hidden="1" customHeight="1">
-      <c r="A161" s="5">
+      <c r="A161" s="4">
         <v>46269.0</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C161" s="7" t="s">
+      <c r="C161" s="8" t="s">
         <v>213</v>
       </c>
       <c r="D161" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F161" s="9">
         <v>8457.0</v>
@@ -6217,14 +6217,14 @@
       </c>
     </row>
     <row r="162" ht="22.5" hidden="1" customHeight="1">
-      <c r="A162" s="5">
+      <c r="A162" s="4">
         <v>46272.0</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C162" s="7" t="s">
         <v>49</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="D162" s="9">
         <v>2110302.0</v>
@@ -6242,27 +6242,27 @@
         <v>40143.0</v>
       </c>
       <c r="I162" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J162" s="12" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="163" ht="22.5" hidden="1" customHeight="1">
-      <c r="A163" s="5">
+      <c r="A163" s="4">
         <v>46273.0</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C163" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D163" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F163" s="9">
         <v>345572.0</v>
@@ -6274,27 +6274,27 @@
         <v>444960.0</v>
       </c>
       <c r="I163" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J163" s="12" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="164" ht="22.5" hidden="1" customHeight="1">
-      <c r="A164" s="5">
+      <c r="A164" s="4">
         <v>46273.0</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C164" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D164" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F164" s="9">
         <v>21960.0</v>
@@ -6306,27 +6306,27 @@
         <v>18330.0</v>
       </c>
       <c r="I164" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J164" s="12" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="165" ht="22.5" hidden="1" customHeight="1">
-      <c r="A165" s="5">
+      <c r="A165" s="4">
         <v>46273.0</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C165" s="7" t="s">
+      <c r="C165" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D165" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F165" s="9">
         <v>35040.0</v>
@@ -6338,20 +6338,20 @@
         <v>21840.0</v>
       </c>
       <c r="I165" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J165" s="12" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="166" ht="22.5" hidden="1" customHeight="1">
-      <c r="A166" s="5">
+      <c r="A166" s="4">
         <v>46273.0</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C166" s="7" t="s">
+      <c r="C166" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D166" s="9">
@@ -6375,20 +6375,20 @@
       <c r="J166" s="12"/>
     </row>
     <row r="167" ht="22.5" hidden="1" customHeight="1">
-      <c r="A167" s="5">
+      <c r="A167" s="4">
         <v>46273.0</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C167" s="7" t="s">
+      <c r="C167" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D167" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F167" s="9">
         <v>10620.0</v>
@@ -6400,20 +6400,20 @@
         <v>8460.0</v>
       </c>
       <c r="I167" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J167" s="12" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="168" ht="22.5" hidden="1" customHeight="1">
-      <c r="A168" s="5">
+      <c r="A168" s="4">
         <v>46273.0</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C168" s="7" t="s">
+      <c r="C168" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D168" s="9">
@@ -6432,21 +6432,21 @@
         <v>123360.0</v>
       </c>
       <c r="I168" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J168" s="12" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="169" ht="22.5" hidden="1" customHeight="1">
-      <c r="A169" s="5">
+      <c r="A169" s="4">
         <v>46274.0</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C169" s="7" t="s">
-        <v>59</v>
+      <c r="C169" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D169" s="9">
         <v>2110302.0</v>
@@ -6464,27 +6464,27 @@
         <v>151680.0</v>
       </c>
       <c r="I169" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J169" s="12" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="170" ht="22.5" hidden="1" customHeight="1">
-      <c r="A170" s="5">
+      <c r="A170" s="4">
         <v>46274.0</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C170" s="7" t="s">
-        <v>59</v>
+      <c r="C170" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D170" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F170" s="9">
         <v>8460.0</v>
@@ -6501,13 +6501,13 @@
       <c r="J170" s="12"/>
     </row>
     <row r="171" ht="22.5" hidden="1" customHeight="1">
-      <c r="A171" s="5">
+      <c r="A171" s="4">
         <v>46274.0</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C171" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D171" s="9">
@@ -6533,20 +6533,20 @@
       </c>
     </row>
     <row r="172" ht="22.5" hidden="1" customHeight="1">
-      <c r="A172" s="5">
+      <c r="A172" s="4">
         <v>46274.0</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C172" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D172" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F172" s="9">
         <v>18330.0</v>
@@ -6569,16 +6569,16 @@
         <v>46275.0</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C173" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D173" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F173" s="9">
         <v>340260.0</v>
@@ -6601,16 +6601,16 @@
         <v>46275.0</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C174" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D174" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F174" s="9">
         <v>52453.0</v>
@@ -6633,16 +6633,16 @@
         <v>46275.0</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C175" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D175" s="9">
         <v>152384.0</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F175" s="9">
         <v>18585.0</v>
@@ -6686,7 +6686,7 @@
         <v>67680.0</v>
       </c>
       <c r="I176" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J176" s="12" t="s">
         <v>224</v>
@@ -6706,7 +6706,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F177" s="9">
         <v>23520.0</v>
@@ -6718,27 +6718,27 @@
         <v>18480.0</v>
       </c>
       <c r="I177" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J177" s="12" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="178" ht="22.5" hidden="1" customHeight="1">
-      <c r="A178" s="5">
+      <c r="A178" s="4">
         <v>46276.0</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C178" s="7" t="s">
+      <c r="C178" s="8" t="s">
         <v>134</v>
       </c>
       <c r="D178" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F178" s="9">
         <v>2130.0</v>
@@ -6750,25 +6750,25 @@
         <v>1740.0</v>
       </c>
       <c r="I178" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J178" s="12"/>
     </row>
     <row r="179" ht="22.5" hidden="1" customHeight="1">
-      <c r="A179" s="5">
+      <c r="A179" s="4">
         <v>46276.0</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C179" s="7" t="s">
-        <v>155</v>
+      <c r="C179" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="D179" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F179" s="9">
         <v>456945.0</v>
@@ -6787,20 +6787,20 @@
       </c>
     </row>
     <row r="180" ht="22.5" hidden="1" customHeight="1">
-      <c r="A180" s="5">
+      <c r="A180" s="4">
         <v>46280.0</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C180" s="7" t="s">
+      <c r="C180" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D180" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F180" s="9">
         <v>653620.0</v>
@@ -6812,18 +6812,18 @@
         <v>382568.0</v>
       </c>
       <c r="I180" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J180" s="12"/>
     </row>
     <row r="181" ht="22.5" hidden="1" customHeight="1">
-      <c r="A181" s="5">
+      <c r="A181" s="4">
         <v>46280.0</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C181" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C181" s="8" t="s">
         <v>196</v>
       </c>
       <c r="D181" s="9">
@@ -6842,25 +6842,25 @@
         <v>255600.0</v>
       </c>
       <c r="I181" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J181" s="12"/>
     </row>
     <row r="182" ht="22.5" hidden="1" customHeight="1">
-      <c r="A182" s="5">
+      <c r="A182" s="4">
         <v>46281.0</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C182" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D182" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F182" s="9">
         <v>13800.0</v>
@@ -6877,20 +6877,20 @@
       <c r="J182" s="12"/>
     </row>
     <row r="183" ht="22.5" hidden="1" customHeight="1">
-      <c r="A183" s="5">
+      <c r="A183" s="4">
         <v>46281.0</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C183" s="7" t="s">
-        <v>59</v>
+      <c r="C183" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D183" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F183" s="9">
         <v>226980.0</v>
@@ -6913,16 +6913,16 @@
         <v>46282.0</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C184" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D184" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F184" s="9">
         <v>616880.0</v>
@@ -6934,7 +6934,7 @@
         <v>515700.0</v>
       </c>
       <c r="I184" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J184" s="12" t="s">
         <v>216</v>
@@ -6947,14 +6947,14 @@
       <c r="B185" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="7" t="s">
+      <c r="C185" s="8" t="s">
         <v>185</v>
       </c>
       <c r="D185" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F185" s="9">
         <v>118254.0</v>
@@ -6979,14 +6979,14 @@
       <c r="B186" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C186" s="7" t="s">
-        <v>59</v>
+      <c r="C186" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D186" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F186" s="9">
         <v>187100.0</v>
@@ -7011,8 +7011,8 @@
       <c r="B187" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C187" s="7" t="s">
-        <v>59</v>
+      <c r="C187" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D187" s="9">
         <v>2110302.0</v>
@@ -7041,16 +7041,16 @@
         <v>46282.0</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C188" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D188" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F188" s="9">
         <v>16680.0</v>
@@ -7069,13 +7069,13 @@
       </c>
     </row>
     <row r="189" ht="22.5" hidden="1" customHeight="1">
-      <c r="A189" s="5">
+      <c r="A189" s="4">
         <v>46283.0</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C189" s="7" t="s">
+      <c r="C189" s="8" t="s">
         <v>231</v>
       </c>
       <c r="D189" s="9">
@@ -7099,20 +7099,20 @@
       <c r="J189" s="12"/>
     </row>
     <row r="190" ht="22.5" hidden="1" customHeight="1">
-      <c r="A190" s="5">
+      <c r="A190" s="4">
         <v>46283.0</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C190" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D190" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F190" s="9">
         <v>13320.0</v>
@@ -7124,27 +7124,27 @@
         <v>14400.0</v>
       </c>
       <c r="I190" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J190" s="12" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="191" ht="22.5" hidden="1" customHeight="1">
-      <c r="A191" s="5">
+      <c r="A191" s="4">
         <v>46286.0</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C191" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D191" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F191" s="9">
         <v>535680.0</v>
@@ -7161,13 +7161,13 @@
       <c r="J191" s="12"/>
     </row>
     <row r="192" ht="22.5" hidden="1" customHeight="1">
-      <c r="A192" s="5">
+      <c r="A192" s="4">
         <v>46286.0</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C192" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D192" s="9">
@@ -7186,20 +7186,20 @@
         <v>128520.0</v>
       </c>
       <c r="I192" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J192" s="12" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="193" ht="22.5" hidden="1" customHeight="1">
-      <c r="A193" s="5">
+      <c r="A193" s="4">
         <v>46286.0</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C193" s="7" t="s">
+      <c r="C193" s="8" t="s">
         <v>197</v>
       </c>
       <c r="D193" s="9">
@@ -7218,25 +7218,25 @@
         <v>27300.0</v>
       </c>
       <c r="I193" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J193" s="12"/>
     </row>
     <row r="194" ht="22.5" hidden="1" customHeight="1">
-      <c r="A194" s="5">
+      <c r="A194" s="4">
         <v>46287.0</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C194" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D194" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F194" s="9">
         <v>60450.0</v>
@@ -7248,20 +7248,20 @@
         <v>47040.0</v>
       </c>
       <c r="I194" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J194" s="12" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="195" ht="22.5" hidden="1" customHeight="1">
-      <c r="A195" s="5">
+      <c r="A195" s="4">
         <v>46287.0</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C195" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D195" s="9">
@@ -7285,20 +7285,20 @@
       <c r="J195" s="12"/>
     </row>
     <row r="196" ht="22.5" hidden="1" customHeight="1">
-      <c r="A196" s="5">
+      <c r="A196" s="4">
         <v>46287.0</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C196" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D196" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F196" s="9">
         <v>19260.0</v>
@@ -7315,20 +7315,20 @@
       <c r="J196" s="12"/>
     </row>
     <row r="197" ht="22.5" hidden="1" customHeight="1">
-      <c r="A197" s="5">
+      <c r="A197" s="4">
         <v>46287.0</v>
       </c>
       <c r="B197" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C197" s="7" t="s">
+      <c r="C197" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D197" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F197" s="9">
         <v>18240.0</v>
@@ -7340,21 +7340,21 @@
         <v>15360.0</v>
       </c>
       <c r="I197" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J197" s="12" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="198" ht="22.5" hidden="1" customHeight="1">
-      <c r="A198" s="5">
+      <c r="A198" s="4">
         <v>46288.0</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C198" s="7" t="s">
         <v>19</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D198" s="9">
         <v>2110302.0</v>
@@ -7372,27 +7372,27 @@
         <v>13655.0</v>
       </c>
       <c r="I198" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J198" s="12" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="199" ht="22.5" hidden="1" customHeight="1">
-      <c r="A199" s="5">
+      <c r="A199" s="4">
         <v>46288.0</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C199" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D199" s="9">
         <v>152384.0</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F199" s="9">
         <v>40980.0</v>
@@ -7409,13 +7409,13 @@
       <c r="J199" s="12"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
-      <c r="A200" s="5">
+      <c r="A200" s="4">
         <v>46289.0</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C200" s="7" t="s">
+      <c r="C200" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D200" s="9">
@@ -7434,25 +7434,25 @@
         <v>13500.0</v>
       </c>
       <c r="I200" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J200" s="12"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
-      <c r="A201" s="5">
+      <c r="A201" s="4">
         <v>46289.0</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C201" s="7" t="s">
+      <c r="C201" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D201" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F201" s="9">
         <v>16320.0</v>
@@ -7464,25 +7464,25 @@
         <v>19200.0</v>
       </c>
       <c r="I201" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J201" s="12"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
-      <c r="A202" s="5">
+      <c r="A202" s="4">
         <v>46289.0</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C202" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D202" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F202" s="9">
         <v>342500.0</v>
@@ -7494,20 +7494,20 @@
         <v>252670.0</v>
       </c>
       <c r="I202" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J202" s="12" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="203" ht="22.5" customHeight="1">
-      <c r="A203" s="5">
+      <c r="A203" s="4">
         <v>46289.0</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C203" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D203" s="9">
@@ -7526,27 +7526,27 @@
         <v>90198.0</v>
       </c>
       <c r="I203" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J203" s="12" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="204" ht="22.5" customHeight="1">
-      <c r="A204" s="5">
+      <c r="A204" s="4">
         <v>46289.0</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C204" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D204" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F204" s="9">
         <v>16830.0</v>
@@ -7558,25 +7558,25 @@
         <v>6600.0</v>
       </c>
       <c r="I204" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J204" s="12"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
-      <c r="A205" s="5">
+      <c r="A205" s="4">
         <v>46290.0</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="D205" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F205" s="9">
         <v>7740.0</v>
@@ -7588,18 +7588,18 @@
         <v>4320.0</v>
       </c>
       <c r="I205" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J205" s="12"/>
     </row>
     <row r="206" ht="22.5" customHeight="1">
-      <c r="A206" s="5">
+      <c r="A206" s="4">
         <v>46290.0</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C206" s="7" t="s">
+      <c r="C206" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D206" s="9">
@@ -7625,20 +7625,20 @@
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
-      <c r="A207" s="5">
+      <c r="A207" s="4">
         <v>46290.0</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C207" s="7" t="s">
+      <c r="C207" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D207" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F207" s="9">
         <v>252000.0</v>
@@ -7657,20 +7657,20 @@
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
-      <c r="A208" s="5">
+      <c r="A208" s="4">
         <v>46290.0</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C208" s="7" t="s">
+      <c r="C208" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D208" s="9">
         <v>152384.0</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F208" s="9">
         <v>10200.0</v>
@@ -7689,13 +7689,13 @@
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
-      <c r="A209" s="5">
+      <c r="A209" s="4">
         <v>46290.0</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C209" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C209" s="8" t="s">
         <v>240</v>
       </c>
       <c r="D209" s="9">
@@ -7719,20 +7719,20 @@
       <c r="J209" s="12"/>
     </row>
     <row r="210" ht="22.5" customHeight="1">
-      <c r="A210" s="5">
+      <c r="A210" s="4">
         <v>46290.0</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C210" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D210" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F210" s="9">
         <v>252670.0</v>
@@ -7744,25 +7744,25 @@
         <v>360960.0</v>
       </c>
       <c r="I210" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J210" s="12"/>
     </row>
     <row r="211" ht="22.5" customHeight="1">
-      <c r="A211" s="5">
+      <c r="A211" s="4">
         <v>46290.0</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C211" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D211" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F211" s="9">
         <v>4785.0</v>
@@ -7774,27 +7774,27 @@
         <v>4425.0</v>
       </c>
       <c r="I211" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J211" s="12" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
-      <c r="A212" s="5">
+      <c r="A212" s="4">
         <v>46290.0</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C212" s="7" t="s">
+      <c r="C212" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D212" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F212" s="9">
         <v>264019.0</v>
@@ -7812,8 +7812,37 @@
         <v>242</v>
       </c>
     </row>
-    <row r="213">
-      <c r="I213" s="23"/>
+    <row r="213" ht="22.5" customHeight="1">
+      <c r="A213" s="18">
+        <v>46293.0</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D213" s="9">
+        <v>2110302.0</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F213" s="9">
+        <v>203400.0</v>
+      </c>
+      <c r="G213" s="9">
+        <v>155588.0</v>
+      </c>
+      <c r="H213" s="9">
+        <v>414900.0</v>
+      </c>
+      <c r="I213" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="214">
       <c r="I214" s="23"/>
@@ -10199,13 +10228,13 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I212">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I213">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I213:I1007">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I214:I1007">
       <formula1>"1. Ingreso Por Devolución,2. Error De Registro De Inventario,3. Falla De Rotación,4. Exigencia Del Cliente (Edad),5. Ingreso De Planta,6. Transformación De Referencias,7. Otro"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A212">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A2:A213">
       <formula1>OR(NOT(ISERROR(DATEVALUE(A2))), AND(ISNUMBER(A2), LEFT(CELL("format", A2))="D"))</formula1>
     </dataValidation>
   </dataValidations>
@@ -10268,18 +10297,18 @@
       </c>
     </row>
     <row r="2" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46224.0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="C2" s="7"/>
       <c r="D2" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="9">
         <v>333.0</v>
@@ -10290,21 +10319,21 @@
       <c r="H2" s="9">
         <v>3712.0</v>
       </c>
-      <c r="I2" s="11" t="s">
-        <v>16</v>
+      <c r="I2" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="4">
         <v>46224.0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8"/>
+        <v>18</v>
+      </c>
+      <c r="C3" s="7"/>
       <c r="D3" s="9">
         <v>2114158.0</v>
       </c>
@@ -10320,7 +10349,7 @@
       <c r="H3" s="9">
         <v>60.0</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="12" t="s">
@@ -10328,11 +10357,11 @@
       </c>
     </row>
     <row r="4" ht="22.5" hidden="1" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>46225.0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="9">
@@ -10350,7 +10379,7 @@
       <c r="H4" s="9">
         <v>543038.0</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J4" s="12" t="s">
@@ -10358,11 +10387,11 @@
       </c>
     </row>
     <row r="5" ht="22.5" hidden="1" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>46225.0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="9">
@@ -10380,19 +10409,19 @@
       <c r="H5" s="9">
         <v>3000.0</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>16</v>
+      <c r="I5" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="22.5" hidden="1" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>46225.0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="9">
@@ -10410,26 +10439,26 @@
       <c r="H6" s="9">
         <v>3300.0</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>16</v>
+      <c r="I6" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" hidden="1" customHeight="1">
+      <c r="A7" s="4">
+        <v>46225.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" hidden="1" customHeight="1">
-      <c r="A7" s="5">
-        <v>46225.0</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="9">
         <v>132357.0</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="9">
         <v>1560.0</v>
@@ -10440,26 +10469,26 @@
       <c r="H7" s="9">
         <v>4560.0</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>16</v>
+      <c r="I7" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="22.5" hidden="1" customHeight="1">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>46225.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="9">
         <v>720.0</v>
@@ -10470,26 +10499,26 @@
       <c r="H8" s="9">
         <v>5940.0</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>16</v>
+      <c r="I8" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="22.5" hidden="1" customHeight="1">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>46225.0</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="9">
         <v>3712.0</v>
@@ -10500,26 +10529,26 @@
       <c r="H9" s="9">
         <v>213.0</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>16</v>
+      <c r="I9" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="22.5" hidden="1" customHeight="1">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>46226.0</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="9">
         <v>73001.0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10" s="9">
         <v>73787.0</v>
@@ -10530,19 +10559,19 @@
       <c r="H10" s="9">
         <v>109487.0</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>16</v>
+      <c r="I10" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" ht="22.5" hidden="1" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>46226.0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="9">
@@ -10560,17 +10589,17 @@
       <c r="H11" s="9">
         <v>3300.0</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="12"/>
     </row>
     <row r="12" ht="22.5" hidden="1" customHeight="1">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>46226.0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="9">
@@ -10588,24 +10617,24 @@
       <c r="H12" s="9">
         <v>3900.0</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J12" s="12"/>
     </row>
     <row r="13" ht="22.5" hidden="1" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>46226.0</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="9">
         <v>379471.0</v>
@@ -10616,26 +10645,26 @@
       <c r="H13" s="9">
         <v>357186.0</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>16</v>
+      <c r="I13" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" ht="22.5" hidden="1" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>46227.0</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="9">
         <v>72001.0</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F14" s="9">
         <v>21905.0</v>
@@ -10646,26 +10675,26 @@
       <c r="H14" s="9">
         <v>38000.0</v>
       </c>
-      <c r="I14" s="11" t="s">
-        <v>16</v>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" ht="22.5" hidden="1" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>46227.0</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="9">
         <v>2110327.0</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F15" s="9">
         <v>69120.0</v>
@@ -10676,19 +10705,19 @@
       <c r="H15" s="9">
         <v>40320.0</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>16</v>
+      <c r="I15" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22.5" hidden="1" customHeight="1">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>46227.0</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="9">
@@ -10706,24 +10735,24 @@
       <c r="H16" s="9">
         <v>1500.0</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="12"/>
     </row>
     <row r="17" ht="22.5" hidden="1" customHeight="1">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>46227.0</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F17" s="9">
         <v>720.0</v>
@@ -10734,17 +10763,17 @@
       <c r="H17" s="9">
         <v>2580.0</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J17" s="12"/>
     </row>
     <row r="18" ht="22.5" hidden="1" customHeight="1">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>46227.0</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="9">
@@ -10762,26 +10791,26 @@
       <c r="H18" s="9">
         <v>600.0</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
+      <c r="I18" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="22.5" hidden="1" customHeight="1">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>46230.0</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" s="9">
         <v>136538.0</v>
@@ -10792,26 +10821,26 @@
       <c r="H19" s="9">
         <v>213000.0</v>
       </c>
-      <c r="I19" s="11" t="s">
-        <v>16</v>
+      <c r="I19" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J19" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="20" ht="22.5" hidden="1" customHeight="1">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>46231.0</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="9">
         <v>591750.0</v>
@@ -10822,19 +10851,19 @@
       <c r="H20" s="9">
         <v>577207.0</v>
       </c>
-      <c r="I20" s="11" t="s">
-        <v>16</v>
+      <c r="I20" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="21" ht="22.5" hidden="1" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <v>46231.0</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="9">
@@ -10852,26 +10881,26 @@
       <c r="H21" s="9">
         <v>1958.0</v>
       </c>
-      <c r="I21" s="11" t="s">
-        <v>16</v>
+      <c r="I21" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22" ht="22.5" hidden="1" customHeight="1">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>46231.0</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" s="9">
         <v>4320.0</v>
@@ -10882,17 +10911,17 @@
       <c r="H22" s="9">
         <v>3420.0</v>
       </c>
-      <c r="I22" s="11" t="s">
-        <v>16</v>
+      <c r="I22" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J22" s="12"/>
     </row>
     <row r="23" ht="22.5" hidden="1" customHeight="1">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <v>46231.0</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="9">
@@ -10910,17 +10939,17 @@
       <c r="H23" s="9">
         <v>240.0</v>
       </c>
-      <c r="I23" s="11" t="s">
-        <v>16</v>
+      <c r="I23" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J23" s="12"/>
     </row>
     <row r="24" ht="22.5" hidden="1" customHeight="1">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <v>46232.0</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="9">
@@ -10938,17 +10967,17 @@
       <c r="H24" s="9">
         <v>29632.0</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>16</v>
+      <c r="I24" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J24" s="12"/>
     </row>
     <row r="25" ht="22.5" hidden="1" customHeight="1">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <v>46232.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="9">
@@ -10966,24 +10995,24 @@
       <c r="H25" s="9">
         <v>5100.0</v>
       </c>
-      <c r="I25" s="11" t="s">
-        <v>16</v>
+      <c r="I25" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J25" s="12"/>
     </row>
     <row r="26" ht="22.5" hidden="1" customHeight="1">
-      <c r="A26" s="5">
+      <c r="A26" s="4">
         <v>46232.0</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F26" s="9">
         <v>720.0</v>
@@ -10994,17 +11023,17 @@
       <c r="H26" s="9">
         <v>720.0</v>
       </c>
-      <c r="I26" s="11" t="s">
-        <v>16</v>
+      <c r="I26" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J26" s="12"/>
     </row>
     <row r="27" ht="22.5" hidden="1" customHeight="1">
-      <c r="A27" s="5">
+      <c r="A27" s="4">
         <v>46232.0</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="9">
@@ -11022,17 +11051,17 @@
       <c r="H27" s="9">
         <v>432.0</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>16</v>
+      <c r="I27" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J27" s="12"/>
     </row>
     <row r="28" ht="22.5" hidden="1" customHeight="1">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>46232.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="9">
@@ -11050,17 +11079,17 @@
       <c r="H28" s="9">
         <v>16698.0</v>
       </c>
-      <c r="I28" s="11" t="s">
-        <v>16</v>
+      <c r="I28" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J28" s="12"/>
     </row>
     <row r="29" ht="22.5" hidden="1" customHeight="1">
-      <c r="A29" s="5">
+      <c r="A29" s="4">
         <v>46233.0</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="9">
@@ -11078,17 +11107,17 @@
       <c r="H29" s="9">
         <v>4800.0</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>34</v>
+      <c r="I29" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J29" s="12"/>
     </row>
     <row r="30" ht="22.5" hidden="1" customHeight="1">
-      <c r="A30" s="5">
+      <c r="A30" s="4">
         <v>46233.0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9">
@@ -11106,13 +11135,13 @@
       <c r="H30" s="9">
         <v>1560.0</v>
       </c>
-      <c r="I30" s="11" t="s">
-        <v>34</v>
+      <c r="I30" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J30" s="12"/>
     </row>
     <row r="31" ht="22.5" hidden="1" customHeight="1">
-      <c r="A31" s="5">
+      <c r="A31" s="4">
         <v>46233.0</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -11134,15 +11163,15 @@
       <c r="H31" s="9">
         <v>12867.0</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>16</v>
+      <c r="I31" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J31" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" ht="22.5" hidden="1" customHeight="1">
-      <c r="A32" s="5">
+      <c r="A32" s="4">
         <v>46234.0</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -11164,7 +11193,7 @@
       <c r="H32" s="9">
         <v>36300.0</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J32" s="17" t="s">
@@ -11172,11 +11201,11 @@
       </c>
     </row>
     <row r="33" ht="22.5" hidden="1" customHeight="1">
-      <c r="A33" s="5">
+      <c r="A33" s="4">
         <v>46234.0</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="9">
@@ -11194,26 +11223,26 @@
       <c r="H33" s="9">
         <v>142801.0</v>
       </c>
-      <c r="I33" s="11" t="s">
-        <v>16</v>
+      <c r="I33" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="34" ht="22.5" hidden="1" customHeight="1">
-      <c r="A34" s="5">
+      <c r="A34" s="4">
         <v>46234.0</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="9">
         <v>73001.0</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F34" s="9">
         <v>73367.0</v>
@@ -11224,17 +11253,17 @@
       <c r="H34" s="9">
         <v>39150.0</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>16</v>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J34" s="12"/>
     </row>
     <row r="35" ht="22.5" hidden="1" customHeight="1">
-      <c r="A35" s="5">
+      <c r="A35" s="4">
         <v>46234.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="9">
@@ -11252,8 +11281,8 @@
       <c r="H35" s="9">
         <v>480.0</v>
       </c>
-      <c r="I35" s="11" t="s">
-        <v>16</v>
+      <c r="I35" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J35" s="12"/>
     </row>
@@ -11262,7 +11291,7 @@
         <v>46237.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="9">
@@ -11280,8 +11309,8 @@
       <c r="H36" s="9">
         <v>21714.0</v>
       </c>
-      <c r="I36" s="11" t="s">
-        <v>16</v>
+      <c r="I36" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>91</v>
@@ -11292,14 +11321,14 @@
         <v>46237.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C37" s="14"/>
       <c r="D37" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F37" s="9">
         <v>194520.0</v>
@@ -11310,7 +11339,7 @@
       <c r="H37" s="9">
         <v>122840.0</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="12"/>
@@ -11320,7 +11349,7 @@
         <v>46237.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="9">
@@ -11338,8 +11367,8 @@
       <c r="H38" s="9">
         <v>7500.0</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>34</v>
+      <c r="I38" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J38" s="12"/>
     </row>
@@ -11348,14 +11377,14 @@
         <v>46237.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C39" s="14"/>
       <c r="D39" s="9">
         <v>2110317.0</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F39" s="9">
         <v>6450.0</v>
@@ -11366,7 +11395,7 @@
       <c r="H39" s="9">
         <v>6480.0</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J39" s="12"/>
@@ -11376,14 +11405,14 @@
         <v>46237.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F40" s="9">
         <v>1398.0</v>
@@ -11394,24 +11423,24 @@
       <c r="H40" s="9">
         <v>438.0</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J40" s="12"/>
     </row>
     <row r="41" ht="22.5" hidden="1" customHeight="1">
-      <c r="A41" s="5">
+      <c r="A41" s="4">
         <v>46238.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="9">
         <v>2460.0</v>
@@ -11422,17 +11451,17 @@
       <c r="H41" s="9">
         <v>3240.0</v>
       </c>
-      <c r="I41" s="11" t="s">
-        <v>15</v>
+      <c r="I41" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J41" s="12"/>
     </row>
     <row r="42" ht="22.5" hidden="1" customHeight="1">
-      <c r="A42" s="5">
+      <c r="A42" s="4">
         <v>46238.0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="9">
@@ -11450,17 +11479,17 @@
       <c r="H42" s="9">
         <v>3900.0</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J42" s="12"/>
     </row>
     <row r="43" ht="22.5" hidden="1" customHeight="1">
-      <c r="A43" s="5">
+      <c r="A43" s="4">
         <v>46238.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="9">
@@ -11478,17 +11507,17 @@
       <c r="H43" s="9">
         <v>8400.0</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="12"/>
     </row>
     <row r="44" ht="22.5" hidden="1" customHeight="1">
-      <c r="A44" s="5">
+      <c r="A44" s="4">
         <v>46238.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C44" s="14"/>
       <c r="D44" s="9">
@@ -11506,13 +11535,13 @@
       <c r="H44" s="9">
         <v>360.0</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="12"/>
     </row>
     <row r="45" ht="22.5" hidden="1" customHeight="1">
-      <c r="A45" s="5">
+      <c r="A45" s="4">
         <v>46239.0</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -11534,19 +11563,19 @@
       <c r="H45" s="9">
         <v>1590.0</v>
       </c>
-      <c r="I45" s="11" t="s">
-        <v>16</v>
+      <c r="I45" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="46" ht="22.5" hidden="1" customHeight="1">
-      <c r="A46" s="5">
+      <c r="A46" s="4">
         <v>46239.0</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C46" s="14"/>
       <c r="D46" s="9">
@@ -11564,17 +11593,17 @@
       <c r="H46" s="9">
         <v>191130.0</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="12"/>
     </row>
     <row r="47" ht="22.5" hidden="1" customHeight="1">
-      <c r="A47" s="5">
+      <c r="A47" s="4">
         <v>46239.0</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="9">
@@ -11592,17 +11621,17 @@
       <c r="H47" s="9">
         <v>1980.0</v>
       </c>
-      <c r="I47" s="11" t="s">
-        <v>34</v>
+      <c r="I47" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J47" s="12"/>
     </row>
     <row r="48" ht="22.5" hidden="1" customHeight="1">
-      <c r="A48" s="5">
+      <c r="A48" s="4">
         <v>46239.0</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="9">
@@ -11620,17 +11649,17 @@
       <c r="H48" s="9">
         <v>1200.0</v>
       </c>
-      <c r="I48" s="11" t="s">
-        <v>34</v>
+      <c r="I48" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J48" s="12"/>
     </row>
     <row r="49" ht="22.5" hidden="1" customHeight="1">
-      <c r="A49" s="5">
+      <c r="A49" s="4">
         <v>46239.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="9">
@@ -11648,17 +11677,17 @@
       <c r="H49" s="9">
         <v>600.0</v>
       </c>
-      <c r="I49" s="11" t="s">
-        <v>34</v>
+      <c r="I49" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J49" s="12"/>
     </row>
     <row r="50" ht="22.5" hidden="1" customHeight="1">
-      <c r="A50" s="5">
+      <c r="A50" s="4">
         <v>46239.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="9">
@@ -11676,17 +11705,17 @@
       <c r="H50" s="9">
         <v>300.0</v>
       </c>
-      <c r="I50" s="11" t="s">
-        <v>34</v>
+      <c r="I50" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J50" s="12"/>
     </row>
     <row r="51" ht="22.5" hidden="1" customHeight="1">
-      <c r="A51" s="5">
+      <c r="A51" s="4">
         <v>46239.0</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="14"/>
       <c r="D51" s="9">
@@ -11704,26 +11733,26 @@
       <c r="H51" s="9">
         <v>13421.0</v>
       </c>
-      <c r="I51" s="11" t="s">
-        <v>16</v>
+      <c r="I51" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="52" ht="22.5" hidden="1" customHeight="1">
-      <c r="A52" s="5">
+      <c r="A52" s="4">
         <v>46239.0</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="9">
         <v>72003.0</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F52" s="9">
         <v>1391.0</v>
@@ -11734,24 +11763,24 @@
       <c r="H52" s="9">
         <v>2407.0</v>
       </c>
-      <c r="I52" s="11" t="s">
-        <v>15</v>
+      <c r="I52" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J52" s="12"/>
     </row>
     <row r="53" ht="22.5" hidden="1" customHeight="1">
-      <c r="A53" s="5">
+      <c r="A53" s="4">
         <v>46239.0</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F53" s="9">
         <v>2974.0</v>
@@ -11762,8 +11791,8 @@
       <c r="H53" s="9">
         <v>3317.0</v>
       </c>
-      <c r="I53" s="11" t="s">
-        <v>16</v>
+      <c r="I53" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J53" s="12" t="s">
         <v>110</v>
@@ -11774,7 +11803,7 @@
         <v>46240.0</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C54" s="14"/>
       <c r="D54" s="9">
@@ -11792,7 +11821,7 @@
       <c r="H54" s="9">
         <v>6900.0</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J54" s="12"/>
@@ -11802,14 +11831,14 @@
         <v>46240.0</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="9">
         <v>73001.0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F55" s="9">
         <v>2415.0</v>
@@ -11820,7 +11849,7 @@
       <c r="H55" s="9">
         <v>2415.0</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="12"/>
@@ -11830,7 +11859,7 @@
         <v>46240.0</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="9">
@@ -11848,7 +11877,7 @@
       <c r="H56" s="9">
         <v>600.0</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J56" s="12"/>
@@ -11858,7 +11887,7 @@
         <v>46240.0</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="9">
@@ -11876,7 +11905,7 @@
       <c r="H57" s="9">
         <v>300.0</v>
       </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J57" s="12"/>
@@ -11886,7 +11915,7 @@
         <v>46244.0</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C58" s="14"/>
       <c r="D58" s="9">
@@ -11904,17 +11933,17 @@
       <c r="H58" s="9">
         <v>5100.0</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J58" s="12"/>
     </row>
     <row r="59" ht="22.5" hidden="1" customHeight="1">
-      <c r="A59" s="5">
+      <c r="A59" s="4">
         <v>46245.0</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C59" s="14"/>
       <c r="D59" s="9">
@@ -11932,17 +11961,17 @@
       <c r="H59" s="9">
         <v>42960.0</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J59" s="12"/>
     </row>
     <row r="60" ht="22.5" hidden="1" customHeight="1">
-      <c r="A60" s="5">
+      <c r="A60" s="4">
         <v>46246.0</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C60" s="14"/>
       <c r="D60" s="9">
@@ -11960,17 +11989,17 @@
       <c r="H60" s="9">
         <v>5400.0</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="12"/>
     </row>
     <row r="61" ht="22.5" hidden="1" customHeight="1">
-      <c r="A61" s="5">
+      <c r="A61" s="4">
         <v>46247.0</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="9">
@@ -11988,17 +12017,17 @@
       <c r="H61" s="9">
         <v>20100.0</v>
       </c>
-      <c r="I61" s="11" t="s">
-        <v>16</v>
+      <c r="I61" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J61" s="12"/>
     </row>
     <row r="62" ht="22.5" hidden="1" customHeight="1">
-      <c r="A62" s="5">
+      <c r="A62" s="4">
         <v>46247.0</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="9">
@@ -12016,24 +12045,24 @@
       <c r="H62" s="9">
         <v>8400.0</v>
       </c>
-      <c r="I62" s="11" t="s">
-        <v>16</v>
+      <c r="I62" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J62" s="12"/>
     </row>
     <row r="63" ht="22.5" hidden="1" customHeight="1">
-      <c r="A63" s="5">
+      <c r="A63" s="4">
         <v>46247.0</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" s="14"/>
       <c r="D63" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" s="9">
         <v>61250.0</v>
@@ -12044,17 +12073,17 @@
       <c r="H63" s="9">
         <v>76033.0</v>
       </c>
-      <c r="I63" s="11" t="s">
-        <v>16</v>
+      <c r="I63" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J63" s="12"/>
     </row>
     <row r="64" ht="22.5" hidden="1" customHeight="1">
-      <c r="A64" s="5">
+      <c r="A64" s="4">
         <v>46247.0</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C64" s="14"/>
       <c r="D64" s="9">
@@ -12072,15 +12101,15 @@
       <c r="H64" s="9">
         <v>73440.0</v>
       </c>
-      <c r="I64" s="11" t="s">
-        <v>16</v>
+      <c r="I64" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J64" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" ht="19.5" hidden="1" customHeight="1">
-      <c r="A65" s="5">
+      <c r="A65" s="4">
         <v>46248.0</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -12102,26 +12131,26 @@
       <c r="H65" s="9">
         <v>72480.0</v>
       </c>
-      <c r="I65" s="11" t="s">
-        <v>34</v>
+      <c r="I65" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" ht="19.5" hidden="1" customHeight="1">
-      <c r="A66" s="5">
+      <c r="A66" s="4">
         <v>46248.0</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="9">
         <v>73001.0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F66" s="9">
         <v>31772.0</v>
@@ -12132,19 +12161,19 @@
       <c r="H66" s="9">
         <v>28820.0</v>
       </c>
-      <c r="I66" s="11" t="s">
-        <v>16</v>
+      <c r="I66" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J66" s="12" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="67" ht="19.5" hidden="1" customHeight="1">
-      <c r="A67" s="5">
+      <c r="A67" s="4">
         <v>46254.0</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="9">
@@ -12162,19 +12191,19 @@
       <c r="H67" s="9">
         <v>78125.0</v>
       </c>
-      <c r="I67" s="11" t="s">
-        <v>16</v>
+      <c r="I67" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" ht="19.5" hidden="1" customHeight="1">
-      <c r="A68" s="5">
+      <c r="A68" s="4">
         <v>46254.0</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="9">
@@ -12192,15 +12221,15 @@
       <c r="H68" s="9">
         <v>18000.0</v>
       </c>
-      <c r="I68" s="11" t="s">
-        <v>16</v>
+      <c r="I68" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J68" s="21" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="69" ht="19.5" hidden="1" customHeight="1">
-      <c r="A69" s="5">
+      <c r="A69" s="4">
         <v>46254.0</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -12222,19 +12251,19 @@
       <c r="H69" s="9">
         <v>120.0</v>
       </c>
-      <c r="I69" s="11" t="s">
-        <v>34</v>
+      <c r="I69" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J69" s="12" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="70" ht="19.5" hidden="1" customHeight="1">
-      <c r="A70" s="5">
+      <c r="A70" s="4">
         <v>46254.0</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="9">
@@ -12252,19 +12281,19 @@
       <c r="H70" s="9">
         <v>9270.0</v>
       </c>
-      <c r="I70" s="11" t="s">
-        <v>16</v>
+      <c r="I70" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J70" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="71" ht="19.5" hidden="1" customHeight="1">
-      <c r="A71" s="5">
+      <c r="A71" s="4">
         <v>46254.0</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C71" s="14"/>
       <c r="D71" s="9">
@@ -12282,19 +12311,19 @@
       <c r="H71" s="9">
         <v>5700.0</v>
       </c>
-      <c r="I71" s="11" t="s">
-        <v>16</v>
+      <c r="I71" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J71" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="72" ht="19.5" hidden="1" customHeight="1">
-      <c r="A72" s="5">
+      <c r="A72" s="4">
         <v>46254.0</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="9">
@@ -12312,19 +12341,19 @@
       <c r="H72" s="9">
         <v>2340.0</v>
       </c>
-      <c r="I72" s="11" t="s">
-        <v>16</v>
+      <c r="I72" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J72" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="73" ht="22.5" hidden="1" customHeight="1">
-      <c r="A73" s="5">
+      <c r="A73" s="4">
         <v>46255.0</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C73" s="14"/>
       <c r="D73" s="9">
@@ -12342,7 +12371,7 @@
       <c r="H73" s="9">
         <v>23165.0</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J73" s="12" t="s">
@@ -12350,18 +12379,18 @@
       </c>
     </row>
     <row r="74" ht="22.5" hidden="1" customHeight="1">
-      <c r="A74" s="5">
+      <c r="A74" s="4">
         <v>46255.0</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C74" s="14"/>
       <c r="D74" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="9">
         <v>72060.0</v>
@@ -12372,26 +12401,26 @@
       <c r="H74" s="9">
         <v>133320.0</v>
       </c>
-      <c r="I74" s="11" t="s">
-        <v>16</v>
+      <c r="I74" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J74" s="12" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="75" ht="22.5" hidden="1" customHeight="1">
-      <c r="A75" s="5">
+      <c r="A75" s="4">
         <v>46255.0</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C75" s="14"/>
       <c r="D75" s="9">
         <v>152384.0</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F75" s="9">
         <v>6600.0</v>
@@ -12402,8 +12431,8 @@
       <c r="H75" s="9">
         <v>1200.0</v>
       </c>
-      <c r="I75" s="11" t="s">
-        <v>16</v>
+      <c r="I75" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J75" s="12" t="s">
         <v>128</v>
@@ -12414,7 +12443,7 @@
         <v>46256.0</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C76" s="14"/>
       <c r="D76" s="9">
@@ -12432,8 +12461,8 @@
       <c r="H76" s="9">
         <v>288.0</v>
       </c>
-      <c r="I76" s="11" t="s">
-        <v>16</v>
+      <c r="I76" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J76" s="12" t="s">
         <v>132</v>
@@ -12444,7 +12473,7 @@
         <v>46261.0</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C77" s="14"/>
       <c r="D77" s="9">
@@ -12462,7 +12491,7 @@
       <c r="H77" s="9">
         <v>2670.0</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J77" s="12"/>
@@ -12472,7 +12501,7 @@
         <v>46261.0</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C78" s="14"/>
       <c r="D78" s="9">
@@ -12490,8 +12519,8 @@
       <c r="H78" s="9">
         <v>3600.0</v>
       </c>
-      <c r="I78" s="11" t="s">
-        <v>34</v>
+      <c r="I78" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J78" s="12"/>
     </row>
@@ -12500,7 +12529,7 @@
         <v>46262.0</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C79" s="14"/>
       <c r="D79" s="9">
@@ -12518,8 +12547,8 @@
       <c r="H79" s="9">
         <v>125400.0</v>
       </c>
-      <c r="I79" s="11" t="s">
-        <v>34</v>
+      <c r="I79" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J79" s="12"/>
     </row>
@@ -12528,7 +12557,7 @@
         <v>46262.0</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C80" s="14"/>
       <c r="D80" s="9">
@@ -12546,8 +12575,8 @@
       <c r="H80" s="9">
         <v>10800.0</v>
       </c>
-      <c r="I80" s="11" t="s">
-        <v>34</v>
+      <c r="I80" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J80" s="12"/>
     </row>
@@ -12556,7 +12585,7 @@
         <v>46262.0</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="9">
@@ -12574,8 +12603,8 @@
       <c r="H81" s="9">
         <v>6300.0</v>
       </c>
-      <c r="I81" s="11" t="s">
-        <v>34</v>
+      <c r="I81" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -12584,7 +12613,7 @@
         <v>46262.0</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C82" s="14"/>
       <c r="D82" s="9">
@@ -12602,8 +12631,8 @@
       <c r="H82" s="9">
         <v>1560.0</v>
       </c>
-      <c r="I82" s="11" t="s">
-        <v>34</v>
+      <c r="I82" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J82" s="12"/>
     </row>
@@ -12612,7 +12641,7 @@
         <v>46262.0</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="9">
@@ -12630,17 +12659,17 @@
       <c r="H83" s="9">
         <v>100.0</v>
       </c>
-      <c r="I83" s="11" t="s">
-        <v>34</v>
+      <c r="I83" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J83" s="12"/>
     </row>
     <row r="84" ht="22.5" hidden="1" customHeight="1">
-      <c r="A84" s="5">
+      <c r="A84" s="4">
         <v>46265.0</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="9">
@@ -12658,17 +12687,17 @@
       <c r="H84" s="9">
         <v>1200.0</v>
       </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J84" s="12"/>
     </row>
     <row r="85" ht="22.5" hidden="1" customHeight="1">
-      <c r="A85" s="5">
+      <c r="A85" s="4">
         <v>46265.0</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C85" s="14"/>
       <c r="D85" s="9">
@@ -12686,17 +12715,17 @@
       <c r="H85" s="9">
         <v>1200.0</v>
       </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J85" s="12"/>
     </row>
     <row r="86" ht="22.5" hidden="1" customHeight="1">
-      <c r="A86" s="5">
+      <c r="A86" s="4">
         <v>46265.0</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="9">
@@ -12714,17 +12743,17 @@
       <c r="H86" s="9">
         <v>36864.0</v>
       </c>
-      <c r="I86" s="11" t="s">
-        <v>34</v>
+      <c r="I86" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J86" s="12"/>
     </row>
     <row r="87" ht="22.5" hidden="1" customHeight="1">
-      <c r="A87" s="5">
+      <c r="A87" s="4">
         <v>46265.0</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="9">
@@ -12742,17 +12771,17 @@
       <c r="H87" s="9">
         <v>138480.0</v>
       </c>
-      <c r="I87" s="11" t="s">
-        <v>47</v>
+      <c r="I87" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J87" s="12"/>
     </row>
     <row r="88" ht="22.5" hidden="1" customHeight="1">
-      <c r="A88" s="5">
+      <c r="A88" s="4">
         <v>46265.0</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="9">
@@ -12770,24 +12799,24 @@
       <c r="H88" s="9">
         <v>600.0</v>
       </c>
-      <c r="I88" s="11" t="s">
-        <v>34</v>
+      <c r="I88" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J88" s="12"/>
     </row>
     <row r="89" ht="22.5" hidden="1" customHeight="1">
-      <c r="A89" s="5">
+      <c r="A89" s="4">
         <v>46267.0</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="9">
         <v>73001.0</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F89" s="9">
         <v>82903.0</v>
@@ -12798,24 +12827,24 @@
       <c r="H89" s="9">
         <v>27336.0</v>
       </c>
-      <c r="I89" s="11" t="s">
-        <v>15</v>
+      <c r="I89" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J89" s="12"/>
     </row>
     <row r="90" ht="22.5" hidden="1" customHeight="1">
-      <c r="A90" s="5">
+      <c r="A90" s="4">
         <v>46268.0</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="9">
         <v>2010102.0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F90" s="9">
         <v>2938.0</v>
@@ -12826,24 +12855,24 @@
       <c r="H90" s="9">
         <v>6058.0</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J90" s="12"/>
     </row>
     <row r="91" ht="22.5" hidden="1" customHeight="1">
-      <c r="A91" s="5">
+      <c r="A91" s="4">
         <v>46269.0</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="9">
         <v>2110427.0</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F91" s="9">
         <v>11520.0</v>
@@ -12854,17 +12883,17 @@
       <c r="H91" s="9">
         <v>17280.0</v>
       </c>
-      <c r="I91" s="11" t="s">
-        <v>15</v>
+      <c r="I91" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J91" s="12"/>
     </row>
     <row r="92" ht="22.5" hidden="1" customHeight="1">
-      <c r="A92" s="5">
+      <c r="A92" s="4">
         <v>46269.0</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="9">
@@ -12882,17 +12911,17 @@
       <c r="H92" s="9">
         <v>232806.0</v>
       </c>
-      <c r="I92" s="11" t="s">
-        <v>15</v>
+      <c r="I92" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J92" s="12"/>
     </row>
     <row r="93" ht="22.5" hidden="1" customHeight="1">
-      <c r="A93" s="5">
+      <c r="A93" s="4">
         <v>46269.0</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="9">
@@ -12910,24 +12939,24 @@
       <c r="H93" s="9">
         <v>4500.0</v>
       </c>
-      <c r="I93" s="11" t="s">
-        <v>15</v>
+      <c r="I93" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J93" s="12"/>
     </row>
     <row r="94" ht="22.5" hidden="1" customHeight="1">
-      <c r="A94" s="5">
+      <c r="A94" s="4">
         <v>46269.0</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F94" s="9">
         <v>5040.0</v>
@@ -12938,24 +12967,24 @@
       <c r="H94" s="9">
         <v>4140.0</v>
       </c>
-      <c r="I94" s="11" t="s">
-        <v>15</v>
+      <c r="I94" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J94" s="12"/>
     </row>
     <row r="95" ht="22.5" hidden="1" customHeight="1">
-      <c r="A95" s="5">
+      <c r="A95" s="4">
         <v>46272.0</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="9">
         <v>2110402.0</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F95" s="9">
         <v>420158.0</v>
@@ -12966,17 +12995,17 @@
       <c r="H95" s="9">
         <v>101620.0</v>
       </c>
-      <c r="I95" s="11" t="s">
-        <v>15</v>
+      <c r="I95" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J95" s="12"/>
     </row>
     <row r="96" ht="22.5" hidden="1" customHeight="1">
-      <c r="A96" s="5">
+      <c r="A96" s="4">
         <v>46272.0</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="9">
@@ -12994,24 +13023,24 @@
       <c r="H96" s="9">
         <v>302802.0</v>
       </c>
-      <c r="I96" s="11" t="s">
+      <c r="I96" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J96" s="12"/>
     </row>
     <row r="97" ht="22.5" hidden="1" customHeight="1">
-      <c r="A97" s="5">
+      <c r="A97" s="4">
         <v>46272.0</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="9">
         <v>272003.0</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F97" s="9">
         <v>25404.0</v>
@@ -13022,24 +13051,24 @@
       <c r="H97" s="9">
         <v>8040.0</v>
       </c>
-      <c r="I97" s="11" t="s">
-        <v>15</v>
+      <c r="I97" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J97" s="12"/>
     </row>
     <row r="98" ht="22.5" hidden="1" customHeight="1">
-      <c r="A98" s="5">
+      <c r="A98" s="4">
         <v>46272.0</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F98" s="9">
         <v>4140.0</v>
@@ -13050,24 +13079,24 @@
       <c r="H98" s="9">
         <v>4320.0</v>
       </c>
-      <c r="I98" s="11" t="s">
-        <v>15</v>
+      <c r="I98" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J98" s="12"/>
     </row>
     <row r="99" ht="22.5" hidden="1" customHeight="1">
-      <c r="A99" s="5">
+      <c r="A99" s="4">
         <v>46272.0</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="9">
         <v>273003.0</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F99" s="9">
         <v>12100.0</v>
@@ -13078,24 +13107,24 @@
       <c r="H99" s="9">
         <v>3900.0</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="I99" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J99" s="12"/>
     </row>
     <row r="100" ht="22.5" hidden="1" customHeight="1">
-      <c r="A100" s="5">
+      <c r="A100" s="4">
         <v>46272.0</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C100" s="14"/>
       <c r="D100" s="9">
         <v>2114268.0</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F100" s="9">
         <v>180.0</v>
@@ -13106,17 +13135,17 @@
       <c r="H100" s="9">
         <v>180.0</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I100" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J100" s="12"/>
     </row>
     <row r="101" ht="22.5" hidden="1" customHeight="1">
-      <c r="A101" s="5">
+      <c r="A101" s="4">
         <v>46274.0</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C101" s="14"/>
       <c r="D101" s="9">
@@ -13134,17 +13163,17 @@
       <c r="H101" s="9">
         <v>2400.0</v>
       </c>
-      <c r="I101" s="11" t="s">
-        <v>15</v>
+      <c r="I101" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J101" s="12"/>
     </row>
     <row r="102" ht="22.5" hidden="1" customHeight="1">
-      <c r="A102" s="5">
+      <c r="A102" s="4">
         <v>46274.0</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C102" s="14"/>
       <c r="D102" s="9">
@@ -13162,13 +13191,13 @@
       <c r="H102" s="9">
         <v>240.0</v>
       </c>
-      <c r="I102" s="11" t="s">
-        <v>15</v>
+      <c r="I102" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J102" s="12"/>
     </row>
     <row r="103" ht="22.5" hidden="1" customHeight="1">
-      <c r="A103" s="5">
+      <c r="A103" s="4">
         <v>46274.0</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -13179,7 +13208,7 @@
         <v>2410401.0</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F103" s="9">
         <v>118286.0</v>
@@ -13190,24 +13219,24 @@
       <c r="H103" s="9">
         <v>247766.0</v>
       </c>
-      <c r="I103" s="11" t="s">
+      <c r="I103" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J103" s="12"/>
     </row>
     <row r="104" ht="22.5" hidden="1" customHeight="1">
-      <c r="A104" s="5">
+      <c r="A104" s="4">
         <v>46276.0</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C104" s="14"/>
       <c r="D104" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F104" s="9">
         <v>264061.0</v>
@@ -13218,24 +13247,24 @@
       <c r="H104" s="9">
         <v>141318.0</v>
       </c>
-      <c r="I104" s="11" t="s">
-        <v>16</v>
+      <c r="I104" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J104" s="12"/>
     </row>
     <row r="105" ht="22.5" hidden="1" customHeight="1">
-      <c r="A105" s="5">
+      <c r="A105" s="4">
         <v>46276.0</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C105" s="14"/>
       <c r="D105" s="9">
         <v>273003.0</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F105" s="9">
         <v>9106.0</v>
@@ -13246,13 +13275,13 @@
       <c r="H105" s="9">
         <v>13876.0</v>
       </c>
-      <c r="I105" s="11" t="s">
-        <v>16</v>
+      <c r="I105" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J105" s="12"/>
     </row>
     <row r="106" ht="22.5" hidden="1" customHeight="1">
-      <c r="A106" s="5">
+      <c r="A106" s="4">
         <v>46276.0</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -13274,24 +13303,24 @@
       <c r="H106" s="9">
         <v>7017.0</v>
       </c>
-      <c r="I106" s="11" t="s">
-        <v>16</v>
+      <c r="I106" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J106" s="12"/>
     </row>
     <row r="107" ht="22.5" customHeight="1">
-      <c r="A107" s="5">
+      <c r="A107" s="4">
         <v>46279.0</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="9">
         <v>2110202.0</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" s="9">
         <v>445991.0</v>
@@ -13302,19 +13331,19 @@
       <c r="H107" s="9">
         <v>221756.0</v>
       </c>
-      <c r="I107" s="11" t="s">
-        <v>16</v>
+      <c r="I107" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J107" s="12" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
-      <c r="A108" s="5">
+      <c r="A108" s="4">
         <v>46279.0</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="9">
@@ -13332,13 +13361,13 @@
       <c r="H108" s="9">
         <v>180.0</v>
       </c>
-      <c r="I108" s="11" t="s">
-        <v>16</v>
+      <c r="I108" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J108" s="12"/>
     </row>
     <row r="109" ht="22.5" customHeight="1">
-      <c r="A109" s="5">
+      <c r="A109" s="4">
         <v>46281.0</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -13349,7 +13378,7 @@
         <v>2010102.0</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F109" s="9">
         <v>35.0</v>
@@ -13360,26 +13389,26 @@
       <c r="H109" s="9">
         <v>2235.0</v>
       </c>
-      <c r="I109" s="11" t="s">
-        <v>16</v>
+      <c r="I109" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
-      <c r="A110" s="5">
+      <c r="A110" s="4">
         <v>46281.0</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="9">
         <v>2010301.0</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F110" s="9">
         <v>213392.0</v>
@@ -13390,15 +13419,15 @@
       <c r="H110" s="9">
         <v>106351.0</v>
       </c>
-      <c r="I110" s="11" t="s">
-        <v>15</v>
+      <c r="I110" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
-      <c r="A111" s="5">
+      <c r="A111" s="4">
         <v>46281.0</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -13409,7 +13438,7 @@
         <v>2110202.0</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F111" s="9">
         <v>34327.0</v>
@@ -13420,24 +13449,24 @@
       <c r="H111" s="9">
         <v>132072.0</v>
       </c>
-      <c r="I111" s="11" t="s">
-        <v>34</v>
+      <c r="I111" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="J111" s="12"/>
     </row>
     <row r="112" ht="22.5" customHeight="1">
-      <c r="A112" s="5">
+      <c r="A112" s="4">
         <v>46281.0</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="9">
         <v>2410401.0</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F112" s="9">
         <v>177481.0</v>
@@ -13448,24 +13477,24 @@
       <c r="H112" s="9">
         <v>12301.0</v>
       </c>
-      <c r="I112" s="11" t="s">
-        <v>15</v>
+      <c r="I112" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J112" s="12"/>
     </row>
     <row r="113" ht="22.5" customHeight="1">
-      <c r="A113" s="5">
+      <c r="A113" s="4">
         <v>46283.0</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F113" s="9">
         <v>9720.0</v>
@@ -13476,17 +13505,17 @@
       <c r="H113" s="9">
         <v>5220.0</v>
       </c>
-      <c r="I113" s="11" t="s">
-        <v>15</v>
+      <c r="I113" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J113" s="12"/>
     </row>
     <row r="114" ht="22.5" customHeight="1">
-      <c r="A114" s="5">
+      <c r="A114" s="4">
         <v>46286.0</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C114" s="14"/>
       <c r="D114" s="9">
@@ -13504,13 +13533,13 @@
       <c r="H114" s="9">
         <v>1477.0</v>
       </c>
-      <c r="I114" s="11" t="s">
+      <c r="I114" s="10" t="s">
         <v>22</v>
       </c>
       <c r="J114" s="12"/>
     </row>
     <row r="115" ht="22.5" customHeight="1">
-      <c r="A115" s="5">
+      <c r="A115" s="4">
         <v>46287.0</v>
       </c>
       <c r="B115" s="6" t="s">
@@ -13521,7 +13550,7 @@
         <v>2110402.0</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F115" s="9">
         <v>67463.0</v>
@@ -13532,24 +13561,24 @@
       <c r="H115" s="9">
         <v>15862.0</v>
       </c>
-      <c r="I115" s="11" t="s">
+      <c r="I115" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J115" s="12"/>
     </row>
     <row r="116" ht="22.5" customHeight="1">
-      <c r="A116" s="5">
+      <c r="A116" s="4">
         <v>46289.0</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C116" s="14"/>
       <c r="D116" s="9">
         <v>2152388.0</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F116" s="9">
         <v>5940.0</v>
@@ -13560,17 +13589,17 @@
       <c r="H116" s="9">
         <v>19980.0</v>
       </c>
-      <c r="I116" s="11" t="s">
-        <v>15</v>
+      <c r="I116" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="J116" s="12"/>
     </row>
     <row r="117" ht="22.5" customHeight="1">
-      <c r="A117" s="5">
+      <c r="A117" s="4">
         <v>46290.0</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="9">
@@ -13588,7 +13617,7 @@
       <c r="H117" s="9">
         <v>322380.0</v>
       </c>
-      <c r="I117" s="11"/>
+      <c r="I117" s="10"/>
       <c r="J117" s="12"/>
     </row>
     <row r="118">
